--- a/model/Outputs/11. Interest rate/30/Output Files/0.2/Output_12_45.xlsx
+++ b/model/Outputs/11. Interest rate/30/Output Files/0.2/Output_12_45.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3800500.790464131</v>
+        <v>3801728.663933934</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13595871.02547102</v>
+        <v>13587736.64870331</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13595871.02547102</v>
+        <v>13587736.64870331</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8356.225371576738</v>
+        <v>3650.182857150161</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8356.225371576738</v>
+        <v>3650.182857150161</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22440453.60293263</v>
+        <v>22442715.21014111</v>
       </c>
     </row>
   </sheetData>
@@ -669,13 +669,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>3.343301935257443</v>
+        <v>3.343301935256358</v>
       </c>
       <c r="H2" t="n">
-        <v>5.722467174369123</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1.953406460792517</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -748,10 +748,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>325.517988705216</v>
+        <v>157.8940948334924</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I3" t="n">
         <v>209.4985557026693</v>
@@ -790,16 +790,16 @@
         <v>4.464774651476091</v>
       </c>
       <c r="U3" t="n">
-        <v>374</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
-        <v>32.37314290982852</v>
+        <v>374</v>
       </c>
       <c r="X3" t="n">
-        <v>150.0898948934622</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -912,7 +912,7 @@
         <v>3.769060713577687</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.953406460791434</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.953406460791602</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>85.41253966161941</v>
@@ -979,7 +979,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R6" t="n">
         <v>133.5184388018132</v>
@@ -1027,19 +1027,19 @@
         <v>4.464774651476091</v>
       </c>
       <c r="U6" t="n">
-        <v>142.8978172642599</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V6" t="n">
-        <v>14.51066719152016</v>
+        <v>374</v>
       </c>
       <c r="W6" t="n">
-        <v>374</v>
+        <v>43.74163974169163</v>
       </c>
       <c r="X6" t="n">
         <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1146,7 +1146,7 @@
         <v>3.343301935257443</v>
       </c>
       <c r="H8" t="n">
-        <v>3.769060713577687</v>
+        <v>5.722467174369123</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.953406460791602</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>85.41253966161941</v>
@@ -1213,10 +1213,10 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1225,7 +1225,7 @@
         <v>325.517988705216</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>144.7989632036872</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>133.5184388018132</v>
@@ -1264,7 +1264,7 @@
         <v>4.464774651476091</v>
       </c>
       <c r="U9" t="n">
-        <v>365.7880242530416</v>
+        <v>185.8241691913804</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
@@ -1380,13 +1380,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>81.36239741264436</v>
+        <v>81.36641751314687</v>
       </c>
       <c r="H11" t="n">
-        <v>72.72337227136661</v>
+        <v>72.76454312563797</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.7700245512435931</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1416,13 +1416,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>142.0601778525742</v>
+        <v>142.1517858927752</v>
       </c>
       <c r="T11" t="n">
-        <v>259.5690792160011</v>
+        <v>259.5866772059508</v>
       </c>
       <c r="U11" t="n">
-        <v>325.1536417028693</v>
+        <v>328.1100201667011</v>
       </c>
       <c r="V11" t="n">
         <v>308.8510241668239</v>
@@ -1456,16 +1456,16 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F12" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G12" t="n">
-        <v>187.1524252956803</v>
+        <v>3.995309459933003</v>
       </c>
       <c r="H12" t="n">
-        <v>3.95965322415698</v>
+        <v>324.9804268090626</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>191.5028009856882</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1492,28 +1492,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>179.932929367851</v>
+        <v>180.0664765376623</v>
       </c>
       <c r="S12" t="n">
-        <v>131.7003678891396</v>
+        <v>131.7403207193283</v>
       </c>
       <c r="T12" t="n">
-        <v>81.34934068921193</v>
+        <v>390.8253259949312</v>
       </c>
       <c r="U12" t="n">
-        <v>79.16125598660184</v>
+        <v>79.1613974960358</v>
       </c>
       <c r="V12" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W12" t="n">
         <v>111.3731429098285</v>
       </c>
       <c r="X12" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y12" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="13">
@@ -1553,28 +1553,28 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>9.517497010238188</v>
+        <v>9.785595370893915</v>
       </c>
       <c r="M13" t="n">
-        <v>101.5443818943532</v>
+        <v>101.8270540255007</v>
       </c>
       <c r="N13" t="n">
-        <v>154.4301408454554</v>
+        <v>154.7060916651275</v>
       </c>
       <c r="O13" t="n">
-        <v>231.0003837511461</v>
+        <v>231.2552689970477</v>
       </c>
       <c r="P13" t="n">
-        <v>290.7677661807365</v>
+        <v>290.9858645413923</v>
       </c>
       <c r="Q13" t="n">
-        <v>352.442266425598</v>
+        <v>352.593266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>377.4666853582003</v>
+        <v>377.5477673254134</v>
       </c>
       <c r="S13" t="n">
-        <v>30.46857806351117</v>
+        <v>30.50000429301937</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1617,13 +1617,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>78.40634055685268</v>
+        <v>81.36641751314687</v>
       </c>
       <c r="H14" t="n">
-        <v>72.7233722713666</v>
+        <v>72.76454312563794</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.7700245512436212</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1653,13 +1653,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>142.0601778525742</v>
+        <v>142.1517858927751</v>
       </c>
       <c r="T14" t="n">
-        <v>259.5690792160011</v>
+        <v>259.5866772059508</v>
       </c>
       <c r="U14" t="n">
-        <v>328.109698558661</v>
+        <v>328.1100201667011</v>
       </c>
       <c r="V14" t="n">
         <v>308.8510241668239</v>
@@ -1684,25 +1684,25 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C15" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D15" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E15" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F15" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G15" t="n">
-        <v>316.7236809137657</v>
+        <v>3.995309459933026</v>
       </c>
       <c r="H15" t="n">
-        <v>3.959653224156966</v>
+        <v>324.9804268090626</v>
       </c>
       <c r="I15" t="n">
-        <v>191.4287443819146</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1729,19 +1729,19 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>179.932929367851</v>
+        <v>180.0664765376623</v>
       </c>
       <c r="S15" t="n">
-        <v>131.7003678891396</v>
+        <v>131.7403207193283</v>
       </c>
       <c r="T15" t="n">
-        <v>81.34934068921194</v>
+        <v>81.35801050053266</v>
       </c>
       <c r="U15" t="n">
-        <v>79.16125598660182</v>
+        <v>400.1613974960358</v>
       </c>
       <c r="V15" t="n">
-        <v>93.51066719152016</v>
+        <v>273.4807836716068</v>
       </c>
       <c r="W15" t="n">
         <v>111.3731429098285</v>
@@ -1790,28 +1790,28 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>9.517497010238174</v>
+        <v>9.78559537089393</v>
       </c>
       <c r="M16" t="n">
-        <v>101.5443818943532</v>
+        <v>101.8270540255007</v>
       </c>
       <c r="N16" t="n">
-        <v>154.4301408454554</v>
+        <v>154.7060916651275</v>
       </c>
       <c r="O16" t="n">
-        <v>231.000383751146</v>
+        <v>231.2552689970478</v>
       </c>
       <c r="P16" t="n">
-        <v>290.7677661807365</v>
+        <v>290.9858645413923</v>
       </c>
       <c r="Q16" t="n">
-        <v>352.4422664255979</v>
+        <v>352.593266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>377.4666853582003</v>
+        <v>377.5477673254134</v>
       </c>
       <c r="S16" t="n">
-        <v>30.46857806351119</v>
+        <v>30.5000042930194</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1857,7 +1857,7 @@
         <v>81.36239741264433</v>
       </c>
       <c r="H17" t="n">
-        <v>72.7233722713666</v>
+        <v>73.64811541557496</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1902,7 +1902,7 @@
         <v>308.8510241668239</v>
       </c>
       <c r="W17" t="n">
-        <v>314.4174191251558</v>
+        <v>317.3734759809475</v>
       </c>
       <c r="X17" t="n">
         <v>271.2818334606677</v>
@@ -1921,19 +1921,19 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D18" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E18" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F18" t="n">
-        <v>123.9906591208807</v>
+        <v>201.7955091170206</v>
       </c>
       <c r="G18" t="n">
-        <v>3.993158516536766</v>
+        <v>324.9931585165368</v>
       </c>
       <c r="H18" t="n">
         <v>3.959653224156966</v>
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>77.80484999613995</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>179.932929367851</v>
@@ -1978,13 +1978,13 @@
         <v>79.16125598660182</v>
       </c>
       <c r="V18" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W18" t="n">
         <v>111.3731429098285</v>
       </c>
       <c r="X18" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y18" t="n">
         <v>78.39139276613435</v>
@@ -2091,7 +2091,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G20" t="n">
-        <v>78.40634055685268</v>
+        <v>81.36239741264433</v>
       </c>
       <c r="H20" t="n">
         <v>72.7233722713666</v>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.9247431442083234</v>
       </c>
       <c r="S20" t="n">
         <v>142.0601778525742</v>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>246.7158234254704</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C21" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D21" t="n">
-        <v>347.9376868977026</v>
+        <v>210.0969536768464</v>
       </c>
       <c r="E21" t="n">
         <v>21.67209722191262</v>
@@ -2170,7 +2170,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
-        <v>3.993158516536766</v>
+        <v>324.9931585165368</v>
       </c>
       <c r="H21" t="n">
         <v>3.959653224156966</v>
@@ -2209,7 +2209,7 @@
         <v>131.7003678891396</v>
       </c>
       <c r="T21" t="n">
-        <v>81.34934068921194</v>
+        <v>402.3493406892119</v>
       </c>
       <c r="U21" t="n">
         <v>79.16125598660182</v>
@@ -2331,7 +2331,7 @@
         <v>81.36239741264433</v>
       </c>
       <c r="H23" t="n">
-        <v>69.76731541560423</v>
+        <v>72.7233722713666</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.9247431442083234</v>
       </c>
       <c r="S23" t="n">
         <v>142.0601778525742</v>
@@ -2395,22 +2395,22 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>223.2591792246631</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E24" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F24" t="n">
-        <v>339.6362423378769</v>
+        <v>123.9906591208807</v>
       </c>
       <c r="G24" t="n">
         <v>3.993158516536766</v>
       </c>
       <c r="H24" t="n">
-        <v>3.959653224156966</v>
+        <v>324.959653224157</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R24" t="n">
         <v>179.932929367851</v>
       </c>
       <c r="S24" t="n">
-        <v>131.7003678891396</v>
+        <v>452.7003678891396</v>
       </c>
       <c r="T24" t="n">
         <v>81.34934068921194</v>
@@ -2461,7 +2461,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y24" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="25">
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>0.9247431442083234</v>
       </c>
       <c r="S26" t="n">
         <v>142.0601778525742</v>
@@ -2613,7 +2613,7 @@
         <v>308.8510241668239</v>
       </c>
       <c r="W26" t="n">
-        <v>314.4174191251689</v>
+        <v>317.3734759809475</v>
       </c>
       <c r="X26" t="n">
         <v>271.2818334606677</v>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C27" t="n">
         <v>40.09991244551929</v>
@@ -2647,10 +2647,10 @@
         <v>3.993158516536777</v>
       </c>
       <c r="H27" t="n">
-        <v>3.95965322415698</v>
+        <v>324.959653224157</v>
       </c>
       <c r="I27" t="n">
-        <v>191.4287443819146</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>77.80484999613995</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>179.932929367851</v>
@@ -2683,19 +2683,19 @@
         <v>131.7003678891396</v>
       </c>
       <c r="T27" t="n">
-        <v>81.34934068921193</v>
+        <v>264.5086074683554</v>
       </c>
       <c r="U27" t="n">
-        <v>79.16125598660184</v>
+        <v>400.1612559866018</v>
       </c>
       <c r="V27" t="n">
-        <v>328.4363395926093</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W27" t="n">
         <v>111.3731429098285</v>
       </c>
       <c r="X27" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y27" t="n">
         <v>78.39139276613435</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>0.9247431442083234</v>
       </c>
       <c r="S29" t="n">
         <v>142.0601778525742</v>
@@ -2850,7 +2850,7 @@
         <v>308.8510241668239</v>
       </c>
       <c r="W29" t="n">
-        <v>314.4174191251687</v>
+        <v>317.3734759809475</v>
       </c>
       <c r="X29" t="n">
         <v>271.2818334606677</v>
@@ -2866,16 +2866,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>168.9109734293301</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C30" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D30" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E30" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F30" t="n">
         <v>18.63624233787687</v>
@@ -2884,7 +2884,7 @@
         <v>3.993158516536766</v>
       </c>
       <c r="H30" t="n">
-        <v>3.959653224156966</v>
+        <v>187.1189200033005</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2911,7 +2911,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>77.80484999613995</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>179.932929367851</v>
@@ -2935,7 +2935,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y30" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="31">
@@ -3039,10 +3039,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G32" t="n">
-        <v>81.36239741264433</v>
+        <v>81.36239741264436</v>
       </c>
       <c r="H32" t="n">
-        <v>69.76731541562378</v>
+        <v>72.72337227136661</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3072,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>0.9247431442083234</v>
       </c>
       <c r="S32" t="n">
         <v>142.0601778525742</v>
@@ -3081,7 +3081,7 @@
         <v>259.5690792160011</v>
       </c>
       <c r="U32" t="n">
-        <v>328.109698558661</v>
+        <v>328.1096985586609</v>
       </c>
       <c r="V32" t="n">
         <v>308.8510241668239</v>
@@ -3106,7 +3106,7 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D33" t="n">
         <v>26.93768689770263</v>
@@ -3115,16 +3115,16 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F33" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G33" t="n">
-        <v>3.993158516536766</v>
+        <v>324.9931585165368</v>
       </c>
       <c r="H33" t="n">
-        <v>3.959653224156966</v>
+        <v>324.959653224157</v>
       </c>
       <c r="I33" t="n">
-        <v>183.1592667791436</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3157,10 +3157,10 @@
         <v>131.7003678891396</v>
       </c>
       <c r="T33" t="n">
-        <v>81.34934068921194</v>
+        <v>402.3493406892119</v>
       </c>
       <c r="U33" t="n">
-        <v>79.16125598660182</v>
+        <v>262.3205227657455</v>
       </c>
       <c r="V33" t="n">
         <v>93.51066719152016</v>
@@ -3169,7 +3169,7 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X33" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y33" t="n">
         <v>78.39139276613435</v>
@@ -3212,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>9.517497010238174</v>
+        <v>9.517497010238188</v>
       </c>
       <c r="M34" t="n">
         <v>101.5443818943532</v>
@@ -3221,19 +3221,19 @@
         <v>154.4301408454554</v>
       </c>
       <c r="O34" t="n">
-        <v>231.000383751146</v>
+        <v>231.0003837511461</v>
       </c>
       <c r="P34" t="n">
         <v>290.7677661807365</v>
       </c>
       <c r="Q34" t="n">
-        <v>352.4422664255979</v>
+        <v>352.442266425598</v>
       </c>
       <c r="R34" t="n">
         <v>377.4666853582003</v>
       </c>
       <c r="S34" t="n">
-        <v>30.46857806351119</v>
+        <v>30.46857806351117</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>136.9993129555745</v>
+        <v>132.4136560998626</v>
       </c>
       <c r="C35" t="n">
         <v>104.4745782429939</v>
@@ -3276,7 +3276,7 @@
         <v>59.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>52.77674055689179</v>
+        <v>57.36239741264433</v>
       </c>
       <c r="H35" t="n">
         <v>48.7233722713666</v>
@@ -3343,13 +3343,13 @@
         <v>39.55655664632661</v>
       </c>
       <c r="C36" t="n">
-        <v>361.0999124455193</v>
+        <v>251.2877334905841</v>
       </c>
       <c r="D36" t="n">
-        <v>9.077305106589106</v>
+        <v>2.937686897702633</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>339.6362423378769</v>
@@ -3361,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>191.4287443819146</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>77.80484999613995</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>155.932929367851</v>
@@ -3397,7 +3397,7 @@
         <v>57.34934068921194</v>
       </c>
       <c r="U36" t="n">
-        <v>55.16125598660187</v>
+        <v>55.16125598660182</v>
       </c>
       <c r="V36" t="n">
         <v>69.51066719152016</v>
@@ -3406,7 +3406,7 @@
         <v>432.3731429098285</v>
       </c>
       <c r="X36" t="n">
-        <v>74.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y36" t="n">
         <v>54.39139276613435</v>
@@ -3516,7 +3516,7 @@
         <v>57.36239741264435</v>
       </c>
       <c r="H38" t="n">
-        <v>48.72337227136661</v>
+        <v>44.13771541563843</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3564,7 +3564,7 @@
         <v>293.3734759809475</v>
       </c>
       <c r="X38" t="n">
-        <v>242.6961766049247</v>
+        <v>247.2818334606677</v>
       </c>
       <c r="Y38" t="n">
         <v>166.3174326828064</v>
@@ -3577,22 +3577,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>384.5565566463266</v>
+        <v>39.55655664632661</v>
       </c>
       <c r="C39" t="n">
-        <v>361.0999124455193</v>
+        <v>16.09991244551929</v>
       </c>
       <c r="D39" t="n">
-        <v>347.9376868977026</v>
+        <v>2.937686897702633</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>78.58071054290289</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>81.61656542696302</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -3634,10 +3634,10 @@
         <v>57.34934068921193</v>
       </c>
       <c r="U39" t="n">
-        <v>55.16125598660184</v>
+        <v>400.1612559866018</v>
       </c>
       <c r="V39" t="n">
-        <v>69.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W39" t="n">
         <v>87.37314290982852</v>
@@ -3646,7 +3646,7 @@
         <v>74.86273944538755</v>
       </c>
       <c r="Y39" t="n">
-        <v>54.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="40">
@@ -3750,10 +3750,10 @@
         <v>59.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>57.36239741264435</v>
+        <v>52.77674055693239</v>
       </c>
       <c r="H41" t="n">
-        <v>44.13771541561404</v>
+        <v>48.7233722713666</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3792,7 +3792,7 @@
         <v>235.5690792160011</v>
       </c>
       <c r="U41" t="n">
-        <v>304.1096985586609</v>
+        <v>304.109698558661</v>
       </c>
       <c r="V41" t="n">
         <v>284.8510241668239</v>
@@ -3817,22 +3817,22 @@
         <v>39.55655664632661</v>
       </c>
       <c r="C42" t="n">
-        <v>42.27987743024889</v>
+        <v>16.09991244551929</v>
       </c>
       <c r="D42" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E42" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>339.6362423378769</v>
+        <v>96.25964924831067</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>324.9931585165368</v>
       </c>
       <c r="H42" t="n">
-        <v>324.959653224157</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3859,22 +3859,22 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>77.80484999613995</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>155.932929367851</v>
+        <v>500.932929367851</v>
       </c>
       <c r="S42" t="n">
         <v>107.7003678891396</v>
       </c>
       <c r="T42" t="n">
-        <v>57.34934068921193</v>
+        <v>57.34934068921194</v>
       </c>
       <c r="U42" t="n">
-        <v>55.16125598660184</v>
+        <v>55.16125598660182</v>
       </c>
       <c r="V42" t="n">
-        <v>69.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W42" t="n">
         <v>87.37314290982852</v>
@@ -3926,25 +3926,25 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>77.54438189435318</v>
+        <v>77.54438189435319</v>
       </c>
       <c r="N43" t="n">
         <v>130.4301408454554</v>
       </c>
       <c r="O43" t="n">
-        <v>207.0003837511461</v>
+        <v>207.000383751146</v>
       </c>
       <c r="P43" t="n">
         <v>266.7677661807365</v>
       </c>
       <c r="Q43" t="n">
-        <v>328.442266425598</v>
+        <v>328.4422664255979</v>
       </c>
       <c r="R43" t="n">
         <v>353.4666853582003</v>
       </c>
       <c r="S43" t="n">
-        <v>6.468578063511176</v>
+        <v>6.468578063511188</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>132.413656099822</v>
+        <v>136.9993129555745</v>
       </c>
       <c r="C44" t="n">
         <v>104.4745782429939</v>
@@ -3987,7 +3987,7 @@
         <v>59.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>57.36239741264435</v>
+        <v>52.77674055693236</v>
       </c>
       <c r="H44" t="n">
         <v>48.72337227136661</v>
@@ -4057,10 +4057,10 @@
         <v>16.09991244551929</v>
       </c>
       <c r="D45" t="n">
-        <v>154.9569002844713</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -4072,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>191.4287443819146</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>77.80484999613995</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>500.932929367851</v>
@@ -4108,13 +4108,13 @@
         <v>57.34934068921193</v>
       </c>
       <c r="U45" t="n">
-        <v>400.1612559866018</v>
+        <v>55.16125598660184</v>
       </c>
       <c r="V45" t="n">
         <v>414.5106671915202</v>
       </c>
       <c r="W45" t="n">
-        <v>87.37314290982852</v>
+        <v>165.9538534527723</v>
       </c>
       <c r="X45" t="n">
         <v>74.86273944538755</v>
@@ -4312,10 +4312,10 @@
         <v>39.07734253497633</v>
       </c>
       <c r="G2" t="n">
-        <v>35.70026987310013</v>
+        <v>35.70026987310122</v>
       </c>
       <c r="H2" t="n">
-        <v>29.92</v>
+        <v>31.89313783918436</v>
       </c>
       <c r="I2" t="n">
         <v>29.92</v>
@@ -4324,16 +4324,16 @@
         <v>400.18</v>
       </c>
       <c r="K2" t="n">
-        <v>452.3245884924623</v>
+        <v>696.8157936111289</v>
       </c>
       <c r="L2" t="n">
-        <v>517.0145614572864</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="M2" t="n">
-        <v>887.2745614572864</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="N2" t="n">
-        <v>1257.534561457286</v>
+        <v>1437.335793611129</v>
       </c>
       <c r="O2" t="n">
         <v>1437.335793611129</v>
@@ -4376,22 +4376,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>570.5406665586214</v>
+        <v>734.5856302651008</v>
       </c>
       <c r="C3" t="n">
-        <v>570.5406665586214</v>
+        <v>734.5856302651008</v>
       </c>
       <c r="D3" t="n">
-        <v>570.5406665586214</v>
+        <v>734.5856302651008</v>
       </c>
       <c r="E3" t="n">
-        <v>570.5406665586214</v>
+        <v>734.5856302651008</v>
       </c>
       <c r="F3" t="n">
-        <v>570.5406665586214</v>
+        <v>734.5856302651008</v>
       </c>
       <c r="G3" t="n">
-        <v>241.7346173614335</v>
+        <v>575.0966455848054</v>
       </c>
       <c r="H3" t="n">
         <v>241.7346173614335</v>
@@ -4433,19 +4433,19 @@
         <v>1147.281782714996</v>
       </c>
       <c r="U3" t="n">
-        <v>769.5040049372183</v>
+        <v>1147.084020807432</v>
       </c>
       <c r="V3" t="n">
-        <v>754.8467653498242</v>
+        <v>1132.426781220038</v>
       </c>
       <c r="W3" t="n">
-        <v>722.146620996462</v>
+        <v>754.64900344226</v>
       </c>
       <c r="X3" t="n">
-        <v>570.5406665586214</v>
+        <v>734.5856302651008</v>
       </c>
       <c r="Y3" t="n">
-        <v>570.5406665586214</v>
+        <v>734.5856302651008</v>
       </c>
     </row>
     <row r="4">
@@ -4455,31 +4455,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>987.0856742947773</v>
+        <v>616.4631353463192</v>
       </c>
       <c r="C4" t="n">
-        <v>987.0856742947773</v>
+        <v>616.4631353463192</v>
       </c>
       <c r="D4" t="n">
-        <v>987.0856742947773</v>
+        <v>729.7822794713193</v>
       </c>
       <c r="E4" t="n">
-        <v>987.0856742947773</v>
+        <v>847.6111836827323</v>
       </c>
       <c r="F4" t="n">
-        <v>987.0856742947773</v>
+        <v>971.9721562746678</v>
       </c>
       <c r="G4" t="n">
-        <v>987.0856742947773</v>
+        <v>971.9721562746678</v>
       </c>
       <c r="H4" t="n">
-        <v>987.0856742947773</v>
+        <v>1143.123604712754</v>
       </c>
       <c r="I4" t="n">
-        <v>1213.74833618168</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="J4" t="n">
-        <v>1381.441257449721</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="K4" t="n">
         <v>1381.441257449721</v>
@@ -4506,25 +4506,25 @@
         <v>29.92</v>
       </c>
       <c r="S4" t="n">
-        <v>29.92</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="T4" t="n">
-        <v>218.7813496506081</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="U4" t="n">
-        <v>465.3425721249604</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="V4" t="n">
-        <v>664.1639650109064</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="W4" t="n">
-        <v>836.0548832705838</v>
+        <v>242.2657059768013</v>
       </c>
       <c r="X4" t="n">
-        <v>987.0856742947773</v>
+        <v>393.2964970009949</v>
       </c>
       <c r="Y4" t="n">
-        <v>987.0856742947773</v>
+        <v>504.7057976800271</v>
       </c>
     </row>
     <row r="5">
@@ -4534,76 +4534,76 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>106.8684999460195</v>
+        <v>108.8416377852028</v>
       </c>
       <c r="C5" t="n">
-        <v>56.89417848844992</v>
+        <v>58.86731632763319</v>
       </c>
       <c r="D5" t="n">
-        <v>46.450586832036</v>
+        <v>48.42372467121926</v>
       </c>
       <c r="E5" t="n">
-        <v>42.04322359277474</v>
+        <v>44.016361431958</v>
       </c>
       <c r="F5" t="n">
-        <v>37.10420469579307</v>
+        <v>39.07734253497633</v>
       </c>
       <c r="G5" t="n">
-        <v>33.72713203391686</v>
+        <v>35.70026987310013</v>
       </c>
       <c r="H5" t="n">
-        <v>29.92</v>
+        <v>31.89313783918327</v>
       </c>
       <c r="I5" t="n">
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>400.18</v>
+        <v>209.7212321538424</v>
       </c>
       <c r="K5" t="n">
-        <v>632.1258206463046</v>
+        <v>261.8658206463047</v>
       </c>
       <c r="L5" t="n">
+        <v>326.5557936111288</v>
+      </c>
+      <c r="M5" t="n">
         <v>696.8157936111288</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>1067.075793611129</v>
       </c>
-      <c r="N5" t="n">
-        <v>1437.335793611129</v>
-      </c>
       <c r="O5" t="n">
-        <v>1437.335793611129</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="P5" t="n">
-        <v>1496</v>
+        <v>1125.74</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
       </c>
       <c r="R5" t="n">
-        <v>1494.026862160817</v>
+        <v>1496</v>
       </c>
       <c r="S5" t="n">
-        <v>1407.751569573322</v>
+        <v>1409.724707412506</v>
       </c>
       <c r="T5" t="n">
-        <v>1221.021277892777</v>
+        <v>1222.994415731961</v>
       </c>
       <c r="U5" t="n">
-        <v>969.3160547407873</v>
+        <v>971.2891925799706</v>
       </c>
       <c r="V5" t="n">
-        <v>737.1433030571268</v>
+        <v>739.1164408963101</v>
       </c>
       <c r="W5" t="n">
-        <v>496.3620141874828</v>
+        <v>498.3351520266661</v>
       </c>
       <c r="X5" t="n">
-        <v>302.1379399847881</v>
+        <v>304.1110778239714</v>
       </c>
       <c r="Y5" t="n">
-        <v>189.6960887900342</v>
+        <v>191.6692266292175</v>
       </c>
     </row>
     <row r="6">
@@ -4613,13 +4613,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>358.7260491971879</v>
+        <v>704.8594807344734</v>
       </c>
       <c r="C6" t="n">
-        <v>358.7260491971879</v>
+        <v>704.8594807344734</v>
       </c>
       <c r="D6" t="n">
-        <v>358.7260491971879</v>
+        <v>704.8594807344734</v>
       </c>
       <c r="E6" t="n">
         <v>358.7260491971879</v>
@@ -4658,31 +4658,31 @@
         <v>1495.800085368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1495.800085368536</v>
+        <v>1349.538506374912</v>
       </c>
       <c r="R6" t="n">
-        <v>1360.932975467714</v>
+        <v>1214.671396474091</v>
       </c>
       <c r="S6" t="n">
-        <v>1297.853320462485</v>
+        <v>1151.591741468861</v>
       </c>
       <c r="T6" t="n">
-        <v>1293.343447077155</v>
+        <v>1147.081868083532</v>
       </c>
       <c r="U6" t="n">
-        <v>1149.002217517297</v>
+        <v>1146.884106175968</v>
       </c>
       <c r="V6" t="n">
-        <v>1134.344977929903</v>
+        <v>769.1063283981898</v>
       </c>
       <c r="W6" t="n">
-        <v>756.5672001521249</v>
+        <v>724.9228539116326</v>
       </c>
       <c r="X6" t="n">
-        <v>736.5038269749657</v>
+        <v>704.8594807344734</v>
       </c>
       <c r="Y6" t="n">
-        <v>358.7260491971879</v>
+        <v>704.8594807344734</v>
       </c>
     </row>
     <row r="7">
@@ -4692,34 +4692,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>579.2141740099605</v>
+        <v>592.978779020126</v>
       </c>
       <c r="C7" t="n">
-        <v>705.2161798283963</v>
+        <v>718.9807848385618</v>
       </c>
       <c r="D7" t="n">
-        <v>818.5353239533964</v>
+        <v>832.2999289635619</v>
       </c>
       <c r="E7" t="n">
-        <v>936.3642281648094</v>
+        <v>832.2999289635619</v>
       </c>
       <c r="F7" t="n">
-        <v>1060.725200756745</v>
+        <v>832.2999289635619</v>
       </c>
       <c r="G7" t="n">
-        <v>1214.315646971499</v>
+        <v>985.890375178316</v>
       </c>
       <c r="H7" t="n">
-        <v>1385.467095409585</v>
+        <v>1023.050610806278</v>
       </c>
       <c r="I7" t="n">
-        <v>1385.467095409585</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="J7" t="n">
-        <v>1385.467095409585</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="K7" t="n">
-        <v>1385.467095409585</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="L7" t="n">
         <v>1385.467095409585</v>
@@ -4746,22 +4746,22 @@
         <v>29.92</v>
       </c>
       <c r="T7" t="n">
-        <v>29.92</v>
+        <v>218.7813496506081</v>
       </c>
       <c r="U7" t="n">
-        <v>29.92</v>
+        <v>218.7813496506081</v>
       </c>
       <c r="V7" t="n">
-        <v>33.1258263807652</v>
+        <v>218.7813496506081</v>
       </c>
       <c r="W7" t="n">
-        <v>205.0167446404426</v>
+        <v>218.7813496506081</v>
       </c>
       <c r="X7" t="n">
-        <v>356.0475356646361</v>
+        <v>369.8121406748016</v>
       </c>
       <c r="Y7" t="n">
-        <v>467.4568363436684</v>
+        <v>481.2214413538339</v>
       </c>
     </row>
     <row r="8">
@@ -4771,22 +4771,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>106.8684999460195</v>
+        <v>108.8416377852028</v>
       </c>
       <c r="C8" t="n">
-        <v>56.89417848844992</v>
+        <v>58.86731632763319</v>
       </c>
       <c r="D8" t="n">
-        <v>46.450586832036</v>
+        <v>48.42372467121926</v>
       </c>
       <c r="E8" t="n">
-        <v>42.04322359277474</v>
+        <v>44.016361431958</v>
       </c>
       <c r="F8" t="n">
-        <v>37.10420469579307</v>
+        <v>39.07734253497633</v>
       </c>
       <c r="G8" t="n">
-        <v>33.72713203391686</v>
+        <v>35.70026987310013</v>
       </c>
       <c r="H8" t="n">
         <v>29.92</v>
@@ -4795,52 +4795,52 @@
         <v>29.92</v>
       </c>
       <c r="J8" t="n">
-        <v>400.18</v>
+        <v>30.01969029977264</v>
       </c>
       <c r="K8" t="n">
-        <v>452.3245884924623</v>
+        <v>400.2796902997726</v>
       </c>
       <c r="L8" t="n">
-        <v>696.8157936111288</v>
+        <v>770.5396902997726</v>
       </c>
       <c r="M8" t="n">
-        <v>696.8157936111288</v>
+        <v>1140.799690299772</v>
       </c>
       <c r="N8" t="n">
-        <v>1067.075793611129</v>
+        <v>1140.799690299772</v>
       </c>
       <c r="O8" t="n">
-        <v>1067.075793611129</v>
+        <v>1437.335793611129</v>
       </c>
       <c r="P8" t="n">
-        <v>1125.74</v>
+        <v>1496</v>
       </c>
       <c r="Q8" t="n">
         <v>1496</v>
       </c>
       <c r="R8" t="n">
-        <v>1494.026862160817</v>
+        <v>1496</v>
       </c>
       <c r="S8" t="n">
-        <v>1407.751569573322</v>
+        <v>1409.724707412506</v>
       </c>
       <c r="T8" t="n">
-        <v>1221.021277892777</v>
+        <v>1222.994415731961</v>
       </c>
       <c r="U8" t="n">
-        <v>969.3160547407873</v>
+        <v>971.2891925799706</v>
       </c>
       <c r="V8" t="n">
-        <v>737.1433030571268</v>
+        <v>739.1164408963101</v>
       </c>
       <c r="W8" t="n">
-        <v>496.3620141874828</v>
+        <v>498.3351520266661</v>
       </c>
       <c r="X8" t="n">
-        <v>302.1379399847881</v>
+        <v>304.1110778239714</v>
       </c>
       <c r="Y8" t="n">
-        <v>189.6960887900342</v>
+        <v>191.6692266292175</v>
       </c>
     </row>
     <row r="9">
@@ -4850,22 +4850,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>710.1782581847664</v>
+        <v>1038.221508957845</v>
       </c>
       <c r="C9" t="n">
-        <v>710.1782581847664</v>
+        <v>1038.221508957845</v>
       </c>
       <c r="D9" t="n">
-        <v>358.7260491971879</v>
+        <v>1038.221508957845</v>
       </c>
       <c r="E9" t="n">
-        <v>358.7260491971879</v>
+        <v>692.0880774205598</v>
       </c>
       <c r="F9" t="n">
-        <v>358.7260491971879</v>
+        <v>692.0880774205598</v>
       </c>
       <c r="G9" t="n">
-        <v>29.92</v>
+        <v>363.2820282233719</v>
       </c>
       <c r="H9" t="n">
         <v>29.92</v>
@@ -4895,31 +4895,31 @@
         <v>1495.800085368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1349.538506374912</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="R9" t="n">
-        <v>1214.671396474091</v>
+        <v>1360.932975467714</v>
       </c>
       <c r="S9" t="n">
-        <v>1151.591741468861</v>
+        <v>1297.853320462485</v>
       </c>
       <c r="T9" t="n">
-        <v>1147.081868083532</v>
+        <v>1293.343447077155</v>
       </c>
       <c r="U9" t="n">
-        <v>777.5990153026818</v>
+        <v>1105.642266075761</v>
       </c>
       <c r="V9" t="n">
-        <v>762.9417757152877</v>
+        <v>1090.985026488367</v>
       </c>
       <c r="W9" t="n">
-        <v>730.2416313619256</v>
+        <v>1058.284882135004</v>
       </c>
       <c r="X9" t="n">
-        <v>710.1782581847664</v>
+        <v>1038.221508957845</v>
       </c>
       <c r="Y9" t="n">
-        <v>710.1782581847664</v>
+        <v>1038.221508957845</v>
       </c>
     </row>
     <row r="10">
@@ -4929,28 +4929,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>141.6773376662921</v>
+        <v>755.092300101245</v>
       </c>
       <c r="C10" t="n">
-        <v>267.679343484728</v>
+        <v>755.092300101245</v>
       </c>
       <c r="D10" t="n">
-        <v>380.998487609728</v>
+        <v>755.092300101245</v>
       </c>
       <c r="E10" t="n">
-        <v>498.8273918211411</v>
+        <v>755.092300101245</v>
       </c>
       <c r="F10" t="n">
-        <v>623.1883644130766</v>
+        <v>879.4532726931805</v>
       </c>
       <c r="G10" t="n">
-        <v>776.7788106278307</v>
+        <v>879.4532726931805</v>
       </c>
       <c r="H10" t="n">
-        <v>947.9302590659167</v>
+        <v>879.4532726931805</v>
       </c>
       <c r="I10" t="n">
-        <v>1174.592920952819</v>
+        <v>879.4532726931805</v>
       </c>
       <c r="J10" t="n">
         <v>1249.71327269318</v>
@@ -4983,22 +4983,22 @@
         <v>29.92</v>
       </c>
       <c r="T10" t="n">
-        <v>29.92</v>
+        <v>218.7813496506081</v>
       </c>
       <c r="U10" t="n">
-        <v>29.92</v>
+        <v>218.7813496506081</v>
       </c>
       <c r="V10" t="n">
-        <v>29.92</v>
+        <v>320.7612901383418</v>
       </c>
       <c r="W10" t="n">
-        <v>29.92</v>
+        <v>492.6522083980192</v>
       </c>
       <c r="X10" t="n">
-        <v>29.92</v>
+        <v>643.6829994222127</v>
       </c>
       <c r="Y10" t="n">
-        <v>29.92</v>
+        <v>755.092300101245</v>
       </c>
     </row>
     <row r="11">
@@ -5008,76 +5008,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>596.4384060421568</v>
+        <v>597.3418560482351</v>
       </c>
       <c r="C11" t="n">
-        <v>466.6661047866074</v>
+        <v>467.5695547926856</v>
       </c>
       <c r="D11" t="n">
-        <v>376.4245333322136</v>
+        <v>377.3279833382919</v>
       </c>
       <c r="E11" t="n">
-        <v>292.2191902949726</v>
+        <v>293.1226403010508</v>
       </c>
       <c r="F11" t="n">
-        <v>207.4821916000111</v>
+        <v>208.3856416060893</v>
       </c>
       <c r="G11" t="n">
-        <v>125.2979517892592</v>
+        <v>126.1973410877592</v>
       </c>
       <c r="H11" t="n">
-        <v>51.84</v>
+        <v>52.69780257701373</v>
       </c>
       <c r="I11" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="J11" t="n">
-        <v>560.3618942939371</v>
+        <v>560.1041052989622</v>
       </c>
       <c r="K11" t="n">
-        <v>1201.881894293937</v>
+        <v>950.7721266502845</v>
       </c>
       <c r="L11" t="n">
-        <v>1843.401894293937</v>
+        <v>1593.282126650284</v>
       </c>
       <c r="M11" t="n">
-        <v>2230.549243836214</v>
+        <v>1593.282126650284</v>
       </c>
       <c r="N11" t="n">
-        <v>2230.549243836214</v>
+        <v>2235.792126650284</v>
       </c>
       <c r="O11" t="n">
-        <v>2393.691050093541</v>
+        <v>2398.263364616154</v>
       </c>
       <c r="P11" t="n">
-        <v>2592</v>
+        <v>2596</v>
       </c>
       <c r="Q11" t="n">
-        <v>2592</v>
+        <v>2596</v>
       </c>
       <c r="R11" t="n">
-        <v>2592</v>
+        <v>2596</v>
       </c>
       <c r="S11" t="n">
-        <v>2448.504870855986</v>
+        <v>2452.412337482045</v>
       </c>
       <c r="T11" t="n">
-        <v>2186.313881748914</v>
+        <v>2190.203572627549</v>
       </c>
       <c r="U11" t="n">
-        <v>1857.875859826824</v>
+        <v>1858.779309832902</v>
       </c>
       <c r="V11" t="n">
-        <v>1545.905128345183</v>
+        <v>1546.808578351262</v>
       </c>
       <c r="W11" t="n">
-        <v>1225.325859677559</v>
+        <v>1226.229309683638</v>
       </c>
       <c r="X11" t="n">
-        <v>951.3038056768851</v>
+        <v>952.2072556829633</v>
       </c>
       <c r="Y11" t="n">
-        <v>759.0639746841513</v>
+        <v>759.9674246902296</v>
       </c>
     </row>
     <row r="12">
@@ -5087,76 +5087,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>353.3127448715645</v>
+        <v>1010.32856177545</v>
       </c>
       <c r="C12" t="n">
-        <v>312.8077828053833</v>
+        <v>969.8235997092687</v>
       </c>
       <c r="D12" t="n">
-        <v>285.5979980602291</v>
+        <v>942.6138149641146</v>
       </c>
       <c r="E12" t="n">
-        <v>263.7069907653679</v>
+        <v>920.7228076692534</v>
       </c>
       <c r="F12" t="n">
-        <v>244.8825035553913</v>
+        <v>577.6558962168524</v>
       </c>
       <c r="G12" t="n">
-        <v>55.83964972137069</v>
+        <v>573.6202300957079</v>
       </c>
       <c r="H12" t="n">
-        <v>51.84</v>
+        <v>245.3571727128164</v>
       </c>
       <c r="I12" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="J12" t="n">
-        <v>245.6076497036009</v>
+        <v>245.4864648922801</v>
       </c>
       <c r="K12" t="n">
-        <v>554.1188055149654</v>
+        <v>553.6537638168522</v>
       </c>
       <c r="L12" t="n">
-        <v>985.9074996573354</v>
+        <v>984.9800999403543</v>
       </c>
       <c r="M12" t="n">
-        <v>1259.211891400195</v>
+        <v>1257.744941683213</v>
       </c>
       <c r="N12" t="n">
-        <v>1584.67128421531</v>
+        <v>1582.65050421531</v>
       </c>
       <c r="O12" t="n">
-        <v>1999.520074672614</v>
+        <v>1996.99264816318</v>
       </c>
       <c r="P12" t="n">
-        <v>2253.149505368536</v>
+        <v>2250.215450368536</v>
       </c>
       <c r="Q12" t="n">
-        <v>2253.149505368536</v>
+        <v>2250.215450368536</v>
       </c>
       <c r="R12" t="n">
-        <v>2071.399071663636</v>
+        <v>2068.330120532513</v>
       </c>
       <c r="S12" t="n">
-        <v>1938.368397028141</v>
+        <v>1935.259089502888</v>
       </c>
       <c r="T12" t="n">
-        <v>1856.197345826917</v>
+        <v>1540.486032942352</v>
       </c>
       <c r="U12" t="n">
-        <v>1776.236481193986</v>
+        <v>1460.525025370599</v>
       </c>
       <c r="V12" t="n">
-        <v>1357.538837566188</v>
+        <v>1366.069805985225</v>
       </c>
       <c r="W12" t="n">
-        <v>1245.040713414846</v>
+        <v>1253.571681833883</v>
       </c>
       <c r="X12" t="n">
-        <v>820.9369361972826</v>
+        <v>1153.710328858744</v>
       </c>
       <c r="Y12" t="n">
-        <v>417.5112869385611</v>
+        <v>1074.527103842446</v>
       </c>
     </row>
     <row r="13">
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>686.5872726401018</v>
+        <v>683.5228537532904</v>
       </c>
       <c r="C13" t="n">
-        <v>734.3792784585376</v>
+        <v>731.3148595717262</v>
       </c>
       <c r="D13" t="n">
-        <v>769.4884225835376</v>
+        <v>766.4240036967262</v>
       </c>
       <c r="E13" t="n">
-        <v>809.1073267949506</v>
+        <v>806.0429079081392</v>
       </c>
       <c r="F13" t="n">
-        <v>855.2582993868861</v>
+        <v>852.1938805000747</v>
       </c>
       <c r="G13" t="n">
-        <v>931.0743456016402</v>
+        <v>928.0081414689272</v>
       </c>
       <c r="H13" t="n">
-        <v>1027.888674039726</v>
+        <v>1024.806597447997</v>
       </c>
       <c r="I13" t="n">
-        <v>1189.441015926629</v>
+        <v>1186.305252121785</v>
       </c>
       <c r="J13" t="n">
-        <v>1510.983618808348</v>
+        <v>1512.850035069318</v>
       </c>
       <c r="K13" t="n">
-        <v>1615.110403564888</v>
+        <v>1616.769406711104</v>
       </c>
       <c r="L13" t="n">
-        <v>1605.496770221213</v>
+        <v>1606.884966942524</v>
       </c>
       <c r="M13" t="n">
-        <v>1502.926687499644</v>
+        <v>1504.029356815756</v>
       </c>
       <c r="N13" t="n">
-        <v>1346.936646241608</v>
+        <v>1347.760577356031</v>
       </c>
       <c r="O13" t="n">
-        <v>1113.602925280855</v>
+        <v>1114.169396550933</v>
       </c>
       <c r="P13" t="n">
-        <v>819.8981109568782</v>
+        <v>820.2442808525564</v>
       </c>
       <c r="Q13" t="n">
-        <v>463.8958216380923</v>
+        <v>464.0894662812452</v>
       </c>
       <c r="R13" t="n">
-        <v>82.61634147829412</v>
+        <v>82.72808514446402</v>
       </c>
       <c r="S13" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="T13" t="n">
-        <v>164.3525496506081</v>
+        <v>161.288228140846</v>
       </c>
       <c r="U13" t="n">
-        <v>332.7275321249604</v>
+        <v>329.663113238149</v>
       </c>
       <c r="V13" t="n">
-        <v>453.3389250109063</v>
+        <v>450.274506124095</v>
       </c>
       <c r="W13" t="n">
-        <v>547.0198432705838</v>
+        <v>543.9554243837724</v>
       </c>
       <c r="X13" t="n">
-        <v>619.8406342947774</v>
+        <v>616.776215407966</v>
       </c>
       <c r="Y13" t="n">
-        <v>653.0399349738096</v>
+        <v>649.9755160869983</v>
       </c>
     </row>
     <row r="14">
@@ -5245,76 +5245,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>593.4524900262056</v>
+        <v>597.3418560482351</v>
       </c>
       <c r="C14" t="n">
-        <v>463.6801887706562</v>
+        <v>467.5695547926856</v>
       </c>
       <c r="D14" t="n">
-        <v>373.4386173162624</v>
+        <v>377.3279833382919</v>
       </c>
       <c r="E14" t="n">
-        <v>289.2332742790214</v>
+        <v>293.1226403010508</v>
       </c>
       <c r="F14" t="n">
-        <v>204.4962755840599</v>
+        <v>208.3856416060893</v>
       </c>
       <c r="G14" t="n">
-        <v>125.2979517892592</v>
+        <v>126.1973410877592</v>
       </c>
       <c r="H14" t="n">
-        <v>51.84</v>
+        <v>52.69780257701376</v>
       </c>
       <c r="I14" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="J14" t="n">
-        <v>560.3618942939371</v>
+        <v>560.1041052989622</v>
       </c>
       <c r="K14" t="n">
-        <v>1201.881894293937</v>
+        <v>1005.9776389343</v>
       </c>
       <c r="L14" t="n">
-        <v>1843.401894293937</v>
+        <v>1648.4876389343</v>
       </c>
       <c r="M14" t="n">
-        <v>2230.549243836214</v>
+        <v>1648.4876389343</v>
       </c>
       <c r="N14" t="n">
-        <v>2230.549243836214</v>
+        <v>1648.4876389343</v>
       </c>
       <c r="O14" t="n">
-        <v>2393.691050093541</v>
+        <v>1810.95887690017</v>
       </c>
       <c r="P14" t="n">
-        <v>2592</v>
+        <v>2008.695512284016</v>
       </c>
       <c r="Q14" t="n">
-        <v>2592</v>
+        <v>2596</v>
       </c>
       <c r="R14" t="n">
-        <v>2592</v>
+        <v>2596</v>
       </c>
       <c r="S14" t="n">
-        <v>2448.504870855986</v>
+        <v>2452.412337482045</v>
       </c>
       <c r="T14" t="n">
-        <v>2186.313881748914</v>
+        <v>2190.203572627549</v>
       </c>
       <c r="U14" t="n">
-        <v>1854.889943810872</v>
+        <v>1858.779309832902</v>
       </c>
       <c r="V14" t="n">
-        <v>1542.919212329232</v>
+        <v>1546.808578351262</v>
       </c>
       <c r="W14" t="n">
-        <v>1222.339943661608</v>
+        <v>1226.229309683638</v>
       </c>
       <c r="X14" t="n">
-        <v>948.3178896609338</v>
+        <v>952.2072556829633</v>
       </c>
       <c r="Y14" t="n">
-        <v>756.0780586682001</v>
+        <v>759.9674246902296</v>
       </c>
     </row>
     <row r="15">
@@ -5324,76 +5324,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1326.040017598837</v>
+        <v>816.8913890626335</v>
       </c>
       <c r="C15" t="n">
-        <v>1285.535055532656</v>
+        <v>452.1440027540281</v>
       </c>
       <c r="D15" t="n">
-        <v>1258.325270787502</v>
+        <v>424.9342180088739</v>
       </c>
       <c r="E15" t="n">
-        <v>912.1918392502164</v>
+        <v>403.0432107140127</v>
       </c>
       <c r="F15" t="n">
-        <v>569.1249277978154</v>
+        <v>384.2187235040361</v>
       </c>
       <c r="G15" t="n">
-        <v>249.2020177839106</v>
+        <v>380.1830573828916</v>
       </c>
       <c r="H15" t="n">
-        <v>245.20236806254</v>
+        <v>51.92</v>
       </c>
       <c r="I15" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="J15" t="n">
-        <v>245.6076497036009</v>
+        <v>245.4864648922801</v>
       </c>
       <c r="K15" t="n">
-        <v>554.1188055149654</v>
+        <v>553.6537638168522</v>
       </c>
       <c r="L15" t="n">
-        <v>985.9074996573354</v>
+        <v>984.9800999403543</v>
       </c>
       <c r="M15" t="n">
-        <v>1259.211891400195</v>
+        <v>1257.744941683213</v>
       </c>
       <c r="N15" t="n">
-        <v>1584.67128421531</v>
+        <v>1582.65050421531</v>
       </c>
       <c r="O15" t="n">
-        <v>1999.520074672614</v>
+        <v>1996.99264816318</v>
       </c>
       <c r="P15" t="n">
-        <v>2253.149505368536</v>
+        <v>2250.215450368536</v>
       </c>
       <c r="Q15" t="n">
-        <v>2253.149505368536</v>
+        <v>2250.215450368536</v>
       </c>
       <c r="R15" t="n">
-        <v>2071.399071663636</v>
+        <v>2068.330120532513</v>
       </c>
       <c r="S15" t="n">
-        <v>1938.368397028141</v>
+        <v>1935.259089502888</v>
       </c>
       <c r="T15" t="n">
-        <v>1856.197345826917</v>
+        <v>1853.079280916492</v>
       </c>
       <c r="U15" t="n">
-        <v>1776.236481193986</v>
+        <v>1448.875849102314</v>
       </c>
       <c r="V15" t="n">
-        <v>1681.781261808612</v>
+        <v>1172.632633272408</v>
       </c>
       <c r="W15" t="n">
-        <v>1569.28313765727</v>
+        <v>1060.134509121066</v>
       </c>
       <c r="X15" t="n">
-        <v>1469.421784682131</v>
+        <v>960.2731561459274</v>
       </c>
       <c r="Y15" t="n">
-        <v>1390.238559665834</v>
+        <v>881.08993112963</v>
       </c>
     </row>
     <row r="16">
@@ -5403,76 +5403,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>681.4588756890412</v>
+        <v>686.6595473942001</v>
       </c>
       <c r="C16" t="n">
-        <v>729.2508815074769</v>
+        <v>734.4515532126359</v>
       </c>
       <c r="D16" t="n">
-        <v>764.360025632477</v>
+        <v>769.5606973376359</v>
       </c>
       <c r="E16" t="n">
-        <v>803.97892984389</v>
+        <v>809.1796015490489</v>
       </c>
       <c r="F16" t="n">
-        <v>850.1299024358254</v>
+        <v>852.1938805000747</v>
       </c>
       <c r="G16" t="n">
-        <v>925.9459486505796</v>
+        <v>928.0081414689272</v>
       </c>
       <c r="H16" t="n">
-        <v>1022.760277088666</v>
+        <v>1024.806597447997</v>
       </c>
       <c r="I16" t="n">
-        <v>1184.312618975568</v>
+        <v>1186.305252121785</v>
       </c>
       <c r="J16" t="n">
-        <v>1510.983618808348</v>
+        <v>1512.850035069318</v>
       </c>
       <c r="K16" t="n">
-        <v>1615.110403564888</v>
+        <v>1616.769406711104</v>
       </c>
       <c r="L16" t="n">
-        <v>1605.496770221213</v>
+        <v>1606.884966942524</v>
       </c>
       <c r="M16" t="n">
-        <v>1502.926687499644</v>
+        <v>1504.029356815756</v>
       </c>
       <c r="N16" t="n">
-        <v>1346.936646241608</v>
+        <v>1347.760577356031</v>
       </c>
       <c r="O16" t="n">
-        <v>1113.602925280855</v>
+        <v>1114.169396550933</v>
       </c>
       <c r="P16" t="n">
-        <v>819.8981109568782</v>
+        <v>820.2442808525564</v>
       </c>
       <c r="Q16" t="n">
-        <v>463.8958216380924</v>
+        <v>464.0894662812452</v>
       </c>
       <c r="R16" t="n">
-        <v>82.61634147829413</v>
+        <v>82.72808514446405</v>
       </c>
       <c r="S16" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="T16" t="n">
-        <v>164.3525496506081</v>
+        <v>164.4249217817557</v>
       </c>
       <c r="U16" t="n">
-        <v>327.5991351738998</v>
+        <v>332.7998068790587</v>
       </c>
       <c r="V16" t="n">
-        <v>448.2105280598458</v>
+        <v>453.4111997650047</v>
       </c>
       <c r="W16" t="n">
-        <v>541.8914463195232</v>
+        <v>547.0921180246821</v>
       </c>
       <c r="X16" t="n">
-        <v>614.7122373437168</v>
+        <v>619.9129090488757</v>
       </c>
       <c r="Y16" t="n">
-        <v>647.911538022749</v>
+        <v>653.112209727908</v>
       </c>
     </row>
     <row r="17">
@@ -5482,76 +5482,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>596.4384060421568</v>
+        <v>597.4524900262056</v>
       </c>
       <c r="C17" t="n">
-        <v>466.6661047866073</v>
+        <v>467.6801887706562</v>
       </c>
       <c r="D17" t="n">
-        <v>376.4245333322136</v>
+        <v>377.4386173162624</v>
       </c>
       <c r="E17" t="n">
-        <v>292.2191902949725</v>
+        <v>293.2332742790214</v>
       </c>
       <c r="F17" t="n">
-        <v>207.482191600011</v>
+        <v>208.4962755840599</v>
       </c>
       <c r="G17" t="n">
-        <v>125.2979517892592</v>
+        <v>126.3120357733081</v>
       </c>
       <c r="H17" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="I17" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="J17" t="n">
-        <v>560.3618942939371</v>
+        <v>134.440205073642</v>
       </c>
       <c r="K17" t="n">
-        <v>1201.881894293937</v>
+        <v>776.950205073642</v>
       </c>
       <c r="L17" t="n">
-        <v>1843.401894293937</v>
+        <v>994.8863275862049</v>
       </c>
       <c r="M17" t="n">
-        <v>2230.549243836214</v>
+        <v>1147.838193742673</v>
       </c>
       <c r="N17" t="n">
-        <v>2230.549243836214</v>
+        <v>1790.348193742673</v>
       </c>
       <c r="O17" t="n">
-        <v>2393.691050093541</v>
+        <v>1953.49</v>
       </c>
       <c r="P17" t="n">
-        <v>2592</v>
+        <v>2596</v>
       </c>
       <c r="Q17" t="n">
-        <v>2592</v>
+        <v>2596</v>
       </c>
       <c r="R17" t="n">
-        <v>2592</v>
+        <v>2596</v>
       </c>
       <c r="S17" t="n">
-        <v>2448.504870855986</v>
+        <v>2452.504870855986</v>
       </c>
       <c r="T17" t="n">
-        <v>2186.313881748914</v>
+        <v>2190.313881748914</v>
       </c>
       <c r="U17" t="n">
-        <v>1854.889943810872</v>
+        <v>1858.889943810872</v>
       </c>
       <c r="V17" t="n">
-        <v>1542.919212329232</v>
+        <v>1546.919212329232</v>
       </c>
       <c r="W17" t="n">
-        <v>1225.325859677559</v>
+        <v>1226.339943661608</v>
       </c>
       <c r="X17" t="n">
-        <v>951.3038056768851</v>
+        <v>952.3178896609338</v>
       </c>
       <c r="Y17" t="n">
-        <v>759.0639746841513</v>
+        <v>760.0780586682001</v>
       </c>
     </row>
     <row r="18">
@@ -5561,76 +5561,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1247.449260026979</v>
+        <v>677.6351691139887</v>
       </c>
       <c r="C18" t="n">
-        <v>882.7018737183735</v>
+        <v>637.1302070478076</v>
       </c>
       <c r="D18" t="n">
-        <v>531.2496647307951</v>
+        <v>609.9204223026535</v>
       </c>
       <c r="E18" t="n">
-        <v>185.1162331935096</v>
+        <v>588.0294150077923</v>
       </c>
       <c r="F18" t="n">
-        <v>59.87314317241791</v>
+        <v>384.1955674148422</v>
       </c>
       <c r="G18" t="n">
-        <v>55.83964972137068</v>
+        <v>55.91964972137067</v>
       </c>
       <c r="H18" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="I18" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="J18" t="n">
-        <v>245.6076497036009</v>
+        <v>245.6876497036009</v>
       </c>
       <c r="K18" t="n">
-        <v>554.1188055149654</v>
+        <v>554.1988055149654</v>
       </c>
       <c r="L18" t="n">
-        <v>985.9074996573354</v>
+        <v>985.9874996573354</v>
       </c>
       <c r="M18" t="n">
-        <v>1259.211891400195</v>
+        <v>1259.291891400195</v>
       </c>
       <c r="N18" t="n">
-        <v>1584.67128421531</v>
+        <v>1584.75128421531</v>
       </c>
       <c r="O18" t="n">
-        <v>1999.520074672614</v>
+        <v>1999.600074672614</v>
       </c>
       <c r="P18" t="n">
-        <v>2253.149505368536</v>
+        <v>2253.229505368536</v>
       </c>
       <c r="Q18" t="n">
-        <v>2174.558747796677</v>
+        <v>2253.229505368536</v>
       </c>
       <c r="R18" t="n">
-        <v>1992.808314091777</v>
+        <v>2071.479071663636</v>
       </c>
       <c r="S18" t="n">
-        <v>1859.777639456283</v>
+        <v>1938.448397028141</v>
       </c>
       <c r="T18" t="n">
-        <v>1777.606588255059</v>
+        <v>1856.277345826917</v>
       </c>
       <c r="U18" t="n">
-        <v>1697.645723622128</v>
+        <v>1776.316481193986</v>
       </c>
       <c r="V18" t="n">
-        <v>1603.190504236754</v>
+        <v>1357.618837566188</v>
       </c>
       <c r="W18" t="n">
-        <v>1490.692380085412</v>
+        <v>1245.120713414846</v>
       </c>
       <c r="X18" t="n">
-        <v>1390.831027110273</v>
+        <v>821.0169361972826</v>
       </c>
       <c r="Y18" t="n">
-        <v>1311.647802093976</v>
+        <v>741.8337111809852</v>
       </c>
     </row>
     <row r="19">
@@ -5640,76 +5640,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>686.5872726401018</v>
+        <v>686.6672726401017</v>
       </c>
       <c r="C19" t="n">
-        <v>734.3792784585376</v>
+        <v>734.4592784585375</v>
       </c>
       <c r="D19" t="n">
-        <v>769.4884225835376</v>
+        <v>769.5684225835375</v>
       </c>
       <c r="E19" t="n">
-        <v>809.1073267949506</v>
+        <v>804.0589298438899</v>
       </c>
       <c r="F19" t="n">
-        <v>855.2582993868861</v>
+        <v>850.2099024358254</v>
       </c>
       <c r="G19" t="n">
-        <v>931.0743456016402</v>
+        <v>926.0259486505795</v>
       </c>
       <c r="H19" t="n">
-        <v>1027.888674039726</v>
+        <v>1022.840277088666</v>
       </c>
       <c r="I19" t="n">
-        <v>1189.441015926629</v>
+        <v>1184.392618975568</v>
       </c>
       <c r="J19" t="n">
-        <v>1510.983618808348</v>
+        <v>1511.063618808347</v>
       </c>
       <c r="K19" t="n">
-        <v>1615.110403564888</v>
+        <v>1615.190403564888</v>
       </c>
       <c r="L19" t="n">
-        <v>1605.496770221213</v>
+        <v>1605.576770221213</v>
       </c>
       <c r="M19" t="n">
-        <v>1502.926687499644</v>
+        <v>1503.006687499644</v>
       </c>
       <c r="N19" t="n">
-        <v>1346.936646241608</v>
+        <v>1347.016646241608</v>
       </c>
       <c r="O19" t="n">
-        <v>1113.602925280855</v>
+        <v>1113.682925280855</v>
       </c>
       <c r="P19" t="n">
-        <v>819.8981109568782</v>
+        <v>819.9781109568783</v>
       </c>
       <c r="Q19" t="n">
-        <v>463.8958216380924</v>
+        <v>463.9758216380924</v>
       </c>
       <c r="R19" t="n">
-        <v>82.61634147829413</v>
+        <v>82.69634147829413</v>
       </c>
       <c r="S19" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="T19" t="n">
-        <v>164.3525496506081</v>
+        <v>164.4325496506081</v>
       </c>
       <c r="U19" t="n">
-        <v>332.7275321249604</v>
+        <v>332.8075321249603</v>
       </c>
       <c r="V19" t="n">
-        <v>453.3389250109063</v>
+        <v>453.4189250109063</v>
       </c>
       <c r="W19" t="n">
-        <v>547.0198432705838</v>
+        <v>547.0998432705837</v>
       </c>
       <c r="X19" t="n">
-        <v>619.8406342947774</v>
+        <v>619.9206342947773</v>
       </c>
       <c r="Y19" t="n">
-        <v>653.0399349738096</v>
+        <v>653.1199349738096</v>
       </c>
     </row>
     <row r="20">
@@ -5719,76 +5719,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>593.4524900262056</v>
+        <v>596.5184060421567</v>
       </c>
       <c r="C20" t="n">
-        <v>463.6801887706562</v>
+        <v>466.7461047866073</v>
       </c>
       <c r="D20" t="n">
-        <v>373.4386173162624</v>
+        <v>376.5045333322136</v>
       </c>
       <c r="E20" t="n">
-        <v>289.2332742790214</v>
+        <v>292.2991902949725</v>
       </c>
       <c r="F20" t="n">
-        <v>204.4962755840599</v>
+        <v>207.562191600011</v>
       </c>
       <c r="G20" t="n">
-        <v>125.2979517892592</v>
+        <v>125.3779517892592</v>
       </c>
       <c r="H20" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="I20" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="J20" t="n">
-        <v>134.360205073642</v>
+        <v>134.440205073642</v>
       </c>
       <c r="K20" t="n">
-        <v>775.8802050736419</v>
+        <v>776.950205073642</v>
       </c>
       <c r="L20" t="n">
-        <v>993.8163275862049</v>
+        <v>1419.460205073642</v>
       </c>
       <c r="M20" t="n">
-        <v>1635.336327586205</v>
+        <v>1419.460205073642</v>
       </c>
       <c r="N20" t="n">
-        <v>2230.549243836214</v>
+        <v>1646.814971748371</v>
       </c>
       <c r="O20" t="n">
-        <v>2393.691050093541</v>
+        <v>1809.956778005698</v>
       </c>
       <c r="P20" t="n">
-        <v>2592</v>
+        <v>2008.265727912157</v>
       </c>
       <c r="Q20" t="n">
-        <v>2592</v>
+        <v>2596</v>
       </c>
       <c r="R20" t="n">
-        <v>2592</v>
+        <v>2595.065916015951</v>
       </c>
       <c r="S20" t="n">
-        <v>2448.504870855986</v>
+        <v>2451.570786871937</v>
       </c>
       <c r="T20" t="n">
-        <v>2186.313881748914</v>
+        <v>2189.379797764865</v>
       </c>
       <c r="U20" t="n">
-        <v>1854.889943810872</v>
+        <v>1857.955859826824</v>
       </c>
       <c r="V20" t="n">
-        <v>1542.919212329232</v>
+        <v>1545.985128345183</v>
       </c>
       <c r="W20" t="n">
-        <v>1222.339943661608</v>
+        <v>1225.405859677559</v>
       </c>
       <c r="X20" t="n">
-        <v>948.3178896609338</v>
+        <v>951.383805676885</v>
       </c>
       <c r="Y20" t="n">
-        <v>756.0780586682001</v>
+        <v>759.1439746841512</v>
       </c>
     </row>
     <row r="21">
@@ -5798,76 +5798,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1141.030657215864</v>
+        <v>1001.877593356413</v>
       </c>
       <c r="C21" t="n">
-        <v>776.2832709072585</v>
+        <v>961.372631290232</v>
       </c>
       <c r="D21" t="n">
-        <v>424.8310619196801</v>
+        <v>749.1534861621043</v>
       </c>
       <c r="E21" t="n">
-        <v>402.9400546248188</v>
+        <v>727.2624788672431</v>
       </c>
       <c r="F21" t="n">
-        <v>59.87314317241791</v>
+        <v>384.1955674148422</v>
       </c>
       <c r="G21" t="n">
-        <v>55.83964972137068</v>
+        <v>55.91964972137067</v>
       </c>
       <c r="H21" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="I21" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="J21" t="n">
-        <v>245.6076497036009</v>
+        <v>245.6876497036009</v>
       </c>
       <c r="K21" t="n">
-        <v>554.1188055149654</v>
+        <v>554.1988055149654</v>
       </c>
       <c r="L21" t="n">
-        <v>985.9074996573354</v>
+        <v>985.9874996573354</v>
       </c>
       <c r="M21" t="n">
-        <v>1259.211891400195</v>
+        <v>1259.291891400195</v>
       </c>
       <c r="N21" t="n">
-        <v>1584.67128421531</v>
+        <v>1584.75128421531</v>
       </c>
       <c r="O21" t="n">
-        <v>1999.520074672614</v>
+        <v>1999.600074672614</v>
       </c>
       <c r="P21" t="n">
-        <v>2253.149505368536</v>
+        <v>2253.229505368536</v>
       </c>
       <c r="Q21" t="n">
-        <v>2253.149505368536</v>
+        <v>2253.229505368536</v>
       </c>
       <c r="R21" t="n">
-        <v>2071.399071663636</v>
+        <v>2071.479071663636</v>
       </c>
       <c r="S21" t="n">
-        <v>1938.368397028141</v>
+        <v>1938.448397028141</v>
       </c>
       <c r="T21" t="n">
-        <v>1856.197345826917</v>
+        <v>1532.034921584493</v>
       </c>
       <c r="U21" t="n">
-        <v>1776.236481193986</v>
+        <v>1452.074056951562</v>
       </c>
       <c r="V21" t="n">
-        <v>1681.781261808612</v>
+        <v>1357.618837566188</v>
       </c>
       <c r="W21" t="n">
-        <v>1569.28313765727</v>
+        <v>1245.120713414846</v>
       </c>
       <c r="X21" t="n">
-        <v>1469.421784682131</v>
+        <v>1145.259360439707</v>
       </c>
       <c r="Y21" t="n">
-        <v>1390.238559665834</v>
+        <v>1066.07613542341</v>
       </c>
     </row>
     <row r="22">
@@ -5877,76 +5877,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>686.5872726401018</v>
+        <v>681.5388756890411</v>
       </c>
       <c r="C22" t="n">
-        <v>734.3792784585376</v>
+        <v>729.3308815074769</v>
       </c>
       <c r="D22" t="n">
-        <v>769.4884225835376</v>
+        <v>764.4400256324769</v>
       </c>
       <c r="E22" t="n">
-        <v>809.1073267949506</v>
+        <v>804.0589298438899</v>
       </c>
       <c r="F22" t="n">
-        <v>855.2582993868861</v>
+        <v>850.2099024358254</v>
       </c>
       <c r="G22" t="n">
-        <v>931.0743456016402</v>
+        <v>926.0259486505795</v>
       </c>
       <c r="H22" t="n">
-        <v>1027.888674039726</v>
+        <v>1022.840277088666</v>
       </c>
       <c r="I22" t="n">
-        <v>1189.441015926629</v>
+        <v>1184.392618975568</v>
       </c>
       <c r="J22" t="n">
-        <v>1510.983618808348</v>
+        <v>1511.063618808347</v>
       </c>
       <c r="K22" t="n">
-        <v>1615.110403564888</v>
+        <v>1615.190403564888</v>
       </c>
       <c r="L22" t="n">
-        <v>1605.496770221213</v>
+        <v>1605.576770221213</v>
       </c>
       <c r="M22" t="n">
-        <v>1502.926687499644</v>
+        <v>1503.006687499644</v>
       </c>
       <c r="N22" t="n">
-        <v>1346.936646241608</v>
+        <v>1347.016646241608</v>
       </c>
       <c r="O22" t="n">
-        <v>1113.602925280855</v>
+        <v>1113.682925280855</v>
       </c>
       <c r="P22" t="n">
-        <v>819.8981109568782</v>
+        <v>819.9781109568783</v>
       </c>
       <c r="Q22" t="n">
-        <v>463.8958216380924</v>
+        <v>463.9758216380924</v>
       </c>
       <c r="R22" t="n">
-        <v>82.61634147829413</v>
+        <v>82.69634147829413</v>
       </c>
       <c r="S22" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="T22" t="n">
-        <v>164.3525496506081</v>
+        <v>164.4325496506081</v>
       </c>
       <c r="U22" t="n">
-        <v>332.7275321249604</v>
+        <v>332.8075321249603</v>
       </c>
       <c r="V22" t="n">
-        <v>453.3389250109063</v>
+        <v>453.4189250109063</v>
       </c>
       <c r="W22" t="n">
-        <v>547.0198432705838</v>
+        <v>547.0998432705837</v>
       </c>
       <c r="X22" t="n">
-        <v>619.8406342947774</v>
+        <v>619.9206342947773</v>
       </c>
       <c r="Y22" t="n">
-        <v>653.0399349738096</v>
+        <v>647.991538022749</v>
       </c>
     </row>
     <row r="23">
@@ -5956,76 +5956,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>593.4524900262352</v>
+        <v>596.5184060421567</v>
       </c>
       <c r="C23" t="n">
-        <v>463.6801887706857</v>
+        <v>466.7461047866073</v>
       </c>
       <c r="D23" t="n">
-        <v>373.438617316292</v>
+        <v>376.5045333322136</v>
       </c>
       <c r="E23" t="n">
-        <v>289.2332742790509</v>
+        <v>292.2991902949725</v>
       </c>
       <c r="F23" t="n">
-        <v>204.4962755840895</v>
+        <v>207.562191600011</v>
       </c>
       <c r="G23" t="n">
-        <v>122.3120357733376</v>
+        <v>125.3779517892592</v>
       </c>
       <c r="H23" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="I23" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="J23" t="n">
-        <v>560.3618942939371</v>
+        <v>560.4418942939371</v>
       </c>
       <c r="K23" t="n">
-        <v>947.5092438362141</v>
+        <v>736.1134691180577</v>
       </c>
       <c r="L23" t="n">
-        <v>1589.029243836214</v>
+        <v>954.0495916306205</v>
       </c>
       <c r="M23" t="n">
-        <v>1589.029243836214</v>
+        <v>1004.304971748371</v>
       </c>
       <c r="N23" t="n">
-        <v>2230.549243836214</v>
+        <v>1646.814971748371</v>
       </c>
       <c r="O23" t="n">
-        <v>2393.691050093541</v>
+        <v>1809.956778005698</v>
       </c>
       <c r="P23" t="n">
-        <v>2592</v>
+        <v>2008.265727912157</v>
       </c>
       <c r="Q23" t="n">
-        <v>2592</v>
+        <v>2596</v>
       </c>
       <c r="R23" t="n">
-        <v>2592.00000000003</v>
+        <v>2595.065916015951</v>
       </c>
       <c r="S23" t="n">
-        <v>2448.504870856015</v>
+        <v>2451.570786871937</v>
       </c>
       <c r="T23" t="n">
-        <v>2186.313881748943</v>
+        <v>2189.379797764865</v>
       </c>
       <c r="U23" t="n">
-        <v>1854.889943810902</v>
+        <v>1857.955859826824</v>
       </c>
       <c r="V23" t="n">
-        <v>1542.919212329262</v>
+        <v>1545.985128345183</v>
       </c>
       <c r="W23" t="n">
-        <v>1222.339943661638</v>
+        <v>1225.405859677559</v>
       </c>
       <c r="X23" t="n">
-        <v>948.3178896609634</v>
+        <v>951.383805676885</v>
       </c>
       <c r="Y23" t="n">
-        <v>756.0780586682297</v>
+        <v>759.1439746841512</v>
       </c>
     </row>
     <row r="24">
@@ -6035,76 +6035,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1326.040017598837</v>
+        <v>599.0444115421303</v>
       </c>
       <c r="C24" t="n">
-        <v>1100.525695149683</v>
+        <v>558.5394494759493</v>
       </c>
       <c r="D24" t="n">
-        <v>749.0734861621042</v>
+        <v>531.3296647307951</v>
       </c>
       <c r="E24" t="n">
-        <v>402.9400546248188</v>
+        <v>509.4386574359339</v>
       </c>
       <c r="F24" t="n">
-        <v>59.87314317241791</v>
+        <v>384.1955674148422</v>
       </c>
       <c r="G24" t="n">
-        <v>55.83964972137068</v>
+        <v>380.162073963795</v>
       </c>
       <c r="H24" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="I24" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="J24" t="n">
-        <v>245.6076497036009</v>
+        <v>245.6876497036009</v>
       </c>
       <c r="K24" t="n">
-        <v>554.1188055149654</v>
+        <v>554.1988055149654</v>
       </c>
       <c r="L24" t="n">
-        <v>985.9074996573354</v>
+        <v>985.9874996573354</v>
       </c>
       <c r="M24" t="n">
-        <v>1259.211891400195</v>
+        <v>1259.291891400195</v>
       </c>
       <c r="N24" t="n">
-        <v>1584.67128421531</v>
+        <v>1584.75128421531</v>
       </c>
       <c r="O24" t="n">
-        <v>1999.520074672614</v>
+        <v>1999.600074672614</v>
       </c>
       <c r="P24" t="n">
-        <v>2253.149505368536</v>
+        <v>2253.229505368536</v>
       </c>
       <c r="Q24" t="n">
-        <v>2253.149505368536</v>
+        <v>2174.638747796677</v>
       </c>
       <c r="R24" t="n">
-        <v>2071.399071663636</v>
+        <v>1992.888314091777</v>
       </c>
       <c r="S24" t="n">
-        <v>1938.368397028141</v>
+        <v>1535.615215213859</v>
       </c>
       <c r="T24" t="n">
-        <v>1856.197345826917</v>
+        <v>1453.444164012634</v>
       </c>
       <c r="U24" t="n">
-        <v>1776.236481193986</v>
+        <v>1373.483299379703</v>
       </c>
       <c r="V24" t="n">
-        <v>1681.781261808612</v>
+        <v>1279.028079994329</v>
       </c>
       <c r="W24" t="n">
-        <v>1569.28313765727</v>
+        <v>1166.529955842987</v>
       </c>
       <c r="X24" t="n">
-        <v>1469.421784682131</v>
+        <v>1066.668602867848</v>
       </c>
       <c r="Y24" t="n">
-        <v>1390.238559665834</v>
+        <v>663.2429536091269</v>
       </c>
     </row>
     <row r="25">
@@ -6114,76 +6114,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>686.5872726401018</v>
+        <v>686.6672726401017</v>
       </c>
       <c r="C25" t="n">
-        <v>734.3792784585376</v>
+        <v>734.4592784585375</v>
       </c>
       <c r="D25" t="n">
-        <v>769.4884225835376</v>
+        <v>769.5684225835375</v>
       </c>
       <c r="E25" t="n">
-        <v>809.1073267949506</v>
+        <v>809.1873267949505</v>
       </c>
       <c r="F25" t="n">
-        <v>855.2582993868861</v>
+        <v>850.2099024358254</v>
       </c>
       <c r="G25" t="n">
-        <v>931.0743456016402</v>
+        <v>926.0259486505795</v>
       </c>
       <c r="H25" t="n">
-        <v>1027.888674039726</v>
+        <v>1022.840277088666</v>
       </c>
       <c r="I25" t="n">
-        <v>1189.441015926629</v>
+        <v>1184.392618975568</v>
       </c>
       <c r="J25" t="n">
-        <v>1510.983618808348</v>
+        <v>1511.063618808347</v>
       </c>
       <c r="K25" t="n">
-        <v>1615.110403564888</v>
+        <v>1615.190403564888</v>
       </c>
       <c r="L25" t="n">
-        <v>1605.496770221213</v>
+        <v>1605.576770221213</v>
       </c>
       <c r="M25" t="n">
-        <v>1502.926687499644</v>
+        <v>1503.006687499644</v>
       </c>
       <c r="N25" t="n">
-        <v>1346.936646241608</v>
+        <v>1347.016646241608</v>
       </c>
       <c r="O25" t="n">
-        <v>1113.602925280855</v>
+        <v>1113.682925280855</v>
       </c>
       <c r="P25" t="n">
-        <v>819.8981109568782</v>
+        <v>819.9781109568783</v>
       </c>
       <c r="Q25" t="n">
-        <v>463.8958216380924</v>
+        <v>463.9758216380924</v>
       </c>
       <c r="R25" t="n">
-        <v>82.61634147829413</v>
+        <v>82.69634147829413</v>
       </c>
       <c r="S25" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="T25" t="n">
-        <v>164.3525496506081</v>
+        <v>164.4325496506081</v>
       </c>
       <c r="U25" t="n">
-        <v>332.7275321249604</v>
+        <v>332.8075321249603</v>
       </c>
       <c r="V25" t="n">
-        <v>453.3389250109063</v>
+        <v>453.4189250109063</v>
       </c>
       <c r="W25" t="n">
-        <v>547.0198432705838</v>
+        <v>547.0998432705837</v>
       </c>
       <c r="X25" t="n">
-        <v>619.8406342947774</v>
+        <v>619.9206342947773</v>
       </c>
       <c r="Y25" t="n">
-        <v>653.0399349738096</v>
+        <v>653.1199349738096</v>
       </c>
     </row>
     <row r="26">
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>596.438406042157</v>
+        <v>596.5184060421568</v>
       </c>
       <c r="C26" t="n">
-        <v>466.6661047866076</v>
+        <v>466.7461047866074</v>
       </c>
       <c r="D26" t="n">
-        <v>376.4245333322139</v>
+        <v>376.5045333322136</v>
       </c>
       <c r="E26" t="n">
-        <v>292.2191902949728</v>
+        <v>292.2991902949726</v>
       </c>
       <c r="F26" t="n">
-        <v>207.4821916000114</v>
+        <v>207.5621916000111</v>
       </c>
       <c r="G26" t="n">
-        <v>125.2979517892595</v>
+        <v>125.3779517892592</v>
       </c>
       <c r="H26" t="n">
-        <v>51.84000000000027</v>
+        <v>51.92</v>
       </c>
       <c r="I26" t="n">
-        <v>51.84000000000027</v>
+        <v>51.92</v>
       </c>
       <c r="J26" t="n">
-        <v>134.3602050736423</v>
+        <v>134.440205073642</v>
       </c>
       <c r="K26" t="n">
-        <v>775.8802050736455</v>
+        <v>776.950205073642</v>
       </c>
       <c r="L26" t="n">
-        <v>993.8163275862082</v>
+        <v>1419.460205073642</v>
       </c>
       <c r="M26" t="n">
-        <v>1635.336327586212</v>
+        <v>1419.460205073642</v>
       </c>
       <c r="N26" t="n">
-        <v>2230.549243836227</v>
+        <v>1419.460205073642</v>
       </c>
       <c r="O26" t="n">
-        <v>2393.691050093554</v>
+        <v>1582.602011330969</v>
       </c>
       <c r="P26" t="n">
-        <v>2592.000000000013</v>
+        <v>2008.265727912157</v>
       </c>
       <c r="Q26" t="n">
-        <v>2592.000000000013</v>
+        <v>2596</v>
       </c>
       <c r="R26" t="n">
-        <v>2592.000000000013</v>
+        <v>2595.065916015951</v>
       </c>
       <c r="S26" t="n">
-        <v>2448.504870855999</v>
+        <v>2451.570786871937</v>
       </c>
       <c r="T26" t="n">
-        <v>2186.313881748927</v>
+        <v>2189.379797764865</v>
       </c>
       <c r="U26" t="n">
-        <v>1854.889943810886</v>
+        <v>1857.955859826824</v>
       </c>
       <c r="V26" t="n">
-        <v>1542.919212329246</v>
+        <v>1545.985128345183</v>
       </c>
       <c r="W26" t="n">
-        <v>1225.32585967756</v>
+        <v>1225.405859677559</v>
       </c>
       <c r="X26" t="n">
-        <v>951.3038056768853</v>
+        <v>951.383805676885</v>
       </c>
       <c r="Y26" t="n">
-        <v>759.0639746841515</v>
+        <v>759.1439746841513</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>361.6657525511313</v>
+        <v>492.6258087310154</v>
       </c>
       <c r="C27" t="n">
-        <v>321.1607904849502</v>
+        <v>452.1208466648343</v>
       </c>
       <c r="D27" t="n">
-        <v>293.951005739796</v>
+        <v>424.9110619196801</v>
       </c>
       <c r="E27" t="n">
-        <v>272.0599984449348</v>
+        <v>403.0200546248188</v>
       </c>
       <c r="F27" t="n">
-        <v>253.2355112349582</v>
+        <v>384.1955674148422</v>
       </c>
       <c r="G27" t="n">
-        <v>249.2020177839109</v>
+        <v>380.162073963795</v>
       </c>
       <c r="H27" t="n">
-        <v>245.2023680625402</v>
+        <v>51.92</v>
       </c>
       <c r="I27" t="n">
-        <v>51.84000000000027</v>
+        <v>51.92</v>
       </c>
       <c r="J27" t="n">
-        <v>245.6076497036011</v>
+        <v>245.6876497036009</v>
       </c>
       <c r="K27" t="n">
-        <v>554.1188055149656</v>
+        <v>554.1988055149654</v>
       </c>
       <c r="L27" t="n">
-        <v>985.9074996573356</v>
+        <v>985.9874996573354</v>
       </c>
       <c r="M27" t="n">
-        <v>1259.211891400195</v>
+        <v>1259.291891400195</v>
       </c>
       <c r="N27" t="n">
-        <v>1584.67128421531</v>
+        <v>1584.75128421531</v>
       </c>
       <c r="O27" t="n">
-        <v>1999.520074672614</v>
+        <v>1999.600074672614</v>
       </c>
       <c r="P27" t="n">
-        <v>2253.149505368536</v>
+        <v>2253.229505368536</v>
       </c>
       <c r="Q27" t="n">
-        <v>2174.558747796677</v>
+        <v>2253.229505368536</v>
       </c>
       <c r="R27" t="n">
-        <v>1992.808314091777</v>
+        <v>2071.479071663636</v>
       </c>
       <c r="S27" t="n">
-        <v>1859.777639456283</v>
+        <v>1938.448397028141</v>
       </c>
       <c r="T27" t="n">
-        <v>1777.606588255059</v>
+        <v>1671.267985443944</v>
       </c>
       <c r="U27" t="n">
-        <v>1697.645723622128</v>
+        <v>1267.064696568588</v>
       </c>
       <c r="V27" t="n">
-        <v>1365.891845245755</v>
+        <v>848.3670529407902</v>
       </c>
       <c r="W27" t="n">
-        <v>1253.393721094413</v>
+        <v>735.8689287894483</v>
       </c>
       <c r="X27" t="n">
-        <v>829.2899438768495</v>
+        <v>636.0075758143093</v>
       </c>
       <c r="Y27" t="n">
-        <v>750.1067188605522</v>
+        <v>556.824350798012</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>681.4588756890414</v>
+        <v>686.6672726401017</v>
       </c>
       <c r="C28" t="n">
-        <v>729.2508815074772</v>
+        <v>734.4592784585375</v>
       </c>
       <c r="D28" t="n">
-        <v>764.3600256324772</v>
+        <v>769.5684225835375</v>
       </c>
       <c r="E28" t="n">
-        <v>803.9789298438902</v>
+        <v>809.1873267949505</v>
       </c>
       <c r="F28" t="n">
-        <v>850.1299024358257</v>
+        <v>855.338299386886</v>
       </c>
       <c r="G28" t="n">
-        <v>925.9459486505798</v>
+        <v>931.1543456016401</v>
       </c>
       <c r="H28" t="n">
-        <v>1022.760277088666</v>
+        <v>1022.840277088666</v>
       </c>
       <c r="I28" t="n">
-        <v>1184.312618975569</v>
+        <v>1184.392618975568</v>
       </c>
       <c r="J28" t="n">
-        <v>1510.983618808348</v>
+        <v>1511.063618808347</v>
       </c>
       <c r="K28" t="n">
-        <v>1615.110403564888</v>
+        <v>1615.190403564888</v>
       </c>
       <c r="L28" t="n">
-        <v>1605.496770221213</v>
+        <v>1605.576770221213</v>
       </c>
       <c r="M28" t="n">
-        <v>1502.926687499644</v>
+        <v>1503.006687499644</v>
       </c>
       <c r="N28" t="n">
-        <v>1346.936646241609</v>
+        <v>1347.016646241608</v>
       </c>
       <c r="O28" t="n">
-        <v>1113.602925280855</v>
+        <v>1113.682925280855</v>
       </c>
       <c r="P28" t="n">
-        <v>819.8981109568786</v>
+        <v>819.9781109568783</v>
       </c>
       <c r="Q28" t="n">
-        <v>463.8958216380926</v>
+        <v>463.9758216380924</v>
       </c>
       <c r="R28" t="n">
-        <v>82.61634147829439</v>
+        <v>82.69634147829412</v>
       </c>
       <c r="S28" t="n">
-        <v>51.84000000000027</v>
+        <v>51.92</v>
       </c>
       <c r="T28" t="n">
-        <v>164.3525496506084</v>
+        <v>164.4325496506081</v>
       </c>
       <c r="U28" t="n">
-        <v>332.7275321249606</v>
+        <v>332.8075321249603</v>
       </c>
       <c r="V28" t="n">
-        <v>453.3389250109066</v>
+        <v>453.4189250109063</v>
       </c>
       <c r="W28" t="n">
-        <v>547.019843270584</v>
+        <v>547.0998432705837</v>
       </c>
       <c r="X28" t="n">
-        <v>619.8406342947776</v>
+        <v>619.9206342947773</v>
       </c>
       <c r="Y28" t="n">
-        <v>647.9115380227493</v>
+        <v>653.1199349738096</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>596.438406042157</v>
+        <v>596.5184060421567</v>
       </c>
       <c r="C29" t="n">
-        <v>466.6661047866076</v>
+        <v>466.7461047866073</v>
       </c>
       <c r="D29" t="n">
-        <v>376.4245333322139</v>
+        <v>376.5045333322136</v>
       </c>
       <c r="E29" t="n">
-        <v>292.2191902949728</v>
+        <v>292.2991902949725</v>
       </c>
       <c r="F29" t="n">
-        <v>207.4821916000113</v>
+        <v>207.562191600011</v>
       </c>
       <c r="G29" t="n">
-        <v>125.2979517892595</v>
+        <v>125.3779517892592</v>
       </c>
       <c r="H29" t="n">
-        <v>51.84000000000027</v>
+        <v>51.92</v>
       </c>
       <c r="I29" t="n">
-        <v>51.84000000000027</v>
+        <v>51.92</v>
       </c>
       <c r="J29" t="n">
-        <v>134.3602050736423</v>
+        <v>134.440205073642</v>
       </c>
       <c r="K29" t="n">
-        <v>775.8802050736455</v>
+        <v>310.1117798977626</v>
       </c>
       <c r="L29" t="n">
-        <v>993.8163275862082</v>
+        <v>528.0479024103255</v>
       </c>
       <c r="M29" t="n">
-        <v>1635.336327586212</v>
+        <v>723.2457279121568</v>
       </c>
       <c r="N29" t="n">
-        <v>2230.549243836227</v>
+        <v>723.2457279121568</v>
       </c>
       <c r="O29" t="n">
-        <v>2393.691050093554</v>
+        <v>1365.755727912157</v>
       </c>
       <c r="P29" t="n">
-        <v>2592.000000000013</v>
+        <v>2008.265727912157</v>
       </c>
       <c r="Q29" t="n">
-        <v>2592.000000000013</v>
+        <v>2596</v>
       </c>
       <c r="R29" t="n">
-        <v>2592.000000000013</v>
+        <v>2595.065916015951</v>
       </c>
       <c r="S29" t="n">
-        <v>2448.504870855999</v>
+        <v>2451.570786871937</v>
       </c>
       <c r="T29" t="n">
-        <v>2186.313881748927</v>
+        <v>2189.379797764865</v>
       </c>
       <c r="U29" t="n">
-        <v>1854.889943810886</v>
+        <v>1857.955859826824</v>
       </c>
       <c r="V29" t="n">
-        <v>1542.919212329245</v>
+        <v>1545.985128345183</v>
       </c>
       <c r="W29" t="n">
-        <v>1225.32585967756</v>
+        <v>1225.405859677559</v>
       </c>
       <c r="X29" t="n">
-        <v>951.3038056768853</v>
+        <v>951.383805676885</v>
       </c>
       <c r="Y29" t="n">
-        <v>759.0639746841515</v>
+        <v>759.1439746841512</v>
       </c>
     </row>
     <row r="30">
@@ -6509,76 +6509,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1141.030657215864</v>
+        <v>677.6351691139887</v>
       </c>
       <c r="C30" t="n">
-        <v>776.2832709072588</v>
+        <v>312.8877828053833</v>
       </c>
       <c r="D30" t="n">
-        <v>424.8310619196803</v>
+        <v>285.6779980602291</v>
       </c>
       <c r="E30" t="n">
-        <v>78.69763038239481</v>
+        <v>263.7869907653679</v>
       </c>
       <c r="F30" t="n">
-        <v>59.87314317241818</v>
+        <v>244.9625035553912</v>
       </c>
       <c r="G30" t="n">
-        <v>55.83964972137094</v>
+        <v>240.929010104344</v>
       </c>
       <c r="H30" t="n">
-        <v>51.84000000000027</v>
+        <v>51.92</v>
       </c>
       <c r="I30" t="n">
-        <v>51.84000000000027</v>
+        <v>51.92</v>
       </c>
       <c r="J30" t="n">
-        <v>245.6076497036011</v>
+        <v>245.6876497036009</v>
       </c>
       <c r="K30" t="n">
-        <v>554.1188055149656</v>
+        <v>554.1988055149654</v>
       </c>
       <c r="L30" t="n">
-        <v>985.9074996573356</v>
+        <v>985.9874996573354</v>
       </c>
       <c r="M30" t="n">
-        <v>1259.211891400195</v>
+        <v>1259.291891400195</v>
       </c>
       <c r="N30" t="n">
-        <v>1584.67128421531</v>
+        <v>1584.75128421531</v>
       </c>
       <c r="O30" t="n">
-        <v>1999.520074672614</v>
+        <v>1999.600074672614</v>
       </c>
       <c r="P30" t="n">
-        <v>2253.149505368536</v>
+        <v>2253.229505368536</v>
       </c>
       <c r="Q30" t="n">
-        <v>2174.558747796677</v>
+        <v>2253.229505368536</v>
       </c>
       <c r="R30" t="n">
-        <v>1992.808314091777</v>
+        <v>2071.479071663636</v>
       </c>
       <c r="S30" t="n">
-        <v>1859.777639456283</v>
+        <v>1938.448397028141</v>
       </c>
       <c r="T30" t="n">
-        <v>1777.606588255059</v>
+        <v>1856.277345826917</v>
       </c>
       <c r="U30" t="n">
-        <v>1697.645723622128</v>
+        <v>1776.316481193986</v>
       </c>
       <c r="V30" t="n">
-        <v>1603.190504236754</v>
+        <v>1681.861261808612</v>
       </c>
       <c r="W30" t="n">
-        <v>1490.692380085412</v>
+        <v>1569.36313765727</v>
       </c>
       <c r="X30" t="n">
-        <v>1390.831027110273</v>
+        <v>1469.501784682131</v>
       </c>
       <c r="Y30" t="n">
-        <v>1311.647802093976</v>
+        <v>1066.07613542341</v>
       </c>
     </row>
     <row r="31">
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>686.587272640102</v>
+        <v>686.6672726401017</v>
       </c>
       <c r="C31" t="n">
-        <v>734.3792784585378</v>
+        <v>734.4592784585375</v>
       </c>
       <c r="D31" t="n">
-        <v>769.4884225835378</v>
+        <v>769.5684225835375</v>
       </c>
       <c r="E31" t="n">
-        <v>809.1073267949508</v>
+        <v>809.1873267949505</v>
       </c>
       <c r="F31" t="n">
-        <v>855.2582993868863</v>
+        <v>855.338299386886</v>
       </c>
       <c r="G31" t="n">
-        <v>931.0743456016404</v>
+        <v>931.1543456016401</v>
       </c>
       <c r="H31" t="n">
-        <v>1027.888674039727</v>
+        <v>1027.968674039726</v>
       </c>
       <c r="I31" t="n">
-        <v>1189.441015926629</v>
+        <v>1189.521015926629</v>
       </c>
       <c r="J31" t="n">
-        <v>1510.983618808348</v>
+        <v>1511.063618808347</v>
       </c>
       <c r="K31" t="n">
-        <v>1615.110403564888</v>
+        <v>1615.190403564888</v>
       </c>
       <c r="L31" t="n">
-        <v>1605.496770221213</v>
+        <v>1605.576770221213</v>
       </c>
       <c r="M31" t="n">
-        <v>1502.926687499644</v>
+        <v>1503.006687499644</v>
       </c>
       <c r="N31" t="n">
-        <v>1346.936646241609</v>
+        <v>1347.016646241608</v>
       </c>
       <c r="O31" t="n">
-        <v>1113.602925280855</v>
+        <v>1113.682925280855</v>
       </c>
       <c r="P31" t="n">
-        <v>819.8981109568786</v>
+        <v>819.9781109568783</v>
       </c>
       <c r="Q31" t="n">
-        <v>463.8958216380927</v>
+        <v>463.9758216380924</v>
       </c>
       <c r="R31" t="n">
-        <v>82.6163414782944</v>
+        <v>82.69634147829413</v>
       </c>
       <c r="S31" t="n">
-        <v>51.84000000000027</v>
+        <v>51.92</v>
       </c>
       <c r="T31" t="n">
-        <v>164.3525496506084</v>
+        <v>164.4325496506081</v>
       </c>
       <c r="U31" t="n">
-        <v>332.7275321249606</v>
+        <v>332.8075321249603</v>
       </c>
       <c r="V31" t="n">
-        <v>453.3389250109066</v>
+        <v>453.4189250109063</v>
       </c>
       <c r="W31" t="n">
-        <v>547.019843270584</v>
+        <v>547.0998432705837</v>
       </c>
       <c r="X31" t="n">
-        <v>619.8406342947776</v>
+        <v>619.9206342947773</v>
       </c>
       <c r="Y31" t="n">
-        <v>653.0399349738099</v>
+        <v>653.1199349738096</v>
       </c>
     </row>
     <row r="32">
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>593.4524900262552</v>
+        <v>596.5184060421568</v>
       </c>
       <c r="C32" t="n">
-        <v>463.6801887707057</v>
+        <v>466.7461047866074</v>
       </c>
       <c r="D32" t="n">
-        <v>373.438617316312</v>
+        <v>376.5045333322136</v>
       </c>
       <c r="E32" t="n">
-        <v>289.2332742790709</v>
+        <v>292.2991902949726</v>
       </c>
       <c r="F32" t="n">
-        <v>204.4962755841095</v>
+        <v>207.5621916000111</v>
       </c>
       <c r="G32" t="n">
-        <v>122.3120357733576</v>
+        <v>125.3779517892592</v>
       </c>
       <c r="H32" t="n">
-        <v>51.84000000000027</v>
+        <v>51.92</v>
       </c>
       <c r="I32" t="n">
-        <v>51.84000000000027</v>
+        <v>51.92</v>
       </c>
       <c r="J32" t="n">
-        <v>134.3602050736423</v>
+        <v>134.440205073642</v>
       </c>
       <c r="K32" t="n">
-        <v>310.0317798977629</v>
+        <v>776.950205073642</v>
       </c>
       <c r="L32" t="n">
-        <v>527.9679024103257</v>
+        <v>994.8863275862049</v>
       </c>
       <c r="M32" t="n">
-        <v>1169.487902410331</v>
+        <v>1637.396327586205</v>
       </c>
       <c r="N32" t="n">
-        <v>1642.814971748384</v>
+        <v>1637.396327586205</v>
       </c>
       <c r="O32" t="n">
-        <v>1805.956778005711</v>
+        <v>2279.906327586205</v>
       </c>
       <c r="P32" t="n">
-        <v>2004.26572791217</v>
+        <v>2478.215277492664</v>
       </c>
       <c r="Q32" t="n">
-        <v>2592.000000000013</v>
+        <v>2596</v>
       </c>
       <c r="R32" t="n">
-        <v>2592.00000000005</v>
+        <v>2595.065916015951</v>
       </c>
       <c r="S32" t="n">
-        <v>2448.504870856035</v>
+        <v>2451.570786871937</v>
       </c>
       <c r="T32" t="n">
-        <v>2186.313881748963</v>
+        <v>2189.379797764865</v>
       </c>
       <c r="U32" t="n">
-        <v>1854.889943810922</v>
+        <v>1857.955859826824</v>
       </c>
       <c r="V32" t="n">
-        <v>1542.919212329282</v>
+        <v>1545.985128345183</v>
       </c>
       <c r="W32" t="n">
-        <v>1222.339943661658</v>
+        <v>1225.405859677559</v>
       </c>
       <c r="X32" t="n">
-        <v>948.3178896609834</v>
+        <v>951.383805676885</v>
       </c>
       <c r="Y32" t="n">
-        <v>756.0780586682497</v>
+        <v>759.1439746841513</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1001.797593356413</v>
+        <v>816.8682329734395</v>
       </c>
       <c r="C33" t="n">
-        <v>637.0502070478078</v>
+        <v>776.3632709072584</v>
       </c>
       <c r="D33" t="n">
-        <v>609.8404223026537</v>
+        <v>749.1534861621043</v>
       </c>
       <c r="E33" t="n">
-        <v>587.9494150077925</v>
+        <v>727.2624788672431</v>
       </c>
       <c r="F33" t="n">
-        <v>244.8825035553916</v>
+        <v>708.4379916572665</v>
       </c>
       <c r="G33" t="n">
-        <v>240.8490101043443</v>
+        <v>380.162073963795</v>
       </c>
       <c r="H33" t="n">
-        <v>236.8493603829737</v>
+        <v>51.92</v>
       </c>
       <c r="I33" t="n">
-        <v>51.84000000000027</v>
+        <v>51.92</v>
       </c>
       <c r="J33" t="n">
-        <v>245.6076497036011</v>
+        <v>245.6876497036009</v>
       </c>
       <c r="K33" t="n">
-        <v>554.1188055149656</v>
+        <v>554.1988055149654</v>
       </c>
       <c r="L33" t="n">
-        <v>985.9074996573356</v>
+        <v>985.9874996573354</v>
       </c>
       <c r="M33" t="n">
-        <v>1259.211891400195</v>
+        <v>1259.291891400195</v>
       </c>
       <c r="N33" t="n">
-        <v>1584.67128421531</v>
+        <v>1584.75128421531</v>
       </c>
       <c r="O33" t="n">
-        <v>1999.520074672614</v>
+        <v>1999.600074672614</v>
       </c>
       <c r="P33" t="n">
-        <v>2253.149505368536</v>
+        <v>2253.229505368536</v>
       </c>
       <c r="Q33" t="n">
-        <v>2253.149505368536</v>
+        <v>2253.229505368536</v>
       </c>
       <c r="R33" t="n">
-        <v>2071.399071663636</v>
+        <v>2071.479071663636</v>
       </c>
       <c r="S33" t="n">
-        <v>1938.368397028141</v>
+        <v>1938.448397028141</v>
       </c>
       <c r="T33" t="n">
-        <v>1856.197345826917</v>
+        <v>1532.034921584493</v>
       </c>
       <c r="U33" t="n">
-        <v>1776.236481193986</v>
+        <v>1267.064696568588</v>
       </c>
       <c r="V33" t="n">
-        <v>1681.781261808612</v>
+        <v>1172.609477183214</v>
       </c>
       <c r="W33" t="n">
-        <v>1569.28313765727</v>
+        <v>1060.111353031872</v>
       </c>
       <c r="X33" t="n">
-        <v>1145.179360439707</v>
+        <v>960.2500000567334</v>
       </c>
       <c r="Y33" t="n">
-        <v>1065.99613542341</v>
+        <v>881.066775040436</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>681.4588756890414</v>
+        <v>681.5388756890411</v>
       </c>
       <c r="C34" t="n">
-        <v>729.2508815074772</v>
+        <v>729.3308815074769</v>
       </c>
       <c r="D34" t="n">
-        <v>764.3600256324772</v>
+        <v>764.4400256324769</v>
       </c>
       <c r="E34" t="n">
-        <v>803.9789298438902</v>
+        <v>804.0589298438899</v>
       </c>
       <c r="F34" t="n">
-        <v>850.1299024358257</v>
+        <v>850.2099024358254</v>
       </c>
       <c r="G34" t="n">
-        <v>925.9459486505798</v>
+        <v>926.0259486505795</v>
       </c>
       <c r="H34" t="n">
-        <v>1022.760277088666</v>
+        <v>1022.840277088666</v>
       </c>
       <c r="I34" t="n">
-        <v>1184.312618975569</v>
+        <v>1184.392618975568</v>
       </c>
       <c r="J34" t="n">
-        <v>1510.983618808348</v>
+        <v>1511.063618808347</v>
       </c>
       <c r="K34" t="n">
-        <v>1615.110403564888</v>
+        <v>1615.190403564888</v>
       </c>
       <c r="L34" t="n">
-        <v>1605.496770221213</v>
+        <v>1605.576770221213</v>
       </c>
       <c r="M34" t="n">
-        <v>1502.926687499644</v>
+        <v>1503.006687499644</v>
       </c>
       <c r="N34" t="n">
-        <v>1346.936646241609</v>
+        <v>1347.016646241608</v>
       </c>
       <c r="O34" t="n">
-        <v>1113.602925280855</v>
+        <v>1113.682925280855</v>
       </c>
       <c r="P34" t="n">
-        <v>819.8981109568786</v>
+        <v>819.9781109568783</v>
       </c>
       <c r="Q34" t="n">
-        <v>463.8958216380927</v>
+        <v>463.9758216380924</v>
       </c>
       <c r="R34" t="n">
-        <v>82.6163414782944</v>
+        <v>82.69634147829412</v>
       </c>
       <c r="S34" t="n">
-        <v>51.84000000000027</v>
+        <v>51.92</v>
       </c>
       <c r="T34" t="n">
-        <v>164.3525496506084</v>
+        <v>164.4325496506081</v>
       </c>
       <c r="U34" t="n">
-        <v>332.7275321249606</v>
+        <v>332.8075321249603</v>
       </c>
       <c r="V34" t="n">
-        <v>453.3389250109066</v>
+        <v>453.4189250109063</v>
       </c>
       <c r="W34" t="n">
-        <v>547.019843270584</v>
+        <v>547.0998432705837</v>
       </c>
       <c r="X34" t="n">
-        <v>619.8406342947776</v>
+        <v>619.9206342947773</v>
       </c>
       <c r="Y34" t="n">
-        <v>647.9115380227493</v>
+        <v>647.991538022749</v>
       </c>
     </row>
     <row r="35">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>439.3918839656399</v>
+        <v>444.0238605876129</v>
       </c>
       <c r="C35" t="n">
-        <v>333.8620069525147</v>
+        <v>338.4939835744877</v>
       </c>
       <c r="D35" t="n">
-        <v>267.8628597405452</v>
+        <v>272.4948363625182</v>
       </c>
       <c r="E35" t="n">
-        <v>207.8999409457283</v>
+        <v>212.5319175677014</v>
       </c>
       <c r="F35" t="n">
-        <v>147.4053664931911</v>
+        <v>152.0373431151642</v>
       </c>
       <c r="G35" t="n">
-        <v>94.09552754683577</v>
+        <v>94.09552754683659</v>
       </c>
       <c r="H35" t="n">
-        <v>44.88000000000081</v>
+        <v>44.88000000000164</v>
       </c>
       <c r="I35" t="n">
-        <v>44.88000000000081</v>
+        <v>44.88000000000164</v>
       </c>
       <c r="J35" t="n">
-        <v>127.4002050736428</v>
+        <v>127.4002050736436</v>
       </c>
       <c r="K35" t="n">
-        <v>303.0717798977635</v>
+        <v>303.0717798977642</v>
       </c>
       <c r="L35" t="n">
-        <v>771.7692438362526</v>
+        <v>858.4617798977846</v>
       </c>
       <c r="M35" t="n">
-        <v>1327.159243836254</v>
+        <v>1327.159243836284</v>
       </c>
       <c r="N35" t="n">
-        <v>1882.549243836255</v>
+        <v>1327.159243836284</v>
       </c>
       <c r="O35" t="n">
-        <v>2045.691050093581</v>
+        <v>1490.301050093611</v>
       </c>
       <c r="P35" t="n">
-        <v>2244.00000000004</v>
+        <v>1688.61000000007</v>
       </c>
       <c r="Q35" t="n">
-        <v>2244.00000000004</v>
+        <v>2244.000000000082</v>
       </c>
       <c r="R35" t="n">
-        <v>2244.00000000004</v>
+        <v>2244.000000000082</v>
       </c>
       <c r="S35" t="n">
-        <v>2124.74729509845</v>
+        <v>2124.747295098492</v>
       </c>
       <c r="T35" t="n">
-        <v>1886.798730233803</v>
+        <v>1886.798730233844</v>
       </c>
       <c r="U35" t="n">
-        <v>1579.617216538185</v>
+        <v>1579.617216538227</v>
       </c>
       <c r="V35" t="n">
-        <v>1291.888909298969</v>
+        <v>1291.888909299011</v>
       </c>
       <c r="W35" t="n">
-        <v>995.5520648737697</v>
+        <v>995.5520648738116</v>
       </c>
       <c r="X35" t="n">
-        <v>745.7724351155196</v>
+        <v>745.7724351155614</v>
       </c>
       <c r="Y35" t="n">
-        <v>577.7750283652101</v>
+        <v>577.775028365252</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1107.996724355453</v>
+        <v>838.1026334425048</v>
       </c>
       <c r="C36" t="n">
-        <v>743.2493380468479</v>
+        <v>584.2766400176724</v>
       </c>
       <c r="D36" t="n">
-        <v>734.0803429896872</v>
+        <v>581.3092795149425</v>
       </c>
       <c r="E36" t="n">
-        <v>387.9469114524017</v>
+        <v>581.3092795149425</v>
       </c>
       <c r="F36" t="n">
-        <v>44.88000000000081</v>
+        <v>238.2423680625416</v>
       </c>
       <c r="G36" t="n">
-        <v>44.88000000000081</v>
+        <v>238.2423680625416</v>
       </c>
       <c r="H36" t="n">
-        <v>44.88000000000081</v>
+        <v>238.2423680625416</v>
       </c>
       <c r="I36" t="n">
-        <v>44.88000000000081</v>
+        <v>44.88000000000164</v>
       </c>
       <c r="J36" t="n">
-        <v>238.6476497036017</v>
+        <v>238.6476497036025</v>
       </c>
       <c r="K36" t="n">
-        <v>547.1588055149662</v>
+        <v>547.1588055149671</v>
       </c>
       <c r="L36" t="n">
-        <v>978.9474996573362</v>
+        <v>978.9474996573371</v>
       </c>
       <c r="M36" t="n">
-        <v>1252.251891400195</v>
+        <v>1252.251891400196</v>
       </c>
       <c r="N36" t="n">
-        <v>1577.711284215311</v>
+        <v>1575.521778846857</v>
       </c>
       <c r="O36" t="n">
-        <v>1990.370569304119</v>
+        <v>1990.370569304161</v>
       </c>
       <c r="P36" t="n">
-        <v>2244.00000000004</v>
+        <v>2244.000000000082</v>
       </c>
       <c r="Q36" t="n">
-        <v>2165.409242428182</v>
+        <v>2244.000000000082</v>
       </c>
       <c r="R36" t="n">
-        <v>2007.901232965706</v>
+        <v>2086.491990537606</v>
       </c>
       <c r="S36" t="n">
-        <v>1899.112982572636</v>
+        <v>1977.703740144536</v>
       </c>
       <c r="T36" t="n">
-        <v>1841.184355613836</v>
+        <v>1919.775113185736</v>
       </c>
       <c r="U36" t="n">
-        <v>1785.465915223329</v>
+        <v>1864.056672795229</v>
       </c>
       <c r="V36" t="n">
-        <v>1715.25312008038</v>
+        <v>1793.84387765228</v>
       </c>
       <c r="W36" t="n">
-        <v>1278.512571686613</v>
+        <v>1357.103329258513</v>
       </c>
       <c r="X36" t="n">
-        <v>1202.893642953899</v>
+        <v>932.9995520409502</v>
       </c>
       <c r="Y36" t="n">
-        <v>1147.952842180026</v>
+        <v>878.0587512670771</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>608.5605946885328</v>
+        <v>442.9648607962332</v>
       </c>
       <c r="C37" t="n">
-        <v>680.1126005069685</v>
+        <v>514.516866614669</v>
       </c>
       <c r="D37" t="n">
-        <v>738.9817446319686</v>
+        <v>573.386010739669</v>
       </c>
       <c r="E37" t="n">
-        <v>802.3606488433816</v>
+        <v>573.386010739669</v>
       </c>
       <c r="F37" t="n">
-        <v>872.2716214353171</v>
+        <v>573.386010739669</v>
       </c>
       <c r="G37" t="n">
-        <v>971.8476676500712</v>
+        <v>672.9620569544231</v>
       </c>
       <c r="H37" t="n">
-        <v>1092.421996088157</v>
+        <v>793.5363853925093</v>
       </c>
       <c r="I37" t="n">
-        <v>1277.73433797506</v>
+        <v>936.1843379750608</v>
       </c>
       <c r="J37" t="n">
-        <v>1286.615337807839</v>
+        <v>1286.61533780784</v>
       </c>
       <c r="K37" t="n">
         <v>1414.50212256438</v>
       </c>
       <c r="L37" t="n">
-        <v>1428.839800524244</v>
+        <v>1428.839800524245</v>
       </c>
       <c r="M37" t="n">
-        <v>1350.512142045099</v>
+        <v>1350.5121420451</v>
       </c>
       <c r="N37" t="n">
-        <v>1218.764525029488</v>
+        <v>1218.764525029489</v>
       </c>
       <c r="O37" t="n">
-        <v>1009.673228311158</v>
+        <v>1009.673228311159</v>
       </c>
       <c r="P37" t="n">
-        <v>740.2108382296062</v>
+        <v>740.2108382296071</v>
       </c>
       <c r="Q37" t="n">
-        <v>408.4509731532447</v>
+        <v>408.4509731532455</v>
       </c>
       <c r="R37" t="n">
-        <v>51.4139172358707</v>
+        <v>51.41391723587153</v>
       </c>
       <c r="S37" t="n">
-        <v>44.88000000000081</v>
+        <v>44.88000000000164</v>
       </c>
       <c r="T37" t="n">
-        <v>44.88000000000081</v>
+        <v>181.1525496506098</v>
       </c>
       <c r="U37" t="n">
-        <v>135.9008541733915</v>
+        <v>181.1525496506098</v>
       </c>
       <c r="V37" t="n">
-        <v>280.2722470593375</v>
+        <v>325.5239425365558</v>
       </c>
       <c r="W37" t="n">
-        <v>397.7131653190149</v>
+        <v>442.9648607962332</v>
       </c>
       <c r="X37" t="n">
-        <v>494.2939563432084</v>
+        <v>442.9648607962332</v>
       </c>
       <c r="Y37" t="n">
-        <v>551.2532570222406</v>
+        <v>442.9648607962332</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>444.0238605876024</v>
+        <v>439.3918839656653</v>
       </c>
       <c r="C38" t="n">
-        <v>338.4939835744772</v>
+        <v>333.8620069525401</v>
       </c>
       <c r="D38" t="n">
-        <v>272.4948363625077</v>
+        <v>267.8628597405706</v>
       </c>
       <c r="E38" t="n">
-        <v>212.5319175676908</v>
+        <v>207.8999409457538</v>
       </c>
       <c r="F38" t="n">
-        <v>152.0373431151536</v>
+        <v>147.4053664932166</v>
       </c>
       <c r="G38" t="n">
-        <v>94.09552754682599</v>
+        <v>89.46355092488895</v>
       </c>
       <c r="H38" t="n">
-        <v>44.87999999999101</v>
+        <v>44.88000000000164</v>
       </c>
       <c r="I38" t="n">
-        <v>44.88000000000081</v>
+        <v>44.88000000000164</v>
       </c>
       <c r="J38" t="n">
-        <v>127.4002050736428</v>
+        <v>553.4018942939388</v>
       </c>
       <c r="K38" t="n">
-        <v>682.7902050736528</v>
+        <v>729.0734691180594</v>
       </c>
       <c r="L38" t="n">
-        <v>900.7263275862157</v>
+        <v>947.0095916306221</v>
       </c>
       <c r="M38" t="n">
-        <v>1456.116327586219</v>
+        <v>1133.220000000064</v>
       </c>
       <c r="N38" t="n">
-        <v>1882.549243836255</v>
+        <v>1133.220000000064</v>
       </c>
       <c r="O38" t="n">
-        <v>2045.691050093581</v>
+        <v>1688.610000000073</v>
       </c>
       <c r="P38" t="n">
-        <v>2244.00000000004</v>
+        <v>2244.000000000082</v>
       </c>
       <c r="Q38" t="n">
-        <v>2244.00000000004</v>
+        <v>2244.000000000082</v>
       </c>
       <c r="R38" t="n">
-        <v>2244.00000000004</v>
+        <v>2244.000000000066</v>
       </c>
       <c r="S38" t="n">
-        <v>2124.74729509845</v>
+        <v>2124.747295098476</v>
       </c>
       <c r="T38" t="n">
-        <v>1886.798730233803</v>
+        <v>1886.798730233828</v>
       </c>
       <c r="U38" t="n">
-        <v>1579.617216538185</v>
+        <v>1579.617216538211</v>
       </c>
       <c r="V38" t="n">
-        <v>1291.888909298969</v>
+        <v>1291.888909298995</v>
       </c>
       <c r="W38" t="n">
-        <v>995.5520648737697</v>
+        <v>995.5520648737952</v>
       </c>
       <c r="X38" t="n">
-        <v>750.4044117374822</v>
+        <v>745.772435115545</v>
       </c>
       <c r="Y38" t="n">
-        <v>582.4070049871726</v>
+        <v>577.7750283652356</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1186.587481927312</v>
+        <v>489.6177849576399</v>
       </c>
       <c r="C39" t="n">
-        <v>821.8400956187061</v>
+        <v>473.355247133883</v>
       </c>
       <c r="D39" t="n">
-        <v>470.3878866311276</v>
+        <v>470.3878866311531</v>
       </c>
       <c r="E39" t="n">
-        <v>124.2544550938421</v>
+        <v>470.3878866311531</v>
       </c>
       <c r="F39" t="n">
-        <v>44.88000000000081</v>
+        <v>127.3209751787522</v>
       </c>
       <c r="G39" t="n">
-        <v>44.88000000000081</v>
+        <v>44.88000000000164</v>
       </c>
       <c r="H39" t="n">
-        <v>44.88000000000081</v>
+        <v>44.88000000000164</v>
       </c>
       <c r="I39" t="n">
-        <v>44.88000000000081</v>
+        <v>44.88000000000164</v>
       </c>
       <c r="J39" t="n">
-        <v>238.6476497036017</v>
+        <v>238.6476497036025</v>
       </c>
       <c r="K39" t="n">
-        <v>547.1588055149662</v>
+        <v>547.1588055149671</v>
       </c>
       <c r="L39" t="n">
-        <v>976.7579942888401</v>
+        <v>976.7579942888656</v>
       </c>
       <c r="M39" t="n">
-        <v>1250.062386031699</v>
+        <v>1250.062386031725</v>
       </c>
       <c r="N39" t="n">
-        <v>1575.521778846815</v>
+        <v>1575.52177884684</v>
       </c>
       <c r="O39" t="n">
-        <v>1990.370569304119</v>
+        <v>1990.370569304144</v>
       </c>
       <c r="P39" t="n">
-        <v>2244.00000000004</v>
+        <v>2244.000000000066</v>
       </c>
       <c r="Q39" t="n">
-        <v>2244.00000000004</v>
+        <v>2244.000000000066</v>
       </c>
       <c r="R39" t="n">
-        <v>2086.491990537565</v>
+        <v>2086.49199053759</v>
       </c>
       <c r="S39" t="n">
-        <v>1977.703740144494</v>
+        <v>1977.70374014452</v>
       </c>
       <c r="T39" t="n">
-        <v>1919.775113185694</v>
+        <v>1919.77511318572</v>
       </c>
       <c r="U39" t="n">
-        <v>1864.056672795188</v>
+        <v>1515.571824310364</v>
       </c>
       <c r="V39" t="n">
-        <v>1793.843877652238</v>
+        <v>1096.874180682566</v>
       </c>
       <c r="W39" t="n">
-        <v>1705.58817774332</v>
+        <v>1008.618480773649</v>
       </c>
       <c r="X39" t="n">
-        <v>1629.969249010605</v>
+        <v>932.9995520409338</v>
       </c>
       <c r="Y39" t="n">
-        <v>1575.028448236732</v>
+        <v>529.5739027822123</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>808.2106145353</v>
+        <v>422.1047335607493</v>
       </c>
       <c r="C40" t="n">
-        <v>879.7626203537358</v>
+        <v>422.1047335607493</v>
       </c>
       <c r="D40" t="n">
-        <v>938.6317644787358</v>
+        <v>480.9738776857494</v>
       </c>
       <c r="E40" t="n">
-        <v>1002.010668690149</v>
+        <v>544.3527818971623</v>
       </c>
       <c r="F40" t="n">
-        <v>1071.921641282084</v>
+        <v>544.3527818971623</v>
       </c>
       <c r="G40" t="n">
-        <v>1171.497687496838</v>
+        <v>643.9288281119165</v>
       </c>
       <c r="H40" t="n">
-        <v>1292.072015934924</v>
+        <v>764.5031565500026</v>
       </c>
       <c r="I40" t="n">
-        <v>1292.072015934924</v>
+        <v>949.8154984369052</v>
       </c>
       <c r="J40" t="n">
-        <v>1300.953015767704</v>
+        <v>1300.246498269684</v>
       </c>
       <c r="K40" t="n">
-        <v>1428.839800524244</v>
+        <v>1414.502122564381</v>
       </c>
       <c r="L40" t="n">
-        <v>1428.839800524244</v>
+        <v>1428.839800524245</v>
       </c>
       <c r="M40" t="n">
-        <v>1350.512142045099</v>
+        <v>1350.5121420451</v>
       </c>
       <c r="N40" t="n">
-        <v>1218.764525029488</v>
+        <v>1218.764525029489</v>
       </c>
       <c r="O40" t="n">
-        <v>1009.673228311158</v>
+        <v>1009.673228311159</v>
       </c>
       <c r="P40" t="n">
-        <v>740.2108382296063</v>
+        <v>740.2108382296071</v>
       </c>
       <c r="Q40" t="n">
-        <v>408.4509731532447</v>
+        <v>408.4509731532455</v>
       </c>
       <c r="R40" t="n">
-        <v>51.41391723587068</v>
+        <v>51.41391723587152</v>
       </c>
       <c r="S40" t="n">
-        <v>44.88000000000081</v>
+        <v>44.88000000000164</v>
       </c>
       <c r="T40" t="n">
-        <v>181.152549650609</v>
+        <v>181.1525496506098</v>
       </c>
       <c r="U40" t="n">
-        <v>335.5508740201587</v>
+        <v>181.1525496506098</v>
       </c>
       <c r="V40" t="n">
-        <v>479.9222669061047</v>
+        <v>325.5239425365558</v>
       </c>
       <c r="W40" t="n">
-        <v>597.3631851657821</v>
+        <v>325.5239425365558</v>
       </c>
       <c r="X40" t="n">
-        <v>693.9439761899756</v>
+        <v>422.1047335607493</v>
       </c>
       <c r="Y40" t="n">
-        <v>750.9032768690079</v>
+        <v>422.1047335607493</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>439.3918839656399</v>
+        <v>439.3918839656817</v>
       </c>
       <c r="C41" t="n">
-        <v>333.8620069525147</v>
+        <v>333.8620069525565</v>
       </c>
       <c r="D41" t="n">
-        <v>267.8628597405452</v>
+        <v>267.862859740587</v>
       </c>
       <c r="E41" t="n">
-        <v>207.8999409457283</v>
+        <v>207.8999409457702</v>
       </c>
       <c r="F41" t="n">
-        <v>147.4053664931911</v>
+        <v>147.4053664932329</v>
       </c>
       <c r="G41" t="n">
-        <v>89.46355092486348</v>
+        <v>94.09552754683659</v>
       </c>
       <c r="H41" t="n">
-        <v>44.88000000000081</v>
+        <v>44.88000000000164</v>
       </c>
       <c r="I41" t="n">
-        <v>44.88000000000081</v>
+        <v>44.88000000000164</v>
       </c>
       <c r="J41" t="n">
-        <v>553.401894293938</v>
+        <v>127.4002050736436</v>
       </c>
       <c r="K41" t="n">
-        <v>729.0734691180586</v>
+        <v>682.790205073664</v>
       </c>
       <c r="L41" t="n">
-        <v>947.0095916306215</v>
+        <v>970.0781937427375</v>
       </c>
       <c r="M41" t="n">
-        <v>970.0781937427043</v>
+        <v>970.0781937427375</v>
       </c>
       <c r="N41" t="n">
-        <v>970.0781937427043</v>
+        <v>970.0781937427375</v>
       </c>
       <c r="O41" t="n">
-        <v>1133.220000000031</v>
+        <v>1133.220000000064</v>
       </c>
       <c r="P41" t="n">
-        <v>1688.610000000036</v>
+        <v>1688.610000000073</v>
       </c>
       <c r="Q41" t="n">
-        <v>2244.00000000004</v>
+        <v>2244.000000000082</v>
       </c>
       <c r="R41" t="n">
-        <v>2244.00000000004</v>
+        <v>2244.000000000082</v>
       </c>
       <c r="S41" t="n">
-        <v>2124.74729509845</v>
+        <v>2124.747295098492</v>
       </c>
       <c r="T41" t="n">
-        <v>1886.798730233803</v>
+        <v>1886.798730233844</v>
       </c>
       <c r="U41" t="n">
-        <v>1579.617216538185</v>
+        <v>1579.617216538227</v>
       </c>
       <c r="V41" t="n">
-        <v>1291.888909298969</v>
+        <v>1291.888909299011</v>
       </c>
       <c r="W41" t="n">
-        <v>995.5520648737697</v>
+        <v>995.5520648738116</v>
       </c>
       <c r="X41" t="n">
-        <v>745.7724351155196</v>
+        <v>745.7724351155614</v>
       </c>
       <c r="Y41" t="n">
-        <v>577.7750283652101</v>
+        <v>577.775028365252</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1456.481572840302</v>
+        <v>838.102633442496</v>
       </c>
       <c r="C42" t="n">
-        <v>1413.774625941061</v>
+        <v>821.8400956187392</v>
       </c>
       <c r="D42" t="n">
-        <v>1062.322416953482</v>
+        <v>470.3878866311607</v>
       </c>
       <c r="E42" t="n">
-        <v>716.1889854161966</v>
+        <v>470.3878866311607</v>
       </c>
       <c r="F42" t="n">
-        <v>373.1220739637957</v>
+        <v>373.1559176934732</v>
       </c>
       <c r="G42" t="n">
-        <v>373.1220739637957</v>
+        <v>44.88000000000164</v>
       </c>
       <c r="H42" t="n">
-        <v>44.88000000000081</v>
+        <v>44.88000000000164</v>
       </c>
       <c r="I42" t="n">
-        <v>44.88000000000081</v>
+        <v>44.88000000000164</v>
       </c>
       <c r="J42" t="n">
-        <v>238.6476497036017</v>
+        <v>238.6476497036025</v>
       </c>
       <c r="K42" t="n">
-        <v>547.1588055149662</v>
+        <v>547.1588055149671</v>
       </c>
       <c r="L42" t="n">
-        <v>976.7579942888401</v>
+        <v>978.9474996573371</v>
       </c>
       <c r="M42" t="n">
-        <v>1250.062386031699</v>
+        <v>1252.251891400196</v>
       </c>
       <c r="N42" t="n">
-        <v>1575.521778846815</v>
+        <v>1577.711284215312</v>
       </c>
       <c r="O42" t="n">
-        <v>1990.370569304119</v>
+        <v>1990.370569304152</v>
       </c>
       <c r="P42" t="n">
-        <v>2244.00000000004</v>
+        <v>2244.000000000073</v>
       </c>
       <c r="Q42" t="n">
-        <v>2165.409242428182</v>
+        <v>2244.000000000073</v>
       </c>
       <c r="R42" t="n">
-        <v>2007.901232965706</v>
+        <v>1738.007142052749</v>
       </c>
       <c r="S42" t="n">
-        <v>1899.112982572636</v>
+        <v>1629.218891659679</v>
       </c>
       <c r="T42" t="n">
-        <v>1841.184355613836</v>
+        <v>1571.290264700879</v>
       </c>
       <c r="U42" t="n">
-        <v>1785.465915223329</v>
+        <v>1515.571824310372</v>
       </c>
       <c r="V42" t="n">
-        <v>1715.25312008038</v>
+        <v>1096.874180682574</v>
       </c>
       <c r="W42" t="n">
-        <v>1626.997420171462</v>
+        <v>1008.618480773656</v>
       </c>
       <c r="X42" t="n">
-        <v>1551.378491438747</v>
+        <v>932.9995520409414</v>
       </c>
       <c r="Y42" t="n">
-        <v>1496.437690664874</v>
+        <v>878.0587512670683</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>380.9243188631514</v>
+        <v>644.2685420878652</v>
       </c>
       <c r="C43" t="n">
-        <v>452.4763246815871</v>
+        <v>715.8205479063009</v>
       </c>
       <c r="D43" t="n">
-        <v>511.3454688065872</v>
+        <v>715.8205479063009</v>
       </c>
       <c r="E43" t="n">
-        <v>574.7243730180003</v>
+        <v>779.1994521177139</v>
       </c>
       <c r="F43" t="n">
-        <v>644.6353456099357</v>
+        <v>779.1994521177139</v>
       </c>
       <c r="G43" t="n">
-        <v>644.6353456099357</v>
+        <v>878.775498332468</v>
       </c>
       <c r="H43" t="n">
-        <v>765.2096740480218</v>
+        <v>936.1843379750608</v>
       </c>
       <c r="I43" t="n">
-        <v>950.5220159349244</v>
+        <v>936.1843379750608</v>
       </c>
       <c r="J43" t="n">
-        <v>1300.953015767704</v>
+        <v>1286.61533780784</v>
       </c>
       <c r="K43" t="n">
-        <v>1428.839800524244</v>
+        <v>1414.50212256438</v>
       </c>
       <c r="L43" t="n">
-        <v>1428.839800524244</v>
+        <v>1428.839800524245</v>
       </c>
       <c r="M43" t="n">
-        <v>1350.512142045099</v>
+        <v>1350.5121420451</v>
       </c>
       <c r="N43" t="n">
-        <v>1218.764525029488</v>
+        <v>1218.764525029489</v>
       </c>
       <c r="O43" t="n">
-        <v>1009.673228311158</v>
+        <v>1009.673228311159</v>
       </c>
       <c r="P43" t="n">
-        <v>740.2108382296063</v>
+        <v>740.2108382296071</v>
       </c>
       <c r="Q43" t="n">
-        <v>408.4509731532447</v>
+        <v>408.4509731532455</v>
       </c>
       <c r="R43" t="n">
-        <v>51.41391723587068</v>
+        <v>51.41391723587153</v>
       </c>
       <c r="S43" t="n">
-        <v>44.88000000000081</v>
+        <v>44.88000000000164</v>
       </c>
       <c r="T43" t="n">
-        <v>44.88000000000081</v>
+        <v>181.1525496506098</v>
       </c>
       <c r="U43" t="n">
-        <v>44.88000000000081</v>
+        <v>373.287532124962</v>
       </c>
       <c r="V43" t="n">
-        <v>149.2167622581496</v>
+        <v>373.287532124962</v>
       </c>
       <c r="W43" t="n">
-        <v>266.657680517827</v>
+        <v>490.7284503846394</v>
       </c>
       <c r="X43" t="n">
-        <v>266.657680517827</v>
+        <v>587.3092414088329</v>
       </c>
       <c r="Y43" t="n">
-        <v>323.6169811968592</v>
+        <v>644.2685420878652</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>444.0238605876121</v>
+        <v>439.3918839656817</v>
       </c>
       <c r="C44" t="n">
-        <v>338.4939835744869</v>
+        <v>333.8620069525565</v>
       </c>
       <c r="D44" t="n">
-        <v>272.4948363625174</v>
+        <v>267.862859740587</v>
       </c>
       <c r="E44" t="n">
-        <v>212.5319175677006</v>
+        <v>207.8999409457702</v>
       </c>
       <c r="F44" t="n">
-        <v>152.0373431151634</v>
+        <v>147.4053664932329</v>
       </c>
       <c r="G44" t="n">
-        <v>94.09552754683578</v>
+        <v>94.09552754683662</v>
       </c>
       <c r="H44" t="n">
-        <v>44.88000000000081</v>
+        <v>44.88000000000164</v>
       </c>
       <c r="I44" t="n">
-        <v>44.88000000000081</v>
+        <v>44.88000000000164</v>
       </c>
       <c r="J44" t="n">
-        <v>127.4002050736428</v>
+        <v>553.4018942939388</v>
       </c>
       <c r="K44" t="n">
-        <v>303.0717798977635</v>
+        <v>729.0734691180594</v>
       </c>
       <c r="L44" t="n">
-        <v>521.0079024103262</v>
+        <v>947.0095916306221</v>
       </c>
       <c r="M44" t="n">
-        <v>771.7692438362348</v>
+        <v>947.0095916306223</v>
       </c>
       <c r="N44" t="n">
-        <v>1327.159243836245</v>
+        <v>947.0095916306223</v>
       </c>
       <c r="O44" t="n">
-        <v>1490.301050093572</v>
+        <v>1502.399591630632</v>
       </c>
       <c r="P44" t="n">
-        <v>1688.610000000031</v>
+        <v>1700.708541537091</v>
       </c>
       <c r="Q44" t="n">
-        <v>2244.00000000004</v>
+        <v>2244.000000000082</v>
       </c>
       <c r="R44" t="n">
-        <v>2244.00000000004</v>
+        <v>2244.000000000082</v>
       </c>
       <c r="S44" t="n">
-        <v>2124.74729509845</v>
+        <v>2124.747295098492</v>
       </c>
       <c r="T44" t="n">
-        <v>1886.798730233803</v>
+        <v>1886.798730233844</v>
       </c>
       <c r="U44" t="n">
-        <v>1579.617216538185</v>
+        <v>1579.617216538227</v>
       </c>
       <c r="V44" t="n">
-        <v>1291.888909298969</v>
+        <v>1291.888909299011</v>
       </c>
       <c r="W44" t="n">
-        <v>995.5520648737697</v>
+        <v>995.5520648738116</v>
       </c>
       <c r="X44" t="n">
-        <v>745.7724351155196</v>
+        <v>745.7724351155614</v>
       </c>
       <c r="Y44" t="n">
-        <v>577.7750283652101</v>
+        <v>577.775028365252</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>411.0270273857636</v>
+        <v>758.7281783486225</v>
       </c>
       <c r="C45" t="n">
-        <v>394.7644895620067</v>
+        <v>742.4656405248656</v>
       </c>
       <c r="D45" t="n">
-        <v>238.2423680625408</v>
+        <v>391.0134315372871</v>
       </c>
       <c r="E45" t="n">
-        <v>238.2423680625408</v>
+        <v>44.88000000000164</v>
       </c>
       <c r="F45" t="n">
-        <v>238.2423680625408</v>
+        <v>44.88000000000164</v>
       </c>
       <c r="G45" t="n">
-        <v>238.2423680625408</v>
+        <v>44.88000000000164</v>
       </c>
       <c r="H45" t="n">
-        <v>238.2423680625408</v>
+        <v>44.88000000000164</v>
       </c>
       <c r="I45" t="n">
-        <v>44.88000000000081</v>
+        <v>44.88000000000164</v>
       </c>
       <c r="J45" t="n">
-        <v>238.6476497036017</v>
+        <v>238.6476497036025</v>
       </c>
       <c r="K45" t="n">
-        <v>547.1588055149662</v>
+        <v>547.1588055149671</v>
       </c>
       <c r="L45" t="n">
-        <v>978.9474996573362</v>
+        <v>978.9474996573371</v>
       </c>
       <c r="M45" t="n">
-        <v>1252.251891400195</v>
+        <v>1252.251891400196</v>
       </c>
       <c r="N45" t="n">
-        <v>1577.711284215311</v>
+        <v>1577.711284215312</v>
       </c>
       <c r="O45" t="n">
-        <v>1990.370569304126</v>
+        <v>1990.370569304161</v>
       </c>
       <c r="P45" t="n">
-        <v>2244.000000000048</v>
+        <v>2244.000000000082</v>
       </c>
       <c r="Q45" t="n">
-        <v>2165.409242428189</v>
+        <v>2244.000000000082</v>
       </c>
       <c r="R45" t="n">
-        <v>1659.416384480865</v>
+        <v>1738.007142052758</v>
       </c>
       <c r="S45" t="n">
-        <v>1550.628134087795</v>
+        <v>1629.218891659688</v>
       </c>
       <c r="T45" t="n">
-        <v>1492.699507128995</v>
+        <v>1571.290264700888</v>
       </c>
       <c r="U45" t="n">
-        <v>1088.49621825364</v>
+        <v>1515.571824310381</v>
       </c>
       <c r="V45" t="n">
-        <v>669.7985746258414</v>
+        <v>1096.874180682583</v>
       </c>
       <c r="W45" t="n">
-        <v>581.5428747169237</v>
+        <v>929.2440256797826</v>
       </c>
       <c r="X45" t="n">
-        <v>505.923945984209</v>
+        <v>853.6250969470678</v>
       </c>
       <c r="Y45" t="n">
-        <v>450.9831452103359</v>
+        <v>798.6842961731948</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>622.8982726483971</v>
+        <v>412.8601062556116</v>
       </c>
       <c r="C46" t="n">
-        <v>694.4502784668329</v>
+        <v>412.8601062556116</v>
       </c>
       <c r="D46" t="n">
-        <v>753.3194225918329</v>
+        <v>471.7292503806117</v>
       </c>
       <c r="E46" t="n">
-        <v>816.6983268032459</v>
+        <v>535.1081545920247</v>
       </c>
       <c r="F46" t="n">
-        <v>886.6092993951814</v>
+        <v>605.0191271839601</v>
       </c>
       <c r="G46" t="n">
-        <v>986.1853456099356</v>
+        <v>630.2976676500723</v>
       </c>
       <c r="H46" t="n">
-        <v>1106.759674048022</v>
+        <v>750.8719960881584</v>
       </c>
       <c r="I46" t="n">
-        <v>1292.072015934924</v>
+        <v>936.184337975061</v>
       </c>
       <c r="J46" t="n">
-        <v>1300.953015767704</v>
+        <v>1286.61533780784</v>
       </c>
       <c r="K46" t="n">
-        <v>1428.839800524244</v>
+        <v>1414.502122564381</v>
       </c>
       <c r="L46" t="n">
-        <v>1428.839800524244</v>
+        <v>1428.839800524245</v>
       </c>
       <c r="M46" t="n">
-        <v>1350.512142045099</v>
+        <v>1350.5121420451</v>
       </c>
       <c r="N46" t="n">
-        <v>1218.764525029488</v>
+        <v>1218.764525029489</v>
       </c>
       <c r="O46" t="n">
-        <v>1009.673228311158</v>
+        <v>1009.673228311159</v>
       </c>
       <c r="P46" t="n">
-        <v>740.2108382296063</v>
+        <v>740.2108382296071</v>
       </c>
       <c r="Q46" t="n">
-        <v>408.4509731532447</v>
+        <v>408.4509731532455</v>
       </c>
       <c r="R46" t="n">
-        <v>51.41391723587068</v>
+        <v>51.41391723587152</v>
       </c>
       <c r="S46" t="n">
-        <v>44.88000000000081</v>
+        <v>44.88000000000164</v>
       </c>
       <c r="T46" t="n">
-        <v>181.152549650609</v>
+        <v>181.1525496506098</v>
       </c>
       <c r="U46" t="n">
-        <v>303.7786238364816</v>
+        <v>181.1525496506098</v>
       </c>
       <c r="V46" t="n">
-        <v>448.1500167224276</v>
+        <v>181.1525496506098</v>
       </c>
       <c r="W46" t="n">
-        <v>565.590934982105</v>
+        <v>298.5934679102872</v>
       </c>
       <c r="X46" t="n">
-        <v>565.590934982105</v>
+        <v>298.5934679102872</v>
       </c>
       <c r="Y46" t="n">
-        <v>565.590934982105</v>
+        <v>355.5527685893194</v>
       </c>
     </row>
   </sheetData>
@@ -7967,19 +7967,19 @@
         <v>373.8993027275024</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>246.9608132511784</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>308.6565929648241</v>
       </c>
       <c r="M2" t="n">
-        <v>845.554996989051</v>
+        <v>471.5549969890509</v>
       </c>
       <c r="N2" t="n">
         <v>777.3653500296342</v>
       </c>
       <c r="O2" t="n">
-        <v>182.0990798101954</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>373.8993027275024</v>
+        <v>181.5167089435048</v>
       </c>
       <c r="K5" t="n">
-        <v>181.6174062160024</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -8222,7 +8222,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>128.1077446289929</v>
+        <v>502.1077446289929</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,28 +8438,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>373.8993027275024</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>321.3286984924623</v>
       </c>
       <c r="L8" t="n">
-        <v>181.6174062160024</v>
+        <v>308.6565929648241</v>
       </c>
       <c r="M8" t="n">
-        <v>471.5549969890509</v>
+        <v>845.554996989051</v>
       </c>
       <c r="N8" t="n">
-        <v>777.3653500296342</v>
+        <v>403.3653500296342</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4816735941929551</v>
+        <v>300.0130910804115</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>502.1077446289929</v>
+        <v>128.1077446289929</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8678,16 +8678,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>470.5539648241206</v>
+        <v>217.6794996645507</v>
       </c>
       <c r="L11" t="n">
-        <v>427.8625025125627</v>
+        <v>429.496904522613</v>
       </c>
       <c r="M11" t="n">
-        <v>690.3746745633521</v>
+        <v>300.0226402051314</v>
       </c>
       <c r="N11" t="n">
-        <v>228.3401037984784</v>
+        <v>878.0574203813931</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8696,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>22.18109136266131</v>
+        <v>22.615216990802</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8915,16 +8915,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>470.5539648241206</v>
+        <v>273.4426433857788</v>
       </c>
       <c r="L14" t="n">
-        <v>427.8625025125627</v>
+        <v>429.496904522613</v>
       </c>
       <c r="M14" t="n">
-        <v>690.3746745633521</v>
+        <v>300.0226402051314</v>
       </c>
       <c r="N14" t="n">
-        <v>228.3401037984784</v>
+        <v>229.057420381393</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -8933,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>22.18109136266131</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,25 +9149,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>470.5539648241206</v>
+        <v>471.5539648241206</v>
       </c>
       <c r="L17" t="n">
-        <v>427.8625025125627</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>690.3746745633521</v>
+        <v>453.8135802342526</v>
       </c>
       <c r="N17" t="n">
-        <v>228.3401037984784</v>
+        <v>877.3401037984784</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>448.6879293874151</v>
       </c>
       <c r="Q17" t="n">
         <v>22.18109136266131</v>
@@ -9389,16 +9389,16 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>470.5539648241206</v>
+        <v>471.5539648241206</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>428.8625025125627</v>
       </c>
       <c r="M20" t="n">
-        <v>947.3167457327697</v>
+        <v>299.3167457327696</v>
       </c>
       <c r="N20" t="n">
-        <v>829.5652717277806</v>
+        <v>457.9913832679015</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>22.18109136266131</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9626,16 +9626,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>213.6118936547034</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>427.8625025125628</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>299.3167457327696</v>
+        <v>350.0797559527193</v>
       </c>
       <c r="N23" t="n">
-        <v>876.3401037984784</v>
+        <v>877.3401037984784</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>22.18109136266131</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9863,25 +9863,25 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>470.5539648241239</v>
+        <v>471.5539648241206</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>428.8625025125627</v>
       </c>
       <c r="M26" t="n">
-        <v>947.3167457327734</v>
+        <v>299.3167457327696</v>
       </c>
       <c r="N26" t="n">
-        <v>829.5652717277867</v>
+        <v>228.3401037984784</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>229.651279469423</v>
       </c>
       <c r="Q26" t="n">
-        <v>22.18109136266131</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10100,25 +10100,25 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>470.5539648241239</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>947.3167457327729</v>
+        <v>496.4862664416901</v>
       </c>
       <c r="N29" t="n">
-        <v>829.5652717277871</v>
+        <v>228.3401037984784</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>484.2102967097708</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>448.6879293874151</v>
       </c>
       <c r="Q29" t="n">
-        <v>22.18109136266131</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10337,25 +10337,25 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>471.5539648241206</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>947.3167457327747</v>
+        <v>948.3167457327697</v>
       </c>
       <c r="N32" t="n">
-        <v>706.4482546449968</v>
+        <v>228.3401037984784</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>484.2102967097708</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>141.1555585417886</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10577,13 +10577,13 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>253.2942842686124</v>
+        <v>340.8625025125833</v>
       </c>
       <c r="M35" t="n">
-        <v>860.3167457327706</v>
+        <v>772.7485274888295</v>
       </c>
       <c r="N35" t="n">
-        <v>789.3401037984793</v>
+        <v>228.3401037984784</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>22.18109136266131</v>
+        <v>583.1810913626741</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10662,10 +10662,10 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N36" t="n">
-        <v>485.4085271713503</v>
+        <v>483.1969055870524</v>
       </c>
       <c r="O36" t="n">
-        <v>380.4701772165646</v>
+        <v>382.6817988009037</v>
       </c>
       <c r="P36" t="n">
         <v>219.1507118405495</v>
@@ -10808,25 +10808,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>383.5539648241307</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>860.3167457327725</v>
+        <v>487.4080673180646</v>
       </c>
       <c r="N38" t="n">
-        <v>659.0804232429592</v>
+        <v>228.3401037984784</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>396.21029670978</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>360.6879293874243</v>
       </c>
       <c r="Q38" t="n">
         <v>22.18109136266131</v>
@@ -10893,7 +10893,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L39" t="n">
-        <v>385.8777148754587</v>
+        <v>385.8777148754835</v>
       </c>
       <c r="M39" t="n">
         <v>471.6948204301074</v>
@@ -11045,16 +11045,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>383.5539648241412</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>70.05239005708165</v>
       </c>
       <c r="M41" t="n">
-        <v>322.6183640278027</v>
+        <v>299.3167457327696</v>
       </c>
       <c r="N41" t="n">
         <v>228.3401037984784</v>
@@ -11063,10 +11063,10 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>360.6879293874198</v>
+        <v>360.6879293874243</v>
       </c>
       <c r="Q41" t="n">
-        <v>583.1810913626659</v>
+        <v>583.1810913626705</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11130,7 +11130,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L42" t="n">
-        <v>385.8777148754587</v>
+        <v>388.0893364597981</v>
       </c>
       <c r="M42" t="n">
         <v>471.6948204301074</v>
@@ -11139,7 +11139,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O42" t="n">
-        <v>382.6817988009037</v>
+        <v>380.4701772165967</v>
       </c>
       <c r="P42" t="n">
         <v>219.1507118405495</v>
@@ -11282,7 +11282,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -11291,19 +11291,19 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>552.611030001364</v>
+        <v>299.3167457327696</v>
       </c>
       <c r="N44" t="n">
-        <v>789.3401037984884</v>
+        <v>228.3401037984784</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>396.2102967097802</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>583.1810913626714</v>
+        <v>570.9603423353801</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -11376,7 +11376,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O45" t="n">
-        <v>380.4701772165719</v>
+        <v>380.4701772166059</v>
       </c>
       <c r="P45" t="n">
         <v>219.1507118405495</v>
@@ -22527,7 +22527,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1.085115611857749e-12</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -23280,7 +23280,7 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.956056855791587</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -23475,7 +23475,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>2.95605685579163</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -23760,7 +23760,7 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.956056855791644</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -23949,7 +23949,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>2.95605685579163</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -24189,7 +24189,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.95605685576237</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -24471,7 +24471,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>2.956056855778627</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -24708,7 +24708,7 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>2.956056855778854</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
@@ -24900,7 +24900,7 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2.956056855742816</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -25119,7 +25119,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>4.585656855711932</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -25134,7 +25134,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>4.585656855752539</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -25374,7 +25374,7 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>4.585656855728182</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -25422,7 +25422,7 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>4.585656855743053</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
@@ -25608,10 +25608,10 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>4.585656855711939</v>
       </c>
       <c r="H41" t="n">
-        <v>4.585656855752568</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25830,7 +25830,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4.585656855752518</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -25845,7 +25845,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>4.585656855711992</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3245404.164969369</v>
+        <v>3245755.62594946</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4032367.751348666</v>
+        <v>4032866.276157333</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4819331.337727963</v>
+        <v>4819867.084365204</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5606294.924107256</v>
+        <v>5606977.734573073</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6393258.51048655</v>
+        <v>6394088.384780941</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7180222.096865843</v>
+        <v>7181199.034988809</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7967185.683245136</v>
+        <v>7968309.685196678</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8754149.269624436</v>
+        <v>8755420.335404553</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9532777.353395369</v>
+        <v>9533953.864023974</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>10319659.86717467</v>
+        <v>10320836.37780328</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>11106542.38095398</v>
+        <v>11107718.89158258</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11893424.89473328</v>
+        <v>11894601.40536189</v>
       </c>
     </row>
   </sheetData>
@@ -26269,7 +26269,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1416799.17037417</v>
+        <v>1416799.170374169</v>
       </c>
       <c r="C2" t="n">
         <v>1416799.170374169</v>
@@ -26278,40 +26278,40 @@
         <v>1416799.170374169</v>
       </c>
       <c r="E2" t="n">
-        <v>1416534.455482733</v>
+        <v>1416799.17037417</v>
       </c>
       <c r="F2" t="n">
-        <v>1416534.455482733</v>
+        <v>1416799.170374169</v>
       </c>
       <c r="G2" t="n">
-        <v>1416534.455482733</v>
+        <v>1416799.170374169</v>
       </c>
       <c r="H2" t="n">
-        <v>1416534.455482733</v>
+        <v>1416799.170374169</v>
       </c>
       <c r="I2" t="n">
-        <v>1416534.455482736</v>
+        <v>1416799.170374169</v>
       </c>
       <c r="J2" t="n">
-        <v>1416534.455482735</v>
+        <v>1416799.170374169</v>
       </c>
       <c r="K2" t="n">
-        <v>1416534.455482735</v>
+        <v>1416799.170374169</v>
       </c>
       <c r="L2" t="n">
-        <v>1416534.455482738</v>
+        <v>1416799.170374169</v>
       </c>
       <c r="M2" t="n">
-        <v>1416388.524802737</v>
+        <v>1416388.524802741</v>
       </c>
       <c r="N2" t="n">
-        <v>1416388.524802738</v>
+        <v>1416388.524802739</v>
       </c>
       <c r="O2" t="n">
-        <v>1416388.524802737</v>
+        <v>1416388.524802741</v>
       </c>
       <c r="P2" t="n">
-        <v>1416388.524802737</v>
+        <v>1416388.52480274</v>
       </c>
     </row>
     <row r="3">
@@ -26330,13 +26330,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>591148</v>
+        <v>590525</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>975</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -26345,7 +26345,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>388448.0000000012</v>
+        <v>388448</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26354,7 +26354,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>85024.0000000024</v>
+        <v>85024.00000000725</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>602166.8573620638</v>
+        <v>601967.7658514546</v>
       </c>
       <c r="C4" t="n">
-        <v>600158.4933044576</v>
+        <v>599959.4017938484</v>
       </c>
       <c r="D4" t="n">
-        <v>598147.4047756541</v>
+        <v>597948.3132650448</v>
       </c>
       <c r="E4" t="n">
-        <v>513949.0290844531</v>
+        <v>514058.4166568755</v>
       </c>
       <c r="F4" t="n">
-        <v>512264.4313324891</v>
+        <v>512373.4279872237</v>
       </c>
       <c r="G4" t="n">
-        <v>510577.5088988312</v>
+        <v>510436.7237234231</v>
       </c>
       <c r="H4" t="n">
-        <v>508888.2451130981</v>
+        <v>508747.6302445563</v>
       </c>
       <c r="I4" t="n">
-        <v>507196.6230877031</v>
+        <v>507056.1787637775</v>
       </c>
       <c r="J4" t="n">
-        <v>505502.6257137288</v>
+        <v>505362.3521738977</v>
       </c>
       <c r="K4" t="n">
-        <v>503806.235656723</v>
+        <v>503666.133142209</v>
       </c>
       <c r="L4" t="n">
-        <v>502107.4353523597</v>
+        <v>501967.5041061557</v>
       </c>
       <c r="M4" t="n">
-        <v>506489.4162279246</v>
+        <v>506308.9084534689</v>
       </c>
       <c r="N4" t="n">
-        <v>504723.3213042076</v>
+        <v>504542.8135297509</v>
       </c>
       <c r="O4" t="n">
-        <v>502954.6717247902</v>
+        <v>502774.1639503348</v>
       </c>
       <c r="P4" t="n">
-        <v>501183.4482814753</v>
+        <v>501002.9405070198</v>
       </c>
     </row>
     <row r="5">
@@ -26434,40 +26434,40 @@
         <v>58612.2</v>
       </c>
       <c r="E5" t="n">
-        <v>73949.149</v>
+        <v>73988.149</v>
       </c>
       <c r="F5" t="n">
-        <v>73949.149</v>
+        <v>73988.149</v>
       </c>
       <c r="G5" t="n">
-        <v>73949.149</v>
+        <v>74009.94899999999</v>
       </c>
       <c r="H5" t="n">
-        <v>73949.149</v>
+        <v>74009.94899999999</v>
       </c>
       <c r="I5" t="n">
-        <v>73949.149</v>
+        <v>74009.94899999999</v>
       </c>
       <c r="J5" t="n">
-        <v>73949.14900000021</v>
+        <v>74009.94899999999</v>
       </c>
       <c r="K5" t="n">
-        <v>73949.14900000021</v>
+        <v>74009.94899999999</v>
       </c>
       <c r="L5" t="n">
-        <v>73949.14900000021</v>
+        <v>74009.94899999999</v>
       </c>
       <c r="M5" t="n">
-        <v>70677.20500000061</v>
+        <v>70677.20500000124</v>
       </c>
       <c r="N5" t="n">
-        <v>70677.20500000061</v>
+        <v>70677.20500000124</v>
       </c>
       <c r="O5" t="n">
-        <v>70677.20500000061</v>
+        <v>70677.20500000124</v>
       </c>
       <c r="P5" t="n">
-        <v>70677.20500000061</v>
+        <v>70677.20500000124</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>523947.1130121059</v>
+        <v>524146.2045227144</v>
       </c>
       <c r="C6" t="n">
-        <v>758028.4770697117</v>
+        <v>758227.5685803205</v>
       </c>
       <c r="D6" t="n">
-        <v>760039.565598515</v>
+        <v>760238.6571091245</v>
       </c>
       <c r="E6" t="n">
-        <v>237488.2773982798</v>
+        <v>238227.6047172942</v>
       </c>
       <c r="F6" t="n">
-        <v>830320.8751502439</v>
+        <v>830437.5933869451</v>
       </c>
       <c r="G6" t="n">
-        <v>832007.797583902</v>
+        <v>831377.4976507464</v>
       </c>
       <c r="H6" t="n">
-        <v>833697.0613696354</v>
+        <v>834041.5911296131</v>
       </c>
       <c r="I6" t="n">
-        <v>835388.6833950328</v>
+        <v>835733.0426103915</v>
       </c>
       <c r="J6" t="n">
-        <v>448634.6807690044</v>
+        <v>448978.8692002718</v>
       </c>
       <c r="K6" t="n">
-        <v>838779.0708260114</v>
+        <v>839123.0882319602</v>
       </c>
       <c r="L6" t="n">
-        <v>840477.8711303778</v>
+        <v>840821.7172680136</v>
       </c>
       <c r="M6" t="n">
-        <v>754197.9035748098</v>
+        <v>754378.4113492637</v>
       </c>
       <c r="N6" t="n">
-        <v>840987.9984985294</v>
+        <v>841168.5062729869</v>
       </c>
       <c r="O6" t="n">
-        <v>585956.6480779458</v>
+        <v>586137.1558524047</v>
       </c>
       <c r="P6" t="n">
-        <v>844527.8715212609</v>
+        <v>844708.3792957192</v>
       </c>
     </row>
   </sheetData>
@@ -26816,10 +26816,10 @@
         <v>103</v>
       </c>
       <c r="E3" t="n">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F3" t="n">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G3" t="n">
         <v>347</v>
@@ -26868,40 +26868,40 @@
         <v>374</v>
       </c>
       <c r="E4" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F4" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="G4" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H4" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="I4" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="J4" t="n">
-        <v>648.0000000000033</v>
+        <v>649</v>
       </c>
       <c r="K4" t="n">
-        <v>648.0000000000033</v>
+        <v>649</v>
       </c>
       <c r="L4" t="n">
-        <v>648.0000000000033</v>
+        <v>649</v>
       </c>
       <c r="M4" t="n">
-        <v>561.0000000000101</v>
+        <v>561.0000000000206</v>
       </c>
       <c r="N4" t="n">
-        <v>561.0000000000101</v>
+        <v>561.0000000000206</v>
       </c>
       <c r="O4" t="n">
-        <v>561.0000000000101</v>
+        <v>561.0000000000206</v>
       </c>
       <c r="P4" t="n">
-        <v>561.0000000000101</v>
+        <v>561.0000000000206</v>
       </c>
     </row>
   </sheetData>
@@ -26999,10 +26999,10 @@
         <v>321</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>24</v>
@@ -27033,13 +27033,13 @@
         <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>-0</v>
@@ -27085,7 +27085,7 @@
         <v>-0</v>
       </c>
       <c r="E4" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F4" t="n">
         <v>-0</v>
@@ -27109,7 +27109,7 @@
         <v>-0</v>
       </c>
       <c r="M4" t="n">
-        <v>187</v>
+        <v>187.0000000000135</v>
       </c>
       <c r="N4" t="n">
         <v>-0</v>
@@ -27326,7 +27326,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -27451,10 +27451,10 @@
         <v>400</v>
       </c>
       <c r="H2" t="n">
-        <v>398.0465935392086</v>
+        <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>134.1177124465037</v>
+        <v>132.1643059857112</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27527,10 +27527,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>167.6238938717235</v>
       </c>
       <c r="H3" t="n">
-        <v>330.0284079411381</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -27569,16 +27569,16 @@
         <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>26.19578428848864</v>
+        <v>400</v>
       </c>
       <c r="V3" t="n">
         <v>400</v>
       </c>
       <c r="W3" t="n">
+        <v>58.37314290982852</v>
+      </c>
+      <c r="X3" t="n">
         <v>400</v>
-      </c>
-      <c r="X3" t="n">
-        <v>269.7728445519253</v>
       </c>
       <c r="Y3" t="n">
         <v>399.3913927661343</v>
@@ -27591,34 +27591,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C4" t="n">
         <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
         <v>244.858135136612</v>
       </c>
       <c r="H4" t="n">
-        <v>227.1197490524383</v>
+        <v>400</v>
       </c>
       <c r="I4" t="n">
+        <v>278.7141475692162</v>
+      </c>
+      <c r="J4" t="n">
+        <v>22.13729309820286</v>
+      </c>
+      <c r="K4" t="n">
         <v>400</v>
-      </c>
-      <c r="J4" t="n">
-        <v>191.5240822578404</v>
-      </c>
-      <c r="K4" t="n">
-        <v>266.941429538848</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27642,16 +27642,16 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>359.1365780635112</v>
+        <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>400</v>
+        <v>209.2309599488807</v>
       </c>
       <c r="U4" t="n">
-        <v>400</v>
+        <v>150.9482601269169</v>
       </c>
       <c r="V4" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
         <v>400</v>
@@ -27660,7 +27660,7 @@
         <v>400</v>
       </c>
       <c r="Y4" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5">
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>134.1177124465037</v>
+        <v>132.1643059857123</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27718,7 +27718,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>222.9148456338345</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S5" t="n">
         <v>400</v>
@@ -27758,7 +27758,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>144.7989632036872</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27806,19 +27806,19 @@
         <v>400</v>
       </c>
       <c r="U6" t="n">
-        <v>257.2979670242288</v>
+        <v>400</v>
       </c>
       <c r="V6" t="n">
-        <v>400</v>
+        <v>40.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>58.37314290982852</v>
+        <v>388.6315031681369</v>
       </c>
       <c r="X6" t="n">
         <v>400</v>
       </c>
       <c r="Y6" t="n">
-        <v>25.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="7">
@@ -27837,28 +27837,28 @@
         <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
         <v>400</v>
       </c>
       <c r="H7" t="n">
+        <v>264.655340595834</v>
+      </c>
+      <c r="I7" t="n">
         <v>400</v>
-      </c>
-      <c r="I7" t="n">
-        <v>171.047816275856</v>
       </c>
       <c r="J7" t="n">
         <v>22.13729309820286</v>
       </c>
       <c r="K7" t="n">
-        <v>266.941429538848</v>
+        <v>400</v>
       </c>
       <c r="L7" t="n">
-        <v>395.9334970102382</v>
+        <v>400</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27882,16 +27882,16 @@
         <v>359.1365780635112</v>
       </c>
       <c r="T7" t="n">
-        <v>209.2309599488807</v>
+        <v>400</v>
       </c>
       <c r="U7" t="n">
         <v>150.9482601269169</v>
       </c>
       <c r="V7" t="n">
-        <v>202.4085186816356</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
         <v>400</v>
@@ -27925,7 +27925,7 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>400</v>
+        <v>398.0465935392086</v>
       </c>
       <c r="I8" t="n">
         <v>134.1177124465037</v>
@@ -27955,7 +27955,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>222.9148456338345</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S8" t="n">
         <v>400</v>
@@ -27992,10 +27992,10 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
@@ -28004,7 +28004,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>330.0284079411381</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>209.4985557026693</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28043,7 +28043,7 @@
         <v>400</v>
       </c>
       <c r="U9" t="n">
-        <v>34.4077600354471</v>
+        <v>214.3716150971082</v>
       </c>
       <c r="V9" t="n">
         <v>400</v>
@@ -28065,31 +28065,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C10" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D10" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
         <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>400</v>
+        <v>244.858135136612</v>
       </c>
       <c r="H10" t="n">
-        <v>400</v>
+        <v>227.1197490524383</v>
       </c>
       <c r="I10" t="n">
-        <v>400</v>
+        <v>171.047816275856</v>
       </c>
       <c r="J10" t="n">
-        <v>98.01643627028469</v>
+        <v>396.1372930982029</v>
       </c>
       <c r="K10" t="n">
         <v>400</v>
@@ -28119,22 +28119,22 @@
         <v>359.1365780635112</v>
       </c>
       <c r="T10" t="n">
-        <v>209.2309599488807</v>
+        <v>400</v>
       </c>
       <c r="U10" t="n">
         <v>150.9482601269169</v>
       </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>302.1803511129169</v>
       </c>
       <c r="W10" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X10" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -28165,7 +28165,7 @@
         <v>321</v>
       </c>
       <c r="I11" t="n">
-        <v>96.3013908384635</v>
+        <v>95.68635121184303</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28192,7 +28192,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>163.2515083760331</v>
+        <v>163.5040360142241</v>
       </c>
       <c r="S11" t="n">
         <v>321</v>
@@ -28235,16 +28235,16 @@
         <v>321</v>
       </c>
       <c r="F12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>137.8407332208564</v>
+        <v>321</v>
       </c>
       <c r="H12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>191.4287443819146</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -28268,7 +28268,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>77.80484999613995</v>
+        <v>78.07941603387582</v>
       </c>
       <c r="R12" t="n">
         <v>321</v>
@@ -28277,22 +28277,22 @@
         <v>321</v>
       </c>
       <c r="T12" t="n">
-        <v>321</v>
+        <v>11.53268450560142</v>
       </c>
       <c r="U12" t="n">
         <v>321</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W12" t="n">
         <v>321</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13">
@@ -28326,7 +28326,7 @@
         <v>321</v>
       </c>
       <c r="J13" t="n">
-        <v>315.8198010595347</v>
+        <v>321</v>
       </c>
       <c r="K13" t="n">
         <v>321</v>
@@ -28356,7 +28356,7 @@
         <v>321</v>
       </c>
       <c r="T13" t="n">
-        <v>321</v>
+        <v>317.8316225849397</v>
       </c>
       <c r="U13" t="n">
         <v>321</v>
@@ -28402,7 +28402,7 @@
         <v>321</v>
       </c>
       <c r="I14" t="n">
-        <v>96.3013908384635</v>
+        <v>95.686351211843</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28429,7 +28429,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>163.2515083760331</v>
+        <v>163.5040360142241</v>
       </c>
       <c r="S14" t="n">
         <v>321</v>
@@ -28463,25 +28463,25 @@
         <v>321</v>
       </c>
       <c r="C15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>321</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G15" t="n">
-        <v>8.269477602771019</v>
+        <v>321</v>
       </c>
       <c r="H15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>191.5028009856882</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -28505,7 +28505,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>77.80484999613995</v>
+        <v>78.07941603387582</v>
       </c>
       <c r="R15" t="n">
         <v>321</v>
@@ -28517,10 +28517,10 @@
         <v>321</v>
       </c>
       <c r="U15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>321</v>
+        <v>141.0298835199133</v>
       </c>
       <c r="W15" t="n">
         <v>321</v>
@@ -28551,7 +28551,7 @@
         <v>321</v>
       </c>
       <c r="F16" t="n">
-        <v>321</v>
+        <v>317.8316225849397</v>
       </c>
       <c r="G16" t="n">
         <v>321</v>
@@ -28596,7 +28596,7 @@
         <v>321</v>
       </c>
       <c r="U16" t="n">
-        <v>315.8198010595348</v>
+        <v>321</v>
       </c>
       <c r="V16" t="n">
         <v>321</v>
@@ -28636,7 +28636,7 @@
         <v>321</v>
       </c>
       <c r="H17" t="n">
-        <v>321</v>
+        <v>320.0752568557916</v>
       </c>
       <c r="I17" t="n">
         <v>96.3013908384635</v>
@@ -28700,19 +28700,19 @@
         <v>321</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F18" t="n">
-        <v>215.6455832169961</v>
+        <v>137.8407332208562</v>
       </c>
       <c r="G18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>321</v>
@@ -28742,7 +28742,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R18" t="n">
         <v>321</v>
@@ -28757,13 +28757,13 @@
         <v>321</v>
       </c>
       <c r="V18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>321</v>
       </c>
       <c r="X18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>321</v>
@@ -28785,7 +28785,7 @@
         <v>321</v>
       </c>
       <c r="E19" t="n">
-        <v>321</v>
+        <v>315.8198010595347</v>
       </c>
       <c r="F19" t="n">
         <v>321</v>
@@ -28800,7 +28800,7 @@
         <v>321</v>
       </c>
       <c r="J19" t="n">
-        <v>315.8198010595347</v>
+        <v>321</v>
       </c>
       <c r="K19" t="n">
         <v>321</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>163.2515083760331</v>
+        <v>162.3267652318248</v>
       </c>
       <c r="S20" t="n">
         <v>321</v>
@@ -28934,14 +28934,14 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>321</v>
+      </c>
+      <c r="C21" t="n">
+        <v>321</v>
+      </c>
+      <c r="D21" t="n">
         <v>137.8407332208562</v>
       </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
       <c r="E21" t="n">
         <v>321</v>
       </c>
@@ -28949,7 +28949,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>321</v>
@@ -28988,7 +28988,7 @@
         <v>321</v>
       </c>
       <c r="T21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
         <v>321</v>
@@ -29037,7 +29037,7 @@
         <v>321</v>
       </c>
       <c r="J22" t="n">
-        <v>315.8198010595347</v>
+        <v>321</v>
       </c>
       <c r="K22" t="n">
         <v>321</v>
@@ -29082,7 +29082,7 @@
         <v>321</v>
       </c>
       <c r="Y22" t="n">
-        <v>321</v>
+        <v>315.8198010595348</v>
       </c>
     </row>
     <row r="23">
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>163.251508376063</v>
+        <v>162.3267652318248</v>
       </c>
       <c r="S23" t="n">
         <v>321</v>
@@ -29174,22 +29174,22 @@
         <v>321</v>
       </c>
       <c r="C24" t="n">
-        <v>137.8407332208562</v>
+        <v>321</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>215.6455832169962</v>
       </c>
       <c r="G24" t="n">
         <v>321</v>
       </c>
       <c r="H24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>191.4287443819146</v>
@@ -29216,13 +29216,13 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>77.80484999613995</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>321</v>
       </c>
       <c r="S24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
         <v>321</v>
@@ -29240,7 +29240,7 @@
         <v>321</v>
       </c>
       <c r="Y24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -29262,7 +29262,7 @@
         <v>321</v>
       </c>
       <c r="F25" t="n">
-        <v>321</v>
+        <v>315.8198010595347</v>
       </c>
       <c r="G25" t="n">
         <v>321</v>
@@ -29274,7 +29274,7 @@
         <v>321</v>
       </c>
       <c r="J25" t="n">
-        <v>315.8198010595347</v>
+        <v>321</v>
       </c>
       <c r="K25" t="n">
         <v>321</v>
@@ -29377,7 +29377,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>163.2515083760331</v>
+        <v>162.3267652318248</v>
       </c>
       <c r="S26" t="n">
         <v>321</v>
@@ -29408,7 +29408,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C27" t="n">
         <v>321</v>
@@ -29426,10 +29426,10 @@
         <v>321</v>
       </c>
       <c r="H27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>191.4287443819146</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -29453,7 +29453,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R27" t="n">
         <v>321</v>
@@ -29462,19 +29462,19 @@
         <v>321</v>
       </c>
       <c r="T27" t="n">
-        <v>321</v>
+        <v>137.8407332208565</v>
       </c>
       <c r="U27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>86.07432759891088</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
         <v>321</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y27" t="n">
         <v>321</v>
@@ -29505,7 +29505,7 @@
         <v>321</v>
       </c>
       <c r="H28" t="n">
-        <v>321</v>
+        <v>315.8198010595348</v>
       </c>
       <c r="I28" t="n">
         <v>321</v>
@@ -29556,7 +29556,7 @@
         <v>321</v>
       </c>
       <c r="Y28" t="n">
-        <v>315.8198010595348</v>
+        <v>321</v>
       </c>
     </row>
     <row r="29">
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>163.2515083760331</v>
+        <v>162.3267652318248</v>
       </c>
       <c r="S29" t="n">
         <v>321</v>
@@ -29645,16 +29645,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>215.6455832169964</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F30" t="n">
         <v>321</v>
@@ -29663,7 +29663,7 @@
         <v>321</v>
       </c>
       <c r="H30" t="n">
-        <v>321</v>
+        <v>137.8407332208564</v>
       </c>
       <c r="I30" t="n">
         <v>191.4287443819146</v>
@@ -29690,7 +29690,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R30" t="n">
         <v>321</v>
@@ -29714,7 +29714,7 @@
         <v>321</v>
       </c>
       <c r="Y30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -29748,7 +29748,7 @@
         <v>321</v>
       </c>
       <c r="J31" t="n">
-        <v>315.8198010595349</v>
+        <v>315.8198010595347</v>
       </c>
       <c r="K31" t="n">
         <v>321</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>163.2515083760699</v>
+        <v>162.3267652318248</v>
       </c>
       <c r="S32" t="n">
         <v>321</v>
@@ -29885,7 +29885,7 @@
         <v>321</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D33" t="n">
         <v>321</v>
@@ -29894,16 +29894,16 @@
         <v>321</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>8.269477602770905</v>
+        <v>191.4287443819146</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29936,10 +29936,10 @@
         <v>321</v>
       </c>
       <c r="T33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>321</v>
+        <v>137.8407332208563</v>
       </c>
       <c r="V33" t="n">
         <v>321</v>
@@ -29948,7 +29948,7 @@
         <v>321</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y33" t="n">
         <v>321</v>
@@ -30122,13 +30122,13 @@
         <v>345</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>109.8121789549352</v>
       </c>
       <c r="D36" t="n">
-        <v>338.8603817911135</v>
+        <v>345</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -30140,7 +30140,7 @@
         <v>324.959653224157</v>
       </c>
       <c r="I36" t="n">
-        <v>191.4287443819146</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30164,7 +30164,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R36" t="n">
         <v>345</v>
@@ -30185,7 +30185,7 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
         <v>345</v>
@@ -30198,7 +30198,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>345</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C37" t="n">
         <v>345</v>
@@ -30207,10 +30207,10 @@
         <v>345</v>
       </c>
       <c r="E37" t="n">
-        <v>345</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F37" t="n">
-        <v>345</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G37" t="n">
         <v>345</v>
@@ -30219,10 +30219,10 @@
         <v>345</v>
       </c>
       <c r="I37" t="n">
+        <v>301.9046572683323</v>
+      </c>
+      <c r="J37" t="n">
         <v>345</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
       </c>
       <c r="K37" t="n">
         <v>345</v>
@@ -30252,10 +30252,10 @@
         <v>345</v>
       </c>
       <c r="T37" t="n">
-        <v>207.3509599488807</v>
+        <v>345</v>
       </c>
       <c r="U37" t="n">
-        <v>242.8645168677156</v>
+        <v>150.9242601269169</v>
       </c>
       <c r="V37" t="n">
         <v>345</v>
@@ -30264,10 +30264,10 @@
         <v>345</v>
       </c>
       <c r="X37" t="n">
-        <v>345</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y37" t="n">
-        <v>345</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="38">
@@ -30298,7 +30298,7 @@
         <v>345</v>
       </c>
       <c r="I38" t="n">
-        <v>96.3013908384734</v>
+        <v>96.3013908384635</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>163.2515083760331</v>
+        <v>163.2515083760167</v>
       </c>
       <c r="S38" t="n">
         <v>345</v>
@@ -30356,22 +30356,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>261.0555317949739</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>324.9931585165368</v>
+        <v>243.3765930895737</v>
       </c>
       <c r="H39" t="n">
         <v>324.959653224157</v>
@@ -30413,10 +30413,10 @@
         <v>345</v>
       </c>
       <c r="U39" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
         <v>345</v>
@@ -30425,7 +30425,7 @@
         <v>345</v>
       </c>
       <c r="Y39" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -30435,10 +30435,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>345</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C40" t="n">
-        <v>345</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D40" t="n">
         <v>345</v>
@@ -30447,7 +30447,7 @@
         <v>345</v>
       </c>
       <c r="F40" t="n">
-        <v>345</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G40" t="n">
         <v>345</v>
@@ -30456,16 +30456,16 @@
         <v>345</v>
       </c>
       <c r="I40" t="n">
-        <v>157.815816275856</v>
+        <v>345</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="K40" t="n">
+        <v>331.2311510486423</v>
+      </c>
+      <c r="L40" t="n">
         <v>345</v>
-      </c>
-      <c r="L40" t="n">
-        <v>330.5174970102382</v>
       </c>
       <c r="M40" t="n">
         <v>345</v>
@@ -30492,19 +30492,19 @@
         <v>345</v>
       </c>
       <c r="U40" t="n">
-        <v>306.8821635305026</v>
+        <v>150.9242601269169</v>
       </c>
       <c r="V40" t="n">
         <v>345</v>
       </c>
       <c r="W40" t="n">
-        <v>345</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X40" t="n">
         <v>345</v>
       </c>
       <c r="Y40" t="n">
-        <v>345</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="41">
@@ -30596,22 +30596,22 @@
         <v>345</v>
       </c>
       <c r="C42" t="n">
-        <v>318.8200350152704</v>
+        <v>345</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>243.3765930895662</v>
       </c>
       <c r="G42" t="n">
-        <v>324.9931585165368</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>324.959653224157</v>
       </c>
       <c r="I42" t="n">
         <v>191.4287443819146</v>
@@ -30638,10 +30638,10 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R42" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>345</v>
@@ -30653,7 +30653,7 @@
         <v>345</v>
       </c>
       <c r="V42" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
         <v>345</v>
@@ -30672,28 +30672,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>345</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C43" t="n">
         <v>345</v>
       </c>
       <c r="D43" t="n">
-        <v>345</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E43" t="n">
         <v>345</v>
       </c>
       <c r="F43" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G43" t="n">
         <v>345</v>
       </c>
-      <c r="G43" t="n">
-        <v>244.418135136612</v>
-      </c>
       <c r="H43" t="n">
-        <v>345</v>
+        <v>281.1964759641481</v>
       </c>
       <c r="I43" t="n">
-        <v>345</v>
+        <v>157.815816275856</v>
       </c>
       <c r="J43" t="n">
         <v>345</v>
@@ -30702,7 +30702,7 @@
         <v>345</v>
       </c>
       <c r="L43" t="n">
-        <v>330.5174970102382</v>
+        <v>345</v>
       </c>
       <c r="M43" t="n">
         <v>345</v>
@@ -30726,19 +30726,19 @@
         <v>345</v>
       </c>
       <c r="T43" t="n">
-        <v>207.3509599488807</v>
+        <v>345</v>
       </c>
       <c r="U43" t="n">
-        <v>150.9242601269169</v>
+        <v>345</v>
       </c>
       <c r="V43" t="n">
-        <v>304.5609791638412</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W43" t="n">
         <v>345</v>
       </c>
       <c r="X43" t="n">
-        <v>247.4436454301076</v>
+        <v>345</v>
       </c>
       <c r="Y43" t="n">
         <v>345</v>
@@ -30836,10 +30836,10 @@
         <v>345</v>
       </c>
       <c r="D45" t="n">
-        <v>192.9807866132314</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>339.6362423378769</v>
@@ -30851,7 +30851,7 @@
         <v>324.959653224157</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>191.4287443819146</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -30875,7 +30875,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -30887,13 +30887,13 @@
         <v>345</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>345</v>
+        <v>266.4192894570563</v>
       </c>
       <c r="X45" t="n">
         <v>345</v>
@@ -30912,7 +30912,7 @@
         <v>345</v>
       </c>
       <c r="C46" t="n">
-        <v>345</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D46" t="n">
         <v>345</v>
@@ -30924,7 +30924,7 @@
         <v>345</v>
       </c>
       <c r="G46" t="n">
-        <v>345</v>
+        <v>269.9520143953112</v>
       </c>
       <c r="H46" t="n">
         <v>345</v>
@@ -30933,13 +30933,13 @@
         <v>345</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="K46" t="n">
         <v>345</v>
       </c>
       <c r="L46" t="n">
-        <v>330.5174970102382</v>
+        <v>345</v>
       </c>
       <c r="M46" t="n">
         <v>345</v>
@@ -30966,10 +30966,10 @@
         <v>345</v>
       </c>
       <c r="U46" t="n">
-        <v>274.7889815267883</v>
+        <v>150.9242601269169</v>
       </c>
       <c r="V46" t="n">
-        <v>345</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W46" t="n">
         <v>345</v>
@@ -30978,7 +30978,7 @@
         <v>247.4436454301076</v>
       </c>
       <c r="Y46" t="n">
-        <v>287.4653528494624</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -31802,49 +31802,49 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.394974874371858</v>
+        <v>1.390954773869346</v>
       </c>
       <c r="H11" t="n">
-        <v>14.2862864321608</v>
+        <v>14.24511557788944</v>
       </c>
       <c r="I11" t="n">
-        <v>53.77976884422112</v>
+        <v>53.624783919598</v>
       </c>
       <c r="J11" t="n">
-        <v>118.3967487437186</v>
+        <v>118.0555477386935</v>
       </c>
       <c r="K11" t="n">
-        <v>177.4460351758794</v>
+        <v>176.9346633165829</v>
       </c>
       <c r="L11" t="n">
-        <v>220.1374974874372</v>
+        <v>219.5030954773869</v>
       </c>
       <c r="M11" t="n">
-        <v>244.9453819095477</v>
+        <v>244.2394874371859</v>
       </c>
       <c r="N11" t="n">
-        <v>248.9088542713568</v>
+        <v>248.1915376884422</v>
       </c>
       <c r="O11" t="n">
-        <v>235.0375728643216</v>
+        <v>234.3602311557789</v>
       </c>
       <c r="P11" t="n">
-        <v>200.5991306532663</v>
+        <v>200.0210351758794</v>
       </c>
       <c r="Q11" t="n">
-        <v>150.6415929648241</v>
+        <v>150.2074673366834</v>
       </c>
       <c r="R11" t="n">
-        <v>87.62709045226131</v>
+        <v>87.37456281407036</v>
       </c>
       <c r="S11" t="n">
-        <v>31.78798994974875</v>
+        <v>31.69638190954775</v>
       </c>
       <c r="T11" t="n">
-        <v>6.106502512562813</v>
+        <v>6.088904522613064</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1115979899497486</v>
+        <v>0.1112763819095476</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -31881,49 +31881,49 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7463773584905661</v>
+        <v>0.7442264150943396</v>
       </c>
       <c r="H12" t="n">
-        <v>7.208433962264152</v>
+        <v>7.187660377358492</v>
       </c>
       <c r="I12" t="n">
-        <v>25.69764150943397</v>
+        <v>25.62358490566038</v>
       </c>
       <c r="J12" t="n">
-        <v>70.5162924528302</v>
+        <v>70.31307547169813</v>
       </c>
       <c r="K12" t="n">
-        <v>120.5235754716981</v>
+        <v>120.1762452830189</v>
       </c>
       <c r="L12" t="n">
-        <v>162.058820754717</v>
+        <v>161.5917924528302</v>
       </c>
       <c r="M12" t="n">
-        <v>189.115</v>
+        <v>188.57</v>
       </c>
       <c r="N12" t="n">
-        <v>194.1203113207547</v>
+        <v>193.5608867924528</v>
       </c>
       <c r="O12" t="n">
-        <v>177.5821603773585</v>
+        <v>177.0703962264151</v>
       </c>
       <c r="P12" t="n">
-        <v>142.5253396226415</v>
+        <v>142.1146037735849</v>
       </c>
       <c r="Q12" t="n">
-        <v>95.27441509433963</v>
+        <v>94.99984905660378</v>
       </c>
       <c r="R12" t="n">
-        <v>46.34086792452832</v>
+        <v>46.207320754717</v>
       </c>
       <c r="S12" t="n">
-        <v>13.86363207547169</v>
+        <v>13.82367924528301</v>
       </c>
       <c r="T12" t="n">
-        <v>3.008424528301886</v>
+        <v>2.999754716981131</v>
       </c>
       <c r="U12" t="n">
-        <v>0.04910377358490568</v>
+        <v>0.04896226415094342</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -31960,49 +31960,49 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6257377049180327</v>
+        <v>0.6239344262295081</v>
       </c>
       <c r="H13" t="n">
-        <v>5.563377049180331</v>
+        <v>5.547344262295085</v>
       </c>
       <c r="I13" t="n">
-        <v>18.8176393442623</v>
+        <v>18.76340983606558</v>
       </c>
       <c r="J13" t="n">
-        <v>44.23965573770491</v>
+        <v>44.11216393442622</v>
       </c>
       <c r="K13" t="n">
-        <v>72.69934426229506</v>
+        <v>72.48983606557374</v>
       </c>
       <c r="L13" t="n">
-        <v>93.03013114754098</v>
+        <v>92.76203278688526</v>
       </c>
       <c r="M13" t="n">
-        <v>98.0872295081967</v>
+        <v>97.80455737704916</v>
       </c>
       <c r="N13" t="n">
-        <v>95.75493442622957</v>
+        <v>95.47898360655743</v>
       </c>
       <c r="O13" t="n">
-        <v>88.44518032786888</v>
+        <v>88.19029508196724</v>
       </c>
       <c r="P13" t="n">
-        <v>75.68013114754095</v>
+        <v>75.4620327868852</v>
       </c>
       <c r="Q13" t="n">
-        <v>52.397</v>
+        <v>52.246</v>
       </c>
       <c r="R13" t="n">
-        <v>28.13544262295081</v>
+        <v>28.0543606557377</v>
       </c>
       <c r="S13" t="n">
-        <v>10.90490163934426</v>
+        <v>10.87347540983606</v>
       </c>
       <c r="T13" t="n">
-        <v>2.673606557377048</v>
+        <v>2.665901639344261</v>
       </c>
       <c r="U13" t="n">
-        <v>0.03413114754098364</v>
+        <v>0.03403278688524593</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -32039,49 +32039,49 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.394974874371858</v>
+        <v>1.390954773869346</v>
       </c>
       <c r="H14" t="n">
-        <v>14.2862864321608</v>
+        <v>14.24511557788944</v>
       </c>
       <c r="I14" t="n">
-        <v>53.77976884422112</v>
+        <v>53.624783919598</v>
       </c>
       <c r="J14" t="n">
-        <v>118.3967487437186</v>
+        <v>118.0555477386935</v>
       </c>
       <c r="K14" t="n">
-        <v>177.4460351758794</v>
+        <v>176.9346633165829</v>
       </c>
       <c r="L14" t="n">
-        <v>220.1374974874372</v>
+        <v>219.5030954773869</v>
       </c>
       <c r="M14" t="n">
-        <v>244.9453819095477</v>
+        <v>244.2394874371859</v>
       </c>
       <c r="N14" t="n">
-        <v>248.9088542713568</v>
+        <v>248.1915376884422</v>
       </c>
       <c r="O14" t="n">
-        <v>235.0375728643216</v>
+        <v>234.3602311557789</v>
       </c>
       <c r="P14" t="n">
-        <v>200.5991306532663</v>
+        <v>200.0210351758794</v>
       </c>
       <c r="Q14" t="n">
-        <v>150.6415929648241</v>
+        <v>150.2074673366834</v>
       </c>
       <c r="R14" t="n">
-        <v>87.62709045226131</v>
+        <v>87.37456281407036</v>
       </c>
       <c r="S14" t="n">
-        <v>31.78798994974875</v>
+        <v>31.69638190954775</v>
       </c>
       <c r="T14" t="n">
-        <v>6.106502512562813</v>
+        <v>6.088904522613064</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1115979899497486</v>
+        <v>0.1112763819095476</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -32118,49 +32118,49 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7463773584905661</v>
+        <v>0.7442264150943396</v>
       </c>
       <c r="H15" t="n">
-        <v>7.208433962264152</v>
+        <v>7.187660377358492</v>
       </c>
       <c r="I15" t="n">
-        <v>25.69764150943397</v>
+        <v>25.62358490566038</v>
       </c>
       <c r="J15" t="n">
-        <v>70.5162924528302</v>
+        <v>70.31307547169813</v>
       </c>
       <c r="K15" t="n">
-        <v>120.5235754716981</v>
+        <v>120.1762452830189</v>
       </c>
       <c r="L15" t="n">
-        <v>162.058820754717</v>
+        <v>161.5917924528302</v>
       </c>
       <c r="M15" t="n">
-        <v>189.115</v>
+        <v>188.57</v>
       </c>
       <c r="N15" t="n">
-        <v>194.1203113207547</v>
+        <v>193.5608867924528</v>
       </c>
       <c r="O15" t="n">
-        <v>177.5821603773585</v>
+        <v>177.0703962264151</v>
       </c>
       <c r="P15" t="n">
-        <v>142.5253396226415</v>
+        <v>142.1146037735849</v>
       </c>
       <c r="Q15" t="n">
-        <v>95.27441509433963</v>
+        <v>94.99984905660378</v>
       </c>
       <c r="R15" t="n">
-        <v>46.34086792452832</v>
+        <v>46.207320754717</v>
       </c>
       <c r="S15" t="n">
-        <v>13.86363207547169</v>
+        <v>13.82367924528301</v>
       </c>
       <c r="T15" t="n">
-        <v>3.008424528301886</v>
+        <v>2.999754716981131</v>
       </c>
       <c r="U15" t="n">
-        <v>0.04910377358490568</v>
+        <v>0.04896226415094342</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -32197,49 +32197,49 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6257377049180327</v>
+        <v>0.6239344262295081</v>
       </c>
       <c r="H16" t="n">
-        <v>5.563377049180331</v>
+        <v>5.547344262295085</v>
       </c>
       <c r="I16" t="n">
-        <v>18.8176393442623</v>
+        <v>18.76340983606558</v>
       </c>
       <c r="J16" t="n">
-        <v>44.23965573770491</v>
+        <v>44.11216393442622</v>
       </c>
       <c r="K16" t="n">
-        <v>72.69934426229506</v>
+        <v>72.48983606557374</v>
       </c>
       <c r="L16" t="n">
-        <v>93.03013114754098</v>
+        <v>92.76203278688526</v>
       </c>
       <c r="M16" t="n">
-        <v>98.0872295081967</v>
+        <v>97.80455737704916</v>
       </c>
       <c r="N16" t="n">
-        <v>95.75493442622957</v>
+        <v>95.47898360655743</v>
       </c>
       <c r="O16" t="n">
-        <v>88.44518032786888</v>
+        <v>88.19029508196724</v>
       </c>
       <c r="P16" t="n">
-        <v>75.68013114754095</v>
+        <v>75.4620327868852</v>
       </c>
       <c r="Q16" t="n">
-        <v>52.397</v>
+        <v>52.246</v>
       </c>
       <c r="R16" t="n">
-        <v>28.13544262295081</v>
+        <v>28.0543606557377</v>
       </c>
       <c r="S16" t="n">
-        <v>10.90490163934426</v>
+        <v>10.87347540983606</v>
       </c>
       <c r="T16" t="n">
-        <v>2.673606557377048</v>
+        <v>2.665901639344261</v>
       </c>
       <c r="U16" t="n">
-        <v>0.03413114754098364</v>
+        <v>0.03403278688524593</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -34746,19 +34746,19 @@
         <v>374</v>
       </c>
       <c r="K2" t="n">
-        <v>52.67130150753769</v>
+        <v>299.6321147587161</v>
       </c>
       <c r="L2" t="n">
-        <v>65.34340703517586</v>
+        <v>374</v>
       </c>
       <c r="M2" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>374</v>
       </c>
       <c r="O2" t="n">
-        <v>181.6174062160025</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>59.25677413017286</v>
@@ -34877,34 +34877,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I4" t="n">
-        <v>228.952183724144</v>
+        <v>107.6663312933602</v>
       </c>
       <c r="J4" t="n">
-        <v>169.3867891596375</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>133.058570461152</v>
       </c>
       <c r="L4" t="n">
         <v>4.06650298976183</v>
@@ -34928,16 +34928,16 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>40.86342193648881</v>
       </c>
       <c r="T4" t="n">
-        <v>190.7690400511193</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0517398730831</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>173.6271901612903</v>
@@ -34946,7 +34946,7 @@
         <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="5">
@@ -34980,10 +34980,10 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>374</v>
+        <v>181.6174062160024</v>
       </c>
       <c r="K5" t="n">
-        <v>234.2887077235401</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L5" t="n">
         <v>65.34340703517591</v>
@@ -35001,7 +35001,7 @@
         <v>59.25677413017286</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35123,28 +35123,28 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>155.141864863388</v>
       </c>
       <c r="H7" t="n">
-        <v>172.8802509475617</v>
+        <v>37.53559154339577</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>133.058570461152</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>4.06650298976183</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35168,16 +35168,16 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>190.7690400511193</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>3.238208465419397</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>152.5563545698924</v>
@@ -35217,28 +35217,28 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
+        <v>0.1006972724976123</v>
+      </c>
+      <c r="K8" t="n">
         <v>374</v>
       </c>
-      <c r="K8" t="n">
-        <v>52.67130150753769</v>
-      </c>
       <c r="L8" t="n">
-        <v>246.9608132511783</v>
+        <v>374</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="N8" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>299.5314174862185</v>
       </c>
       <c r="P8" t="n">
         <v>59.25677413017286</v>
       </c>
       <c r="Q8" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35351,31 +35351,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>155.141864863388</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>172.8802509475617</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>228.952183724144</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>75.87914317208183</v>
+        <v>374</v>
       </c>
       <c r="K10" t="n">
         <v>133.058570461152</v>
@@ -35405,22 +35405,22 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>190.7690400511193</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>103.0100408967006</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35454,25 +35454,25 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>513.658479084785</v>
+        <v>513.3172780797598</v>
       </c>
       <c r="K11" t="n">
-        <v>648</v>
+        <v>394.6141629811336</v>
       </c>
       <c r="L11" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="M11" t="n">
-        <v>391.0579288305826</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="O11" t="n">
-        <v>164.7897032902292</v>
+        <v>164.1123615816865</v>
       </c>
       <c r="P11" t="n">
-        <v>200.3120706125849</v>
+        <v>199.733975135198</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -35533,25 +35533,25 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>195.7248986905059</v>
+        <v>195.5216817093738</v>
       </c>
       <c r="K12" t="n">
-        <v>311.6274301124894</v>
+        <v>311.2800999238102</v>
       </c>
       <c r="L12" t="n">
-        <v>436.150196103404</v>
+        <v>435.6831678015172</v>
       </c>
       <c r="M12" t="n">
-        <v>276.0650421645042</v>
+        <v>275.5200421645043</v>
       </c>
       <c r="N12" t="n">
-        <v>328.7468614294096</v>
+        <v>328.1874369011077</v>
       </c>
       <c r="O12" t="n">
-        <v>419.0391822801049</v>
+        <v>418.5274181291614</v>
       </c>
       <c r="P12" t="n">
-        <v>256.1913441372947</v>
+        <v>255.7806082882381</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -35603,19 +35603,19 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G13" t="n">
-        <v>76.58186486338801</v>
+        <v>76.58006158469948</v>
       </c>
       <c r="H13" t="n">
-        <v>97.79225094756171</v>
+        <v>97.77621816067646</v>
       </c>
       <c r="I13" t="n">
-        <v>163.184183724144</v>
+        <v>163.1299542159473</v>
       </c>
       <c r="J13" t="n">
-        <v>324.7905079613318</v>
+        <v>329.8432150985184</v>
       </c>
       <c r="K13" t="n">
-        <v>105.178570461152</v>
+        <v>104.9690622644307</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -35642,10 +35642,10 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>113.6490400511193</v>
+        <v>110.4729577180263</v>
       </c>
       <c r="U13" t="n">
-        <v>170.0757398730831</v>
+        <v>170.0756415124273</v>
       </c>
       <c r="V13" t="n">
         <v>121.8296897837838</v>
@@ -35691,28 +35691,28 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>513.658479084785</v>
+        <v>513.3172780797598</v>
       </c>
       <c r="K14" t="n">
-        <v>648</v>
+        <v>450.3773067023617</v>
       </c>
       <c r="L14" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="M14" t="n">
-        <v>391.0579288305826</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>164.7897032902292</v>
+        <v>164.1123615816865</v>
       </c>
       <c r="P14" t="n">
-        <v>200.3120706125849</v>
+        <v>199.733975135198</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>593.2368562787717</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35770,25 +35770,25 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>195.7248986905059</v>
+        <v>195.5216817093738</v>
       </c>
       <c r="K15" t="n">
-        <v>311.6274301124894</v>
+        <v>311.2800999238102</v>
       </c>
       <c r="L15" t="n">
-        <v>436.150196103404</v>
+        <v>435.6831678015172</v>
       </c>
       <c r="M15" t="n">
-        <v>276.0650421645042</v>
+        <v>275.5200421645043</v>
       </c>
       <c r="N15" t="n">
-        <v>328.7468614294096</v>
+        <v>328.1874369011077</v>
       </c>
       <c r="O15" t="n">
-        <v>419.0391822801049</v>
+        <v>418.5274181291614</v>
       </c>
       <c r="P15" t="n">
-        <v>256.1913441372947</v>
+        <v>255.7806082882381</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -35837,22 +35837,22 @@
         <v>40.01909516304346</v>
       </c>
       <c r="F16" t="n">
-        <v>46.61714403225807</v>
+        <v>43.44876661719772</v>
       </c>
       <c r="G16" t="n">
-        <v>76.58186486338801</v>
+        <v>76.58006158469948</v>
       </c>
       <c r="H16" t="n">
-        <v>97.79225094756171</v>
+        <v>97.77621816067648</v>
       </c>
       <c r="I16" t="n">
-        <v>163.184183724144</v>
+        <v>163.1299542159473</v>
       </c>
       <c r="J16" t="n">
-        <v>329.9707069017971</v>
+        <v>329.8432150985184</v>
       </c>
       <c r="K16" t="n">
-        <v>105.178570461152</v>
+        <v>104.9690622644307</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -35879,10 +35879,10 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>113.6490400511193</v>
+        <v>113.6413351330866</v>
       </c>
       <c r="U16" t="n">
-        <v>164.8955409326179</v>
+        <v>170.0756415124273</v>
       </c>
       <c r="V16" t="n">
         <v>121.8296897837838</v>
@@ -35928,25 +35928,25 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>513.658479084785</v>
+        <v>83.35374249862829</v>
       </c>
       <c r="K17" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="L17" t="n">
-        <v>648</v>
+        <v>220.1374974874373</v>
       </c>
       <c r="M17" t="n">
-        <v>391.0579288305826</v>
+        <v>154.4968345014831</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="O17" t="n">
         <v>164.7897032902292</v>
       </c>
       <c r="P17" t="n">
-        <v>200.3120706125849</v>
+        <v>649</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -36071,7 +36071,7 @@
         <v>35.46378194444452</v>
       </c>
       <c r="E19" t="n">
-        <v>40.01909516304346</v>
+        <v>34.83889622257817</v>
       </c>
       <c r="F19" t="n">
         <v>46.61714403225807</v>
@@ -36086,7 +36086,7 @@
         <v>163.184183724144</v>
       </c>
       <c r="J19" t="n">
-        <v>324.7905079613318</v>
+        <v>329.9707069017971</v>
       </c>
       <c r="K19" t="n">
         <v>105.178570461152</v>
@@ -36168,16 +36168,16 @@
         <v>83.35374249862829</v>
       </c>
       <c r="K20" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="L20" t="n">
-        <v>220.1374974874373</v>
+        <v>649</v>
       </c>
       <c r="M20" t="n">
-        <v>648</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>601.2251679293022</v>
+        <v>229.651279469423</v>
       </c>
       <c r="O20" t="n">
         <v>164.7897032902292</v>
@@ -36186,7 +36186,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>593.6709819069124</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36323,7 +36323,7 @@
         <v>163.184183724144</v>
       </c>
       <c r="J22" t="n">
-        <v>324.7905079613318</v>
+        <v>329.9707069017971</v>
       </c>
       <c r="K22" t="n">
         <v>105.178570461152</v>
@@ -36368,7 +36368,7 @@
         <v>73.55635456989245</v>
       </c>
       <c r="Y22" t="n">
-        <v>33.53464715053764</v>
+        <v>28.35444821007238</v>
       </c>
     </row>
     <row r="23">
@@ -36405,16 +36405,16 @@
         <v>513.658479084785</v>
       </c>
       <c r="K23" t="n">
-        <v>391.0579288305828</v>
+        <v>177.4460351758794</v>
       </c>
       <c r="L23" t="n">
-        <v>648</v>
+        <v>220.1374974874373</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>50.76301021994979</v>
       </c>
       <c r="N23" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="O23" t="n">
         <v>164.7897032902292</v>
@@ -36423,10 +36423,10 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>593.6709819069124</v>
       </c>
       <c r="R23" t="n">
-        <v>2.985714930062643e-11</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -36548,7 +36548,7 @@
         <v>40.01909516304346</v>
       </c>
       <c r="F25" t="n">
-        <v>46.61714403225807</v>
+        <v>41.43694509179277</v>
       </c>
       <c r="G25" t="n">
         <v>76.58186486338801</v>
@@ -36560,7 +36560,7 @@
         <v>163.184183724144</v>
       </c>
       <c r="J25" t="n">
-        <v>324.7905079613318</v>
+        <v>329.9707069017971</v>
       </c>
       <c r="K25" t="n">
         <v>105.178570461152</v>
@@ -36642,25 +36642,25 @@
         <v>83.35374249862829</v>
       </c>
       <c r="K26" t="n">
-        <v>648.0000000000033</v>
+        <v>649</v>
       </c>
       <c r="L26" t="n">
-        <v>220.1374974874371</v>
+        <v>649</v>
       </c>
       <c r="M26" t="n">
-        <v>648.0000000000038</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>601.2251679293081</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>164.7897032902292</v>
       </c>
       <c r="P26" t="n">
-        <v>200.3120706125849</v>
+        <v>429.9633500820079</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>593.6709819069124</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36791,7 +36791,7 @@
         <v>76.58186486338801</v>
       </c>
       <c r="H28" t="n">
-        <v>97.79225094756171</v>
+        <v>92.61205200709649</v>
       </c>
       <c r="I28" t="n">
         <v>163.184183724144</v>
@@ -36842,7 +36842,7 @@
         <v>73.55635456989245</v>
       </c>
       <c r="Y28" t="n">
-        <v>28.35444821007238</v>
+        <v>33.53464715053764</v>
       </c>
     </row>
     <row r="29">
@@ -36879,25 +36879,25 @@
         <v>83.35374249862829</v>
       </c>
       <c r="K29" t="n">
-        <v>648.0000000000033</v>
+        <v>177.4460351758794</v>
       </c>
       <c r="L29" t="n">
-        <v>220.1374974874371</v>
+        <v>220.1374974874373</v>
       </c>
       <c r="M29" t="n">
-        <v>648.0000000000033</v>
+        <v>197.1695207089205</v>
       </c>
       <c r="N29" t="n">
-        <v>601.2251679293086</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>164.7897032902292</v>
+        <v>649</v>
       </c>
       <c r="P29" t="n">
-        <v>200.3120706125849</v>
+        <v>649</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>593.6709819069124</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37034,7 +37034,7 @@
         <v>163.184183724144</v>
       </c>
       <c r="J31" t="n">
-        <v>324.790507961332</v>
+        <v>324.7905079613318</v>
       </c>
       <c r="K31" t="n">
         <v>105.178570461152</v>
@@ -37116,28 +37116,28 @@
         <v>83.35374249862829</v>
       </c>
       <c r="K32" t="n">
-        <v>177.4460351758794</v>
+        <v>649</v>
       </c>
       <c r="L32" t="n">
         <v>220.1374974874373</v>
       </c>
       <c r="M32" t="n">
-        <v>648.0000000000051</v>
+        <v>649</v>
       </c>
       <c r="N32" t="n">
-        <v>478.1081508465184</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>164.7897032902292</v>
+        <v>649</v>
       </c>
       <c r="P32" t="n">
         <v>200.3120706125849</v>
       </c>
       <c r="Q32" t="n">
-        <v>593.6709819069124</v>
+        <v>118.9744671791273</v>
       </c>
       <c r="R32" t="n">
-        <v>3.674726067769407e-11</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -37356,13 +37356,13 @@
         <v>177.4460351758794</v>
       </c>
       <c r="L35" t="n">
-        <v>473.4317817560496</v>
+        <v>561.0000000000206</v>
       </c>
       <c r="M35" t="n">
-        <v>561.000000000001</v>
+        <v>473.4317817560599</v>
       </c>
       <c r="N35" t="n">
-        <v>561.000000000001</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>164.7897032902292</v>
@@ -37371,7 +37371,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>561.0000000000128</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37441,10 +37441,10 @@
         <v>276.0650421645042</v>
       </c>
       <c r="N36" t="n">
-        <v>328.7468614294096</v>
+        <v>326.5352398451116</v>
       </c>
       <c r="O36" t="n">
-        <v>416.8275606957657</v>
+        <v>419.0391822801049</v>
       </c>
       <c r="P36" t="n">
         <v>256.1913441372947</v>
@@ -37484,7 +37484,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>57.88619966292134</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
         <v>72.27475335195533</v>
@@ -37493,10 +37493,10 @@
         <v>59.46378194444452</v>
       </c>
       <c r="E37" t="n">
-        <v>64.01909516304346</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>70.61714403225807</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
         <v>100.581864863388</v>
@@ -37505,10 +37505,10 @@
         <v>121.7922509475617</v>
       </c>
       <c r="I37" t="n">
-        <v>187.184183724144</v>
+        <v>144.0888409924763</v>
       </c>
       <c r="J37" t="n">
-        <v>8.970706901797143</v>
+        <v>353.9707069017971</v>
       </c>
       <c r="K37" t="n">
         <v>129.178570461152</v>
@@ -37538,10 +37538,10 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>137.6490400511193</v>
       </c>
       <c r="U37" t="n">
-        <v>91.94025674079867</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
         <v>145.8296897837838</v>
@@ -37550,10 +37550,10 @@
         <v>118.6271901612903</v>
       </c>
       <c r="X37" t="n">
-        <v>97.55635456989245</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>57.53464715053764</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -37584,34 +37584,34 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>9.897357905183617e-12</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>83.35374249862829</v>
+        <v>513.658479084785</v>
       </c>
       <c r="K38" t="n">
-        <v>561.0000000000102</v>
+        <v>177.4460351758794</v>
       </c>
       <c r="L38" t="n">
-        <v>220.1374974874373</v>
+        <v>220.1374974874371</v>
       </c>
       <c r="M38" t="n">
-        <v>561.0000000000028</v>
+        <v>188.0913215852951</v>
       </c>
       <c r="N38" t="n">
-        <v>430.7403194444808</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>164.7897032902292</v>
+        <v>561.0000000000092</v>
       </c>
       <c r="P38" t="n">
-        <v>200.3120706125849</v>
+        <v>561.0000000000092</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>-1.653626730496233e-11</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -37672,7 +37672,7 @@
         <v>311.6274301124894</v>
       </c>
       <c r="L39" t="n">
-        <v>433.9385745190646</v>
+        <v>433.9385745190894</v>
       </c>
       <c r="M39" t="n">
         <v>276.0650421645042</v>
@@ -37721,10 +37721,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>57.88619966292134</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>72.27475335195533</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
         <v>59.46378194444452</v>
@@ -37733,7 +37733,7 @@
         <v>64.01909516304346</v>
       </c>
       <c r="F40" t="n">
-        <v>70.61714403225807</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
         <v>100.581864863388</v>
@@ -37742,16 +37742,16 @@
         <v>121.7922509475617</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>187.184183724144</v>
       </c>
       <c r="J40" t="n">
-        <v>8.970706901797143</v>
+        <v>353.9707069017971</v>
       </c>
       <c r="K40" t="n">
-        <v>129.178570461152</v>
+        <v>115.4097215097944</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>14.48250298976181</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -37778,19 +37778,19 @@
         <v>137.6490400511193</v>
       </c>
       <c r="U40" t="n">
-        <v>155.9579034035856</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>145.8296897837838</v>
       </c>
       <c r="W40" t="n">
-        <v>118.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
         <v>97.55635456989245</v>
       </c>
       <c r="Y40" t="n">
-        <v>57.53464715053764</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -37824,16 +37824,16 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>513.658479084785</v>
+        <v>83.35374249862829</v>
       </c>
       <c r="K41" t="n">
-        <v>177.4460351758794</v>
+        <v>561.0000000000206</v>
       </c>
       <c r="L41" t="n">
-        <v>220.1374974874373</v>
+        <v>290.1898875445188</v>
       </c>
       <c r="M41" t="n">
-        <v>23.3016182950331</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -37842,10 +37842,10 @@
         <v>164.7897032902292</v>
       </c>
       <c r="P41" t="n">
-        <v>561.0000000000047</v>
+        <v>561.0000000000092</v>
       </c>
       <c r="Q41" t="n">
-        <v>561.0000000000047</v>
+        <v>561.0000000000092</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37909,7 +37909,7 @@
         <v>311.6274301124894</v>
       </c>
       <c r="L42" t="n">
-        <v>433.9385745190646</v>
+        <v>436.150196103404</v>
       </c>
       <c r="M42" t="n">
         <v>276.0650421645042</v>
@@ -37918,7 +37918,7 @@
         <v>328.7468614294096</v>
       </c>
       <c r="O42" t="n">
-        <v>419.0391822801049</v>
+        <v>416.8275606957978</v>
       </c>
       <c r="P42" t="n">
         <v>256.1913441372947</v>
@@ -37958,28 +37958,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>57.88619966292134</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
         <v>72.27475335195533</v>
       </c>
       <c r="D43" t="n">
-        <v>59.46378194444452</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
         <v>64.01909516304346</v>
       </c>
       <c r="F43" t="n">
-        <v>70.61714403225807</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>100.581864863388</v>
       </c>
       <c r="H43" t="n">
-        <v>121.7922509475617</v>
+        <v>57.98872691170984</v>
       </c>
       <c r="I43" t="n">
-        <v>187.184183724144</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
         <v>353.9707069017971</v>
@@ -37988,7 +37988,7 @@
         <v>129.178570461152</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>14.48250298976183</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -38012,19 +38012,19 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>137.6490400511193</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>194.0757398730831</v>
       </c>
       <c r="V43" t="n">
-        <v>105.390668947625</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
         <v>118.6271901612903</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>97.55635456989245</v>
       </c>
       <c r="Y43" t="n">
         <v>57.53464715053764</v>
@@ -38061,7 +38061,7 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>83.35374249862829</v>
+        <v>513.658479084785</v>
       </c>
       <c r="K44" t="n">
         <v>177.4460351758794</v>
@@ -38070,19 +38070,19 @@
         <v>220.1374974874371</v>
       </c>
       <c r="M44" t="n">
-        <v>253.2942842685945</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>561.0000000000101</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>164.7897032902292</v>
+        <v>561.0000000000094</v>
       </c>
       <c r="P44" t="n">
         <v>200.3120706125849</v>
       </c>
       <c r="Q44" t="n">
-        <v>561.0000000000101</v>
+        <v>548.7792509727188</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38155,7 +38155,7 @@
         <v>328.7468614294096</v>
       </c>
       <c r="O45" t="n">
-        <v>416.827560695773</v>
+        <v>416.827560695807</v>
       </c>
       <c r="P45" t="n">
         <v>256.1913441372947</v>
@@ -38198,7 +38198,7 @@
         <v>57.88619966292134</v>
       </c>
       <c r="C46" t="n">
-        <v>72.27475335195533</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
         <v>59.46378194444452</v>
@@ -38210,7 +38210,7 @@
         <v>70.61714403225807</v>
       </c>
       <c r="G46" t="n">
-        <v>100.581864863388</v>
+        <v>25.53387925869918</v>
       </c>
       <c r="H46" t="n">
         <v>121.7922509475617</v>
@@ -38219,13 +38219,13 @@
         <v>187.184183724144</v>
       </c>
       <c r="J46" t="n">
-        <v>8.970706901797143</v>
+        <v>353.9707069017971</v>
       </c>
       <c r="K46" t="n">
         <v>129.178570461152</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>14.48250298976181</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -38252,10 +38252,10 @@
         <v>137.6490400511193</v>
       </c>
       <c r="U46" t="n">
-        <v>123.8647213998713</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>145.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
         <v>118.6271901612903</v>
@@ -38264,7 +38264,7 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>57.53464715053764</v>
       </c>
     </row>
   </sheetData>
